--- a/tests/fixtures/etoro/releve-demo.xlsx
+++ b/tests/fixtures/etoro/releve-demo.xlsx
@@ -10,7 +10,7 @@
 </x:workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?><x:sst count="88"><x:si><x:r><x:t xml:space="preserve">No</x:t></x:r><x:r><x:t xml:space="preserve">m</x:t></x:r></x:si><x:si><x:t>Totaux</x:t></x:si><x:si><x:t>Deposits</x:t></x:si><x:si><x:t>Récapitulatif du compte (USD)</x:t></x:si><x:si><x:t>Total&#10; en (USD)</x:t></x:si><x:si><x:t>Snapshot Date</x:t></x:si><x:si><x:t>Asset</x:t></x:si><x:si><x:t>Position ID</x:t></x:si><x:si><x:t>Direction</x:t></x:si><x:si><x:t>Open Date</x:t></x:si><x:si><x:t>Leverage</x:t></x:si><x:si><x:t>Open Rate</x:t></x:si><x:si><x:t>Units</x:t></x:si><x:si><x:t>Current Rate</x:t></x:si><x:si><x:t>Value in USD</x:t></x:si><x:si><x:t>Value in EUR</x:t></x:si><x:si><x:t>Type</x:t></x:si><x:si><x:t>ISIN</x:t></x:si><x:si><x:t>DEMO</x:t></x:si><x:si><x:t>p-101</x:t></x:si><x:si><x:t>Long</x:t></x:si><x:si><x:t>12/02/2025 09:30:00</x:t></x:si><x:si><x:t>X1</x:t></x:si><x:si><x:t>Stocks</x:t></x:si><x:si><x:t>XX0000000001</x:t></x:si><x:si><x:t>IDX</x:t></x:si><x:si><x:t>p-102</x:t></x:si><x:si><x:t>03/03/2025 11:00:00</x:t></x:si><x:si><x:t>ETF</x:t></x:si><x:si><x:t>XX0000000002</x:t></x:si><x:si><x:t>ZCH</x:t></x:si><x:si><x:t>p-103</x:t></x:si><x:si><x:t>20/05/2025 16:45:00</x:t></x:si><x:si><x:t>Crypto Currencies</x:t></x:si><x:si><x:t>XX0000000003</x:t></x:si><x:si><x:t>LEVR</x:t></x:si><x:si><x:t>p-104</x:t></x:si><x:si><x:t>02/06/2025 10:00:00</x:t></x:si><x:si><x:t>X2</x:t></x:si><x:si><x:t>XX0000000004</x:t></x:si><x:si><x:t>Identifiant de position</x:t></x:si><x:si><x:t>Action</x:t></x:si><x:si><x:t>Long / Short</x:t></x:si><x:si><x:t>Montant</x:t></x:si><x:si><x:t>Unités</x:t></x:si><x:si><x:t>Date d'ouverture</x:t></x:si><x:si><x:t>Date de clôture</x:t></x:si><x:si><x:t>Effet de levier</x:t></x:si><x:si><x:t>Frais de spread (USD)</x:t></x:si><x:si><x:t>Spread du marché (USD)</x:t></x:si><x:si><x:t>Profit (USD)</x:t></x:si><x:si><x:t>Profit (EUR)</x:t></x:si><x:si><x:t>Taux de change à l'ouverture (USD)</x:t></x:si><x:si><x:t>Taux de change à la clôture (USD)</x:t></x:si><x:si><x:t>Taux à l'ouverture</x:t></x:si><x:si><x:t>Taux à la clôture</x:t></x:si><x:si><x:t>Taux Take Profit</x:t></x:si><x:si><x:t>Taux Stop Loss</x:t></x:si><x:si><x:t>Frais overnight et dividendes</x:t></x:si><x:si><x:t>Copie de</x:t></x:si><x:si><x:t>Remarques</x:t></x:si><x:si><x:t>p-201</x:t></x:si><x:si><x:t>05/01/2025 10:00:00</x:t></x:si><x:si><x:t>10/04/2025 15:00:00</x:t></x:si><x:si><x:t>1</x:t></x:si><x:si><x:t>Actions</x:t></x:si><x:si><x:t>p-202</x:t></x:si><x:si><x:t>CFDX</x:t></x:si><x:si><x:t>06/01/2025 10:00:00</x:t></x:si><x:si><x:t>11/04/2025 15:00:00</x:t></x:si><x:si><x:t>2</x:t></x:si><x:si><x:t>CFD</x:t></x:si><x:si><x:t>XX0000000005</x:t></x:si><x:si><x:t>Date</x:t></x:si><x:si><x:t>Détails</x:t></x:si><x:si><x:t>Variation Fonds propres réalisés</x:t></x:si><x:si><x:t>Équité réalisée</x:t></x:si><x:si><x:t>Solde</x:t></x:si><x:si><x:t>Type d'actif</x:t></x:si><x:si><x:t>NWA (fonds non retirables)</x:t></x:si><x:si><x:t>01/02/2025 08:00:00</x:t></x:si><x:si><x:t>Dépôt</x:t></x:si><x:si><x:t>Virement</x:t></x:si><x:si><x:t>-</x:t></x:si><x:si><x:t>Position ouverte</x:t></x:si><x:si><x:t>Crypto-monnaies</x:t></x:si><x:si><x:t>15/07/2025 12:00:00</x:t></x:si><x:si><x:t>Frais overnight</x:t></x:si></x:sst>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?><x:sst count="87"><x:si><x:r><x:t xml:space="preserve">No</x:t></x:r><x:r><x:t xml:space="preserve">m</x:t></x:r></x:si><x:si><x:t>Totaux</x:t></x:si><x:si><x:t>Deposits</x:t></x:si><x:si><x:t>Récapitulatif du compte (USD)</x:t></x:si><x:si><x:t>Total&#10; en (USD)</x:t></x:si><x:si><x:t>Snapshot Date</x:t></x:si><x:si><x:t>Asset</x:t></x:si><x:si><x:t>Position ID</x:t></x:si><x:si><x:t>Direction</x:t></x:si><x:si><x:t>Open Date</x:t></x:si><x:si><x:t>Leverage</x:t></x:si><x:si><x:t>Open Rate</x:t></x:si><x:si><x:t>Units</x:t></x:si><x:si><x:t>Current Rate</x:t></x:si><x:si><x:t>Value in USD</x:t></x:si><x:si><x:t>Value in EUR</x:t></x:si><x:si><x:t>Type</x:t></x:si><x:si><x:t>ISIN</x:t></x:si><x:si><x:t>Demo Industries Inc.</x:t></x:si><x:si><x:t>p-101</x:t></x:si><x:si><x:t>Long</x:t></x:si><x:si><x:t>12/02/2025 09:30:00</x:t></x:si><x:si><x:t>X1</x:t></x:si><x:si><x:t>Stocks</x:t></x:si><x:si><x:t>XX0000000001</x:t></x:si><x:si><x:t>Indice Monde UCITS ETF</x:t></x:si><x:si><x:t>p-102</x:t></x:si><x:si><x:t>03/03/2025 11:00:00</x:t></x:si><x:si><x:t>ETF</x:t></x:si><x:si><x:t>XX0000000002</x:t></x:si><x:si><x:t>Bitcoin (BTC)</x:t></x:si><x:si><x:t>p-103</x:t></x:si><x:si><x:t>20/05/2025 16:45:00</x:t></x:si><x:si><x:t>Crypto Currencies</x:t></x:si><x:si><x:t>-</x:t></x:si><x:si><x:t>Levier SA</x:t></x:si><x:si><x:t>p-104</x:t></x:si><x:si><x:t>02/06/2025 10:00:00</x:t></x:si><x:si><x:t>X2</x:t></x:si><x:si><x:t>XX0000000004</x:t></x:si><x:si><x:t>Identifiant de position</x:t></x:si><x:si><x:t>Action</x:t></x:si><x:si><x:t>Long / Short</x:t></x:si><x:si><x:t>Montant</x:t></x:si><x:si><x:t>Unités</x:t></x:si><x:si><x:t>Date d'ouverture</x:t></x:si><x:si><x:t>Date de clôture</x:t></x:si><x:si><x:t>Effet de levier</x:t></x:si><x:si><x:t>Frais de spread (USD)</x:t></x:si><x:si><x:t>Spread du marché (USD)</x:t></x:si><x:si><x:t>Profit (USD)</x:t></x:si><x:si><x:t>Profit (EUR)</x:t></x:si><x:si><x:t>Taux de change à l'ouverture (USD)</x:t></x:si><x:si><x:t>Taux de change à la clôture (USD)</x:t></x:si><x:si><x:t>Taux à l'ouverture</x:t></x:si><x:si><x:t>Taux à la clôture</x:t></x:si><x:si><x:t>Taux Take Profit</x:t></x:si><x:si><x:t>Taux Stop Loss</x:t></x:si><x:si><x:t>Frais overnight et dividendes</x:t></x:si><x:si><x:t>Copie de</x:t></x:si><x:si><x:t>Remarques</x:t></x:si><x:si><x:t>p-201</x:t></x:si><x:si><x:t>05/01/2025 10:00:00</x:t></x:si><x:si><x:t>10/04/2025 15:00:00</x:t></x:si><x:si><x:t>1</x:t></x:si><x:si><x:t>Actions</x:t></x:si><x:si><x:t>p-202</x:t></x:si><x:si><x:t>Pétrole CFD</x:t></x:si><x:si><x:t>06/01/2025 10:00:00</x:t></x:si><x:si><x:t>11/04/2025 15:00:00</x:t></x:si><x:si><x:t>2</x:t></x:si><x:si><x:t>CFD</x:t></x:si><x:si><x:t>XX0000000005</x:t></x:si><x:si><x:t>Date</x:t></x:si><x:si><x:t>Détails</x:t></x:si><x:si><x:t>Variation Fonds propres réalisés</x:t></x:si><x:si><x:t>Équité réalisée</x:t></x:si><x:si><x:t>Solde</x:t></x:si><x:si><x:t>Type d'actif</x:t></x:si><x:si><x:t>NWA (fonds non retirables)</x:t></x:si><x:si><x:t>01/02/2025 08:00:00</x:t></x:si><x:si><x:t>Dépôt</x:t></x:si><x:si><x:t>Virement</x:t></x:si><x:si><x:t>Position ouverte</x:t></x:si><x:si><x:t>Crypto-monnaies</x:t></x:si><x:si><x:t>15/07/2025 12:00:00</x:t></x:si><x:si><x:t>Frais overnight</x:t></x:si></x:sst>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?><x:worksheet><x:sheetData><x:row r="1"><x:c r="A1" t="s"><x:v>0</x:v></x:c><x:c r="B1" t="s"><x:v>1</x:v></x:c></x:row><x:row r="2"><x:c r="A2" t="s"><x:v>2</x:v></x:c><x:c r="B2"><x:v>5000</x:v></x:c></x:row><x:row r="3"><x:c r="A3" t="s"><x:v>3</x:v></x:c><x:c r="B3" t="s"><x:v>4</x:v></x:c></x:row></x:sheetData></x:worksheet>
@@ -22,5 +22,5 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?><x:worksheet><x:sheetData><x:row r="1"><x:c r="A1" t="s"><x:v>40</x:v></x:c><x:c r="B1" t="s"><x:v>41</x:v></x:c><x:c r="C1" t="s"><x:v>42</x:v></x:c><x:c r="D1" t="s"><x:v>43</x:v></x:c><x:c r="E1" t="s"><x:v>44</x:v></x:c><x:c r="F1" t="s"><x:v>45</x:v></x:c><x:c r="G1" t="s"><x:v>46</x:v></x:c><x:c r="H1" t="s"><x:v>47</x:v></x:c><x:c r="I1" t="s"><x:v>48</x:v></x:c><x:c r="J1" t="s"><x:v>49</x:v></x:c><x:c r="K1" t="s"><x:v>50</x:v></x:c><x:c r="L1" t="s"><x:v>51</x:v></x:c><x:c r="M1" t="s"><x:v>52</x:v></x:c><x:c r="N1" t="s"><x:v>53</x:v></x:c><x:c r="O1" t="s"><x:v>54</x:v></x:c><x:c r="P1" t="s"><x:v>55</x:v></x:c><x:c r="Q1" t="s"><x:v>56</x:v></x:c><x:c r="R1" t="s"><x:v>57</x:v></x:c><x:c r="S1" t="s"><x:v>58</x:v></x:c><x:c r="T1" t="s"><x:v>59</x:v></x:c><x:c r="U1" t="s"><x:v>16</x:v></x:c><x:c r="V1" t="s"><x:v>17</x:v></x:c><x:c r="W1" t="s"><x:v>60</x:v></x:c></x:row><x:row r="2"><x:c r="A2" t="s"><x:v>61</x:v></x:c><x:c r="B2" t="s"><x:v>18</x:v></x:c><x:c r="C2" t="s"><x:v>20</x:v></x:c><x:c r="D2"><x:v>200</x:v></x:c><x:c r="E2"><x:v>5</x:v></x:c><x:c r="F2" t="s"><x:v>62</x:v></x:c><x:c r="G2" t="s"><x:v>63</x:v></x:c><x:c r="H2" t="s"><x:v>64</x:v></x:c><x:c r="I2"><x:v>0</x:v></x:c><x:c r="J2"><x:v>0</x:v></x:c><x:c r="K2"><x:v>40</x:v></x:c><x:c r="L2"><x:v>36</x:v></x:c><x:c r="M2"><x:v>1</x:v></x:c><x:c r="N2"><x:v>1</x:v></x:c><x:c r="O2"><x:v>40</x:v></x:c><x:c r="P2"><x:v>48</x:v></x:c><x:c r="Q2"><x:v>0</x:v></x:c><x:c r="R2"><x:v>0</x:v></x:c><x:c r="S2"><x:v>0</x:v></x:c><x:c r="U2" t="s"><x:v>65</x:v></x:c><x:c r="V2" t="s"><x:v>24</x:v></x:c></x:row><x:row r="3"><x:c r="A3" t="s"><x:v>66</x:v></x:c><x:c r="B3" t="s"><x:v>67</x:v></x:c><x:c r="C3" t="s"><x:v>20</x:v></x:c><x:c r="D3"><x:v>100</x:v></x:c><x:c r="E3"><x:v>1</x:v></x:c><x:c r="F3" t="s"><x:v>68</x:v></x:c><x:c r="G3" t="s"><x:v>69</x:v></x:c><x:c r="H3" t="s"><x:v>70</x:v></x:c><x:c r="I3"><x:v>0</x:v></x:c><x:c r="J3"><x:v>0</x:v></x:c><x:c r="K3"><x:v>5</x:v></x:c><x:c r="L3"><x:v>4</x:v></x:c><x:c r="M3"><x:v>1</x:v></x:c><x:c r="N3"><x:v>1</x:v></x:c><x:c r="O3"><x:v>100</x:v></x:c><x:c r="P3"><x:v>105</x:v></x:c><x:c r="Q3"><x:v>0</x:v></x:c><x:c r="R3"><x:v>0</x:v></x:c><x:c r="S3"><x:v>0</x:v></x:c><x:c r="U3" t="s"><x:v>71</x:v></x:c><x:c r="V3" t="s"><x:v>72</x:v></x:c></x:row></x:sheetData></x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?><x:worksheet><x:sheetData><x:row r="1"><x:c r="A1" t="s"><x:v>73</x:v></x:c><x:c r="B1" t="s"><x:v>16</x:v></x:c><x:c r="C1" t="s"><x:v>74</x:v></x:c><x:c r="D1" t="s"><x:v>43</x:v></x:c><x:c r="E1" t="s"><x:v>44</x:v></x:c><x:c r="F1" t="s"><x:v>75</x:v></x:c><x:c r="G1" t="s"><x:v>76</x:v></x:c><x:c r="H1" t="s"><x:v>77</x:v></x:c><x:c r="I1" t="s"><x:v>40</x:v></x:c><x:c r="J1" t="s"><x:v>78</x:v></x:c><x:c r="K1" t="s"><x:v>79</x:v></x:c></x:row><x:row r="2"><x:c r="A2" t="s"><x:v>80</x:v></x:c><x:c r="B2" t="s"><x:v>81</x:v></x:c><x:c r="C2" t="s"><x:v>82</x:v></x:c><x:c r="D2"><x:v>5000</x:v></x:c><x:c r="E2" t="s"><x:v>83</x:v></x:c><x:c r="F2"><x:v>0</x:v></x:c><x:c r="G2"><x:v>0</x:v></x:c><x:c r="H2"><x:v>5000</x:v></x:c><x:c r="J2" t="s"><x:v>83</x:v></x:c><x:c r="K2"><x:v>0</x:v></x:c></x:row><x:row r="3"><x:c r="A3" t="s"><x:v>21</x:v></x:c><x:c r="B3" t="s"><x:v>84</x:v></x:c><x:c r="C3" t="s"><x:v>18</x:v></x:c><x:c r="D3"><x:v>400</x:v></x:c><x:c r="E3"><x:v>10</x:v></x:c><x:c r="F3"><x:v>0</x:v></x:c><x:c r="G3"><x:v>0</x:v></x:c><x:c r="H3"><x:v>4600</x:v></x:c><x:c r="I3" t="s"><x:v>19</x:v></x:c><x:c r="J3" t="s"><x:v>65</x:v></x:c><x:c r="K3"><x:v>0</x:v></x:c></x:row><x:row r="4"><x:c r="A4" t="s"><x:v>27</x:v></x:c><x:c r="B4" t="s"><x:v>84</x:v></x:c><x:c r="C4" t="s"><x:v>25</x:v></x:c><x:c r="D4"><x:v>450</x:v></x:c><x:c r="E4"><x:v>5</x:v></x:c><x:c r="F4"><x:v>0</x:v></x:c><x:c r="G4"><x:v>0</x:v></x:c><x:c r="H4"><x:v>4150</x:v></x:c><x:c r="I4" t="s"><x:v>26</x:v></x:c><x:c r="J4" t="s"><x:v>28</x:v></x:c><x:c r="K4"><x:v>0</x:v></x:c></x:row><x:row r="5"><x:c r="A5" t="s"><x:v>32</x:v></x:c><x:c r="B5" t="s"><x:v>84</x:v></x:c><x:c r="C5" t="s"><x:v>30</x:v></x:c><x:c r="D5"><x:v>600</x:v></x:c><x:c r="E5"><x:v>2</x:v></x:c><x:c r="F5"><x:v>0</x:v></x:c><x:c r="G5"><x:v>0</x:v></x:c><x:c r="H5"><x:v>3550</x:v></x:c><x:c r="I5" t="s"><x:v>31</x:v></x:c><x:c r="J5" t="s"><x:v>85</x:v></x:c><x:c r="K5"><x:v>0</x:v></x:c></x:row><x:row r="6"><x:c r="A6" t="s"><x:v>37</x:v></x:c><x:c r="B6" t="s"><x:v>84</x:v></x:c><x:c r="C6" t="s"><x:v>35</x:v></x:c><x:c r="D6"><x:v>60</x:v></x:c><x:c r="E6"><x:v>3</x:v></x:c><x:c r="F6"><x:v>0</x:v></x:c><x:c r="G6"><x:v>0</x:v></x:c><x:c r="H6"><x:v>3490</x:v></x:c><x:c r="I6" t="s"><x:v>36</x:v></x:c><x:c r="J6" t="s"><x:v>65</x:v></x:c><x:c r="K6"><x:v>0</x:v></x:c></x:row><x:row r="7"><x:c r="A7" t="s"><x:v>86</x:v></x:c><x:c r="B7" t="s"><x:v>87</x:v></x:c><x:c r="C7" t="s"><x:v>35</x:v></x:c><x:c r="D7"><x:v>-2</x:v></x:c><x:c r="E7" t="s"><x:v>83</x:v></x:c><x:c r="F7"><x:v>0</x:v></x:c><x:c r="G7"><x:v>0</x:v></x:c><x:c r="H7"><x:v>3488</x:v></x:c><x:c r="I7" t="s"><x:v>36</x:v></x:c><x:c r="J7" t="s"><x:v>65</x:v></x:c><x:c r="K7"><x:v>0</x:v></x:c></x:row></x:sheetData></x:worksheet>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?><x:worksheet><x:sheetData><x:row r="1"><x:c r="A1" t="s"><x:v>73</x:v></x:c><x:c r="B1" t="s"><x:v>16</x:v></x:c><x:c r="C1" t="s"><x:v>74</x:v></x:c><x:c r="D1" t="s"><x:v>43</x:v></x:c><x:c r="E1" t="s"><x:v>44</x:v></x:c><x:c r="F1" t="s"><x:v>75</x:v></x:c><x:c r="G1" t="s"><x:v>76</x:v></x:c><x:c r="H1" t="s"><x:v>77</x:v></x:c><x:c r="I1" t="s"><x:v>40</x:v></x:c><x:c r="J1" t="s"><x:v>78</x:v></x:c><x:c r="K1" t="s"><x:v>79</x:v></x:c></x:row><x:row r="2"><x:c r="A2" t="s"><x:v>80</x:v></x:c><x:c r="B2" t="s"><x:v>81</x:v></x:c><x:c r="C2" t="s"><x:v>82</x:v></x:c><x:c r="D2"><x:v>5000</x:v></x:c><x:c r="E2" t="s"><x:v>34</x:v></x:c><x:c r="F2"><x:v>0</x:v></x:c><x:c r="G2"><x:v>0</x:v></x:c><x:c r="H2"><x:v>5000</x:v></x:c><x:c r="J2" t="s"><x:v>34</x:v></x:c><x:c r="K2"><x:v>0</x:v></x:c></x:row><x:row r="3"><x:c r="A3" t="s"><x:v>21</x:v></x:c><x:c r="B3" t="s"><x:v>83</x:v></x:c><x:c r="C3" t="s"><x:v>18</x:v></x:c><x:c r="D3"><x:v>400</x:v></x:c><x:c r="E3"><x:v>10</x:v></x:c><x:c r="F3"><x:v>0</x:v></x:c><x:c r="G3"><x:v>0</x:v></x:c><x:c r="H3"><x:v>4600</x:v></x:c><x:c r="I3" t="s"><x:v>19</x:v></x:c><x:c r="J3" t="s"><x:v>65</x:v></x:c><x:c r="K3"><x:v>0</x:v></x:c></x:row><x:row r="4"><x:c r="A4" t="s"><x:v>27</x:v></x:c><x:c r="B4" t="s"><x:v>83</x:v></x:c><x:c r="C4" t="s"><x:v>25</x:v></x:c><x:c r="D4"><x:v>450</x:v></x:c><x:c r="E4"><x:v>5</x:v></x:c><x:c r="F4"><x:v>0</x:v></x:c><x:c r="G4"><x:v>0</x:v></x:c><x:c r="H4"><x:v>4150</x:v></x:c><x:c r="I4" t="s"><x:v>26</x:v></x:c><x:c r="J4" t="s"><x:v>28</x:v></x:c><x:c r="K4"><x:v>0</x:v></x:c></x:row><x:row r="5"><x:c r="A5" t="s"><x:v>32</x:v></x:c><x:c r="B5" t="s"><x:v>83</x:v></x:c><x:c r="C5" t="s"><x:v>30</x:v></x:c><x:c r="D5"><x:v>600</x:v></x:c><x:c r="E5"><x:v>2</x:v></x:c><x:c r="F5"><x:v>0</x:v></x:c><x:c r="G5"><x:v>0</x:v></x:c><x:c r="H5"><x:v>3550</x:v></x:c><x:c r="I5" t="s"><x:v>31</x:v></x:c><x:c r="J5" t="s"><x:v>84</x:v></x:c><x:c r="K5"><x:v>0</x:v></x:c></x:row><x:row r="6"><x:c r="A6" t="s"><x:v>37</x:v></x:c><x:c r="B6" t="s"><x:v>83</x:v></x:c><x:c r="C6" t="s"><x:v>35</x:v></x:c><x:c r="D6"><x:v>60</x:v></x:c><x:c r="E6"><x:v>3</x:v></x:c><x:c r="F6"><x:v>0</x:v></x:c><x:c r="G6"><x:v>0</x:v></x:c><x:c r="H6"><x:v>3490</x:v></x:c><x:c r="I6" t="s"><x:v>36</x:v></x:c><x:c r="J6" t="s"><x:v>65</x:v></x:c><x:c r="K6"><x:v>0</x:v></x:c></x:row><x:row r="7"><x:c r="A7" t="s"><x:v>85</x:v></x:c><x:c r="B7" t="s"><x:v>86</x:v></x:c><x:c r="C7" t="s"><x:v>35</x:v></x:c><x:c r="D7"><x:v>-2</x:v></x:c><x:c r="E7" t="s"><x:v>34</x:v></x:c><x:c r="F7"><x:v>0</x:v></x:c><x:c r="G7"><x:v>0</x:v></x:c><x:c r="H7"><x:v>3488</x:v></x:c><x:c r="I7" t="s"><x:v>36</x:v></x:c><x:c r="J7" t="s"><x:v>65</x:v></x:c><x:c r="K7"><x:v>0</x:v></x:c></x:row></x:sheetData></x:worksheet>
 </file>
--- a/tests/fixtures/etoro/releve-demo.xlsx
+++ b/tests/fixtures/etoro/releve-demo.xlsx
@@ -10,17 +10,17 @@
 </x:workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?><x:sst count="87"><x:si><x:r><x:t xml:space="preserve">No</x:t></x:r><x:r><x:t xml:space="preserve">m</x:t></x:r></x:si><x:si><x:t>Totaux</x:t></x:si><x:si><x:t>Deposits</x:t></x:si><x:si><x:t>Récapitulatif du compte (USD)</x:t></x:si><x:si><x:t>Total&#10; en (USD)</x:t></x:si><x:si><x:t>Snapshot Date</x:t></x:si><x:si><x:t>Asset</x:t></x:si><x:si><x:t>Position ID</x:t></x:si><x:si><x:t>Direction</x:t></x:si><x:si><x:t>Open Date</x:t></x:si><x:si><x:t>Leverage</x:t></x:si><x:si><x:t>Open Rate</x:t></x:si><x:si><x:t>Units</x:t></x:si><x:si><x:t>Current Rate</x:t></x:si><x:si><x:t>Value in USD</x:t></x:si><x:si><x:t>Value in EUR</x:t></x:si><x:si><x:t>Type</x:t></x:si><x:si><x:t>ISIN</x:t></x:si><x:si><x:t>Demo Industries Inc.</x:t></x:si><x:si><x:t>p-101</x:t></x:si><x:si><x:t>Long</x:t></x:si><x:si><x:t>12/02/2025 09:30:00</x:t></x:si><x:si><x:t>X1</x:t></x:si><x:si><x:t>Stocks</x:t></x:si><x:si><x:t>XX0000000001</x:t></x:si><x:si><x:t>Indice Monde UCITS ETF</x:t></x:si><x:si><x:t>p-102</x:t></x:si><x:si><x:t>03/03/2025 11:00:00</x:t></x:si><x:si><x:t>ETF</x:t></x:si><x:si><x:t>XX0000000002</x:t></x:si><x:si><x:t>Bitcoin (BTC)</x:t></x:si><x:si><x:t>p-103</x:t></x:si><x:si><x:t>20/05/2025 16:45:00</x:t></x:si><x:si><x:t>Crypto Currencies</x:t></x:si><x:si><x:t>-</x:t></x:si><x:si><x:t>Levier SA</x:t></x:si><x:si><x:t>p-104</x:t></x:si><x:si><x:t>02/06/2025 10:00:00</x:t></x:si><x:si><x:t>X2</x:t></x:si><x:si><x:t>XX0000000004</x:t></x:si><x:si><x:t>Identifiant de position</x:t></x:si><x:si><x:t>Action</x:t></x:si><x:si><x:t>Long / Short</x:t></x:si><x:si><x:t>Montant</x:t></x:si><x:si><x:t>Unités</x:t></x:si><x:si><x:t>Date d'ouverture</x:t></x:si><x:si><x:t>Date de clôture</x:t></x:si><x:si><x:t>Effet de levier</x:t></x:si><x:si><x:t>Frais de spread (USD)</x:t></x:si><x:si><x:t>Spread du marché (USD)</x:t></x:si><x:si><x:t>Profit (USD)</x:t></x:si><x:si><x:t>Profit (EUR)</x:t></x:si><x:si><x:t>Taux de change à l'ouverture (USD)</x:t></x:si><x:si><x:t>Taux de change à la clôture (USD)</x:t></x:si><x:si><x:t>Taux à l'ouverture</x:t></x:si><x:si><x:t>Taux à la clôture</x:t></x:si><x:si><x:t>Taux Take Profit</x:t></x:si><x:si><x:t>Taux Stop Loss</x:t></x:si><x:si><x:t>Frais overnight et dividendes</x:t></x:si><x:si><x:t>Copie de</x:t></x:si><x:si><x:t>Remarques</x:t></x:si><x:si><x:t>p-201</x:t></x:si><x:si><x:t>05/01/2025 10:00:00</x:t></x:si><x:si><x:t>10/04/2025 15:00:00</x:t></x:si><x:si><x:t>1</x:t></x:si><x:si><x:t>Actions</x:t></x:si><x:si><x:t>p-202</x:t></x:si><x:si><x:t>Pétrole CFD</x:t></x:si><x:si><x:t>06/01/2025 10:00:00</x:t></x:si><x:si><x:t>11/04/2025 15:00:00</x:t></x:si><x:si><x:t>2</x:t></x:si><x:si><x:t>CFD</x:t></x:si><x:si><x:t>XX0000000005</x:t></x:si><x:si><x:t>Date</x:t></x:si><x:si><x:t>Détails</x:t></x:si><x:si><x:t>Variation Fonds propres réalisés</x:t></x:si><x:si><x:t>Équité réalisée</x:t></x:si><x:si><x:t>Solde</x:t></x:si><x:si><x:t>Type d'actif</x:t></x:si><x:si><x:t>NWA (fonds non retirables)</x:t></x:si><x:si><x:t>01/02/2025 08:00:00</x:t></x:si><x:si><x:t>Dépôt</x:t></x:si><x:si><x:t>Virement</x:t></x:si><x:si><x:t>Position ouverte</x:t></x:si><x:si><x:t>Crypto-monnaies</x:t></x:si><x:si><x:t>15/07/2025 12:00:00</x:t></x:si><x:si><x:t>Frais overnight</x:t></x:si></x:sst>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?><x:sst count="92"><x:si><x:r><x:t xml:space="preserve">No</x:t></x:r><x:r><x:t xml:space="preserve">m</x:t></x:r></x:si><x:si><x:t>Totaux</x:t></x:si><x:si><x:t>Deposits</x:t></x:si><x:si><x:t>Récapitulatif du compte (USD)</x:t></x:si><x:si><x:t>Total&#10; en (USD)</x:t></x:si><x:si><x:t>Snapshot Date</x:t></x:si><x:si><x:t>Asset</x:t></x:si><x:si><x:t>Position ID</x:t></x:si><x:si><x:t>Direction</x:t></x:si><x:si><x:t>Open Date</x:t></x:si><x:si><x:t>Leverage</x:t></x:si><x:si><x:t>Open Rate</x:t></x:si><x:si><x:t>Units</x:t></x:si><x:si><x:t>Current Rate</x:t></x:si><x:si><x:t>Value in USD</x:t></x:si><x:si><x:t>Value in EUR</x:t></x:si><x:si><x:t>Type</x:t></x:si><x:si><x:t>ISIN</x:t></x:si><x:si><x:t>Demo Industries Inc.</x:t></x:si><x:si><x:t>p-101</x:t></x:si><x:si><x:t>Long</x:t></x:si><x:si><x:t>12/02/2025 09:30:00</x:t></x:si><x:si><x:t>X1</x:t></x:si><x:si><x:t>Stocks</x:t></x:si><x:si><x:t>XX0000000001</x:t></x:si><x:si><x:t>Indice Monde UCITS ETF</x:t></x:si><x:si><x:t>p-102</x:t></x:si><x:si><x:t>03/03/2025 11:00:00</x:t></x:si><x:si><x:t>ETF</x:t></x:si><x:si><x:t>XX0000000002</x:t></x:si><x:si><x:t>Bitcoin</x:t></x:si><x:si><x:t>p-103</x:t></x:si><x:si><x:t>20/05/2025 16:45:00</x:t></x:si><x:si><x:t>Crypto Currencies</x:t></x:si><x:si><x:t>-</x:t></x:si><x:si><x:t>Identifiant de position</x:t></x:si><x:si><x:t>Action</x:t></x:si><x:si><x:t>Long / Short</x:t></x:si><x:si><x:t>Montant</x:t></x:si><x:si><x:t>Unités</x:t></x:si><x:si><x:t>Date d'ouverture</x:t></x:si><x:si><x:t>Date de clôture</x:t></x:si><x:si><x:t>Effet de levier</x:t></x:si><x:si><x:t>Frais de spread (USD)</x:t></x:si><x:si><x:t>Spread du marché (USD)</x:t></x:si><x:si><x:t>Profit (USD)</x:t></x:si><x:si><x:t>Profit (EUR)</x:t></x:si><x:si><x:t>Taux de change à l'ouverture (USD)</x:t></x:si><x:si><x:t>Taux de change à la clôture (USD)</x:t></x:si><x:si><x:t>Taux à l'ouverture</x:t></x:si><x:si><x:t>Taux à la clôture</x:t></x:si><x:si><x:t>Taux Take Profit</x:t></x:si><x:si><x:t>Taux Stop Loss</x:t></x:si><x:si><x:t>Frais overnight et dividendes</x:t></x:si><x:si><x:t>Copie de</x:t></x:si><x:si><x:t>Remarques</x:t></x:si><x:si><x:t>p-201</x:t></x:si><x:si><x:t>Demo Industries Inc. (DEMO)</x:t></x:si><x:si><x:t>05/01/2025 10:00:00</x:t></x:si><x:si><x:t>10/04/2025 15:00:00</x:t></x:si><x:si><x:t>1</x:t></x:si><x:si><x:t>Actions</x:t></x:si><x:si><x:t>p-202</x:t></x:si><x:si><x:t>Pétrole (OIL)</x:t></x:si><x:si><x:t>06/01/2025 10:00:00</x:t></x:si><x:si><x:t>11/04/2025 15:00:00</x:t></x:si><x:si><x:t>2</x:t></x:si><x:si><x:t>CFD</x:t></x:si><x:si><x:t>XX0000000005</x:t></x:si><x:si><x:t>Date</x:t></x:si><x:si><x:t>Détails</x:t></x:si><x:si><x:t>Variation Fonds propres réalisés</x:t></x:si><x:si><x:t>Équité réalisée</x:t></x:si><x:si><x:t>Solde</x:t></x:si><x:si><x:t>Type d'actif</x:t></x:si><x:si><x:t>NWA (fonds non retirables)</x:t></x:si><x:si><x:t>01/02/2025 08:00:00</x:t></x:si><x:si><x:t>Dépôt</x:t></x:si><x:si><x:t>Virement</x:t></x:si><x:si><x:t>Position ouverte</x:t></x:si><x:si><x:t>DEMO/USD</x:t></x:si><x:si><x:t>IDX.DE/EUR</x:t></x:si><x:si><x:t>BTC/USD</x:t></x:si><x:si><x:t>Crypto-monnaies</x:t></x:si><x:si><x:t>02/06/2025 10:00:00</x:t></x:si><x:si><x:t>OIL/USD</x:t></x:si><x:si><x:t>p-104</x:t></x:si><x:si><x:t>15/07/2025 12:00:00</x:t></x:si><x:si><x:t>Frais overnight</x:t></x:si><x:si><x:t>14/04/2026 14:20:00</x:t></x:si><x:si><x:t>NEWCO/USD</x:t></x:si><x:si><x:t>p-301</x:t></x:si></x:sst>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?><x:worksheet><x:sheetData><x:row r="1"><x:c r="A1" t="s"><x:v>0</x:v></x:c><x:c r="B1" t="s"><x:v>1</x:v></x:c></x:row><x:row r="2"><x:c r="A2" t="s"><x:v>2</x:v></x:c><x:c r="B2"><x:v>5000</x:v></x:c></x:row><x:row r="3"><x:c r="A3" t="s"><x:v>3</x:v></x:c><x:c r="B3" t="s"><x:v>4</x:v></x:c></x:row></x:sheetData></x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?><x:worksheet><x:sheetData><x:row r="1"><x:c r="A1" t="s"><x:v>5</x:v></x:c><x:c r="B1" t="s"><x:v>6</x:v></x:c><x:c r="C1" t="s"><x:v>7</x:v></x:c><x:c r="D1" t="s"><x:v>8</x:v></x:c><x:c r="E1" t="s"><x:v>9</x:v></x:c><x:c r="F1" t="s"><x:v>10</x:v></x:c><x:c r="G1" t="s"><x:v>11</x:v></x:c><x:c r="H1" t="s"><x:v>12</x:v></x:c><x:c r="I1" t="s"><x:v>13</x:v></x:c><x:c r="J1" t="s"><x:v>14</x:v></x:c><x:c r="K1" t="s"><x:v>15</x:v></x:c><x:c r="L1" t="s"><x:v>16</x:v></x:c><x:c r="M1" t="s"><x:v>17</x:v></x:c></x:row><x:row r="2"><x:c r="A2"><x:v>45838</x:v></x:c><x:c r="B2" t="s"><x:v>18</x:v></x:c><x:c r="C2" t="s"><x:v>19</x:v></x:c><x:c r="D2" t="s"><x:v>20</x:v></x:c><x:c r="E2" t="s"><x:v>21</x:v></x:c><x:c r="F2" t="s"><x:v>22</x:v></x:c><x:c r="G2"><x:v>40</x:v></x:c><x:c r="H2"><x:v>10</x:v></x:c><x:c r="I2"><x:v>45</x:v></x:c><x:c r="J2"><x:v>450</x:v></x:c><x:c r="K2"><x:v>410</x:v></x:c><x:c r="L2" t="s"><x:v>23</x:v></x:c><x:c r="M2" t="s"><x:v>24</x:v></x:c></x:row><x:row r="3"><x:c r="A3"><x:v>45838</x:v></x:c><x:c r="B3" t="s"><x:v>25</x:v></x:c><x:c r="C3" t="s"><x:v>26</x:v></x:c><x:c r="D3" t="s"><x:v>20</x:v></x:c><x:c r="E3" t="s"><x:v>27</x:v></x:c><x:c r="F3" t="s"><x:v>22</x:v></x:c><x:c r="G3"><x:v>90</x:v></x:c><x:c r="H3"><x:v>5</x:v></x:c><x:c r="I3"><x:v>95</x:v></x:c><x:c r="J3"><x:v>475</x:v></x:c><x:c r="K3"><x:v>432</x:v></x:c><x:c r="L3" t="s"><x:v>28</x:v></x:c><x:c r="M3" t="s"><x:v>29</x:v></x:c></x:row><x:row r="4"><x:c r="A4"><x:v>46023</x:v></x:c><x:c r="B4" t="s"><x:v>18</x:v></x:c><x:c r="C4" t="s"><x:v>19</x:v></x:c><x:c r="D4" t="s"><x:v>20</x:v></x:c><x:c r="E4" t="s"><x:v>21</x:v></x:c><x:c r="F4" t="s"><x:v>22</x:v></x:c><x:c r="G4"><x:v>40</x:v></x:c><x:c r="H4"><x:v>10</x:v></x:c><x:c r="I4"><x:v>52</x:v></x:c><x:c r="J4"><x:v>520</x:v></x:c><x:c r="K4"><x:v>470</x:v></x:c><x:c r="L4" t="s"><x:v>23</x:v></x:c><x:c r="M4" t="s"><x:v>24</x:v></x:c></x:row><x:row r="5"><x:c r="A5"><x:v>46023</x:v></x:c><x:c r="B5" t="s"><x:v>25</x:v></x:c><x:c r="C5" t="s"><x:v>26</x:v></x:c><x:c r="D5" t="s"><x:v>20</x:v></x:c><x:c r="E5" t="s"><x:v>27</x:v></x:c><x:c r="F5" t="s"><x:v>22</x:v></x:c><x:c r="G5"><x:v>90</x:v></x:c><x:c r="H5"><x:v>5</x:v></x:c><x:c r="I5"><x:v>101</x:v></x:c><x:c r="J5"><x:v>505</x:v></x:c><x:c r="K5"><x:v>456</x:v></x:c><x:c r="L5" t="s"><x:v>28</x:v></x:c><x:c r="M5" t="s"><x:v>29</x:v></x:c></x:row><x:row r="6"><x:c r="A6"><x:v>46023</x:v></x:c><x:c r="B6" t="s"><x:v>30</x:v></x:c><x:c r="C6" t="s"><x:v>31</x:v></x:c><x:c r="D6" t="s"><x:v>20</x:v></x:c><x:c r="E6" t="s"><x:v>32</x:v></x:c><x:c r="F6" t="s"><x:v>22</x:v></x:c><x:c r="G6"><x:v>300</x:v></x:c><x:c r="H6"><x:v>2</x:v></x:c><x:c r="I6"><x:v>350</x:v></x:c><x:c r="J6"><x:v>700</x:v></x:c><x:c r="K6"><x:v>633</x:v></x:c><x:c r="L6" t="s"><x:v>33</x:v></x:c><x:c r="M6" t="s"><x:v>34</x:v></x:c></x:row><x:row r="7"><x:c r="A7"><x:v>46023</x:v></x:c><x:c r="B7" t="s"><x:v>35</x:v></x:c><x:c r="C7" t="s"><x:v>36</x:v></x:c><x:c r="D7" t="s"><x:v>20</x:v></x:c><x:c r="E7" t="s"><x:v>37</x:v></x:c><x:c r="F7" t="s"><x:v>38</x:v></x:c><x:c r="G7"><x:v>20</x:v></x:c><x:c r="H7"><x:v>3</x:v></x:c><x:c r="I7"><x:v>22</x:v></x:c><x:c r="J7"><x:v>66</x:v></x:c><x:c r="K7"><x:v>60</x:v></x:c><x:c r="L7" t="s"><x:v>23</x:v></x:c><x:c r="M7" t="s"><x:v>39</x:v></x:c></x:row></x:sheetData></x:worksheet>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?><x:worksheet><x:sheetData><x:row r="1"><x:c r="A1" t="s"><x:v>5</x:v></x:c><x:c r="B1" t="s"><x:v>6</x:v></x:c><x:c r="C1" t="s"><x:v>7</x:v></x:c><x:c r="D1" t="s"><x:v>8</x:v></x:c><x:c r="E1" t="s"><x:v>9</x:v></x:c><x:c r="F1" t="s"><x:v>10</x:v></x:c><x:c r="G1" t="s"><x:v>11</x:v></x:c><x:c r="H1" t="s"><x:v>12</x:v></x:c><x:c r="I1" t="s"><x:v>13</x:v></x:c><x:c r="J1" t="s"><x:v>14</x:v></x:c><x:c r="K1" t="s"><x:v>15</x:v></x:c><x:c r="L1" t="s"><x:v>16</x:v></x:c><x:c r="M1" t="s"><x:v>17</x:v></x:c></x:row><x:row r="2"><x:c r="A2"><x:v>45838</x:v></x:c><x:c r="B2" t="s"><x:v>18</x:v></x:c><x:c r="C2" t="s"><x:v>19</x:v></x:c><x:c r="D2" t="s"><x:v>20</x:v></x:c><x:c r="E2" t="s"><x:v>21</x:v></x:c><x:c r="F2" t="s"><x:v>22</x:v></x:c><x:c r="G2"><x:v>40</x:v></x:c><x:c r="H2"><x:v>10</x:v></x:c><x:c r="I2"><x:v>45</x:v></x:c><x:c r="J2"><x:v>450</x:v></x:c><x:c r="K2"><x:v>410</x:v></x:c><x:c r="L2" t="s"><x:v>23</x:v></x:c><x:c r="M2" t="s"><x:v>24</x:v></x:c></x:row><x:row r="3"><x:c r="A3"><x:v>45838</x:v></x:c><x:c r="B3" t="s"><x:v>25</x:v></x:c><x:c r="C3" t="s"><x:v>26</x:v></x:c><x:c r="D3" t="s"><x:v>20</x:v></x:c><x:c r="E3" t="s"><x:v>27</x:v></x:c><x:c r="F3" t="s"><x:v>22</x:v></x:c><x:c r="G3"><x:v>90</x:v></x:c><x:c r="H3"><x:v>5</x:v></x:c><x:c r="I3"><x:v>95</x:v></x:c><x:c r="J3"><x:v>475</x:v></x:c><x:c r="K3"><x:v>432</x:v></x:c><x:c r="L3" t="s"><x:v>28</x:v></x:c><x:c r="M3" t="s"><x:v>29</x:v></x:c></x:row><x:row r="4"><x:c r="A4"><x:v>46023</x:v></x:c><x:c r="B4" t="s"><x:v>18</x:v></x:c><x:c r="C4" t="s"><x:v>19</x:v></x:c><x:c r="D4" t="s"><x:v>20</x:v></x:c><x:c r="E4" t="s"><x:v>21</x:v></x:c><x:c r="F4" t="s"><x:v>22</x:v></x:c><x:c r="G4"><x:v>40</x:v></x:c><x:c r="H4"><x:v>10</x:v></x:c><x:c r="I4"><x:v>52</x:v></x:c><x:c r="J4"><x:v>520</x:v></x:c><x:c r="K4"><x:v>470</x:v></x:c><x:c r="L4" t="s"><x:v>23</x:v></x:c><x:c r="M4" t="s"><x:v>24</x:v></x:c></x:row><x:row r="5"><x:c r="A5"><x:v>46023</x:v></x:c><x:c r="B5" t="s"><x:v>25</x:v></x:c><x:c r="C5" t="s"><x:v>26</x:v></x:c><x:c r="D5" t="s"><x:v>20</x:v></x:c><x:c r="E5" t="s"><x:v>27</x:v></x:c><x:c r="F5" t="s"><x:v>22</x:v></x:c><x:c r="G5"><x:v>90</x:v></x:c><x:c r="H5"><x:v>5</x:v></x:c><x:c r="I5"><x:v>101</x:v></x:c><x:c r="J5"><x:v>505</x:v></x:c><x:c r="K5"><x:v>456</x:v></x:c><x:c r="L5" t="s"><x:v>28</x:v></x:c><x:c r="M5" t="s"><x:v>29</x:v></x:c></x:row><x:row r="6"><x:c r="A6"><x:v>46023</x:v></x:c><x:c r="B6" t="s"><x:v>30</x:v></x:c><x:c r="C6" t="s"><x:v>31</x:v></x:c><x:c r="D6" t="s"><x:v>20</x:v></x:c><x:c r="E6" t="s"><x:v>32</x:v></x:c><x:c r="F6" t="s"><x:v>22</x:v></x:c><x:c r="G6"><x:v>300</x:v></x:c><x:c r="H6"><x:v>2</x:v></x:c><x:c r="I6"><x:v>350</x:v></x:c><x:c r="J6"><x:v>700</x:v></x:c><x:c r="K6"><x:v>633</x:v></x:c><x:c r="L6" t="s"><x:v>33</x:v></x:c><x:c r="M6" t="s"><x:v>34</x:v></x:c></x:row></x:sheetData></x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?><x:worksheet><x:sheetData><x:row r="1"><x:c r="A1" t="s"><x:v>40</x:v></x:c><x:c r="B1" t="s"><x:v>41</x:v></x:c><x:c r="C1" t="s"><x:v>42</x:v></x:c><x:c r="D1" t="s"><x:v>43</x:v></x:c><x:c r="E1" t="s"><x:v>44</x:v></x:c><x:c r="F1" t="s"><x:v>45</x:v></x:c><x:c r="G1" t="s"><x:v>46</x:v></x:c><x:c r="H1" t="s"><x:v>47</x:v></x:c><x:c r="I1" t="s"><x:v>48</x:v></x:c><x:c r="J1" t="s"><x:v>49</x:v></x:c><x:c r="K1" t="s"><x:v>50</x:v></x:c><x:c r="L1" t="s"><x:v>51</x:v></x:c><x:c r="M1" t="s"><x:v>52</x:v></x:c><x:c r="N1" t="s"><x:v>53</x:v></x:c><x:c r="O1" t="s"><x:v>54</x:v></x:c><x:c r="P1" t="s"><x:v>55</x:v></x:c><x:c r="Q1" t="s"><x:v>56</x:v></x:c><x:c r="R1" t="s"><x:v>57</x:v></x:c><x:c r="S1" t="s"><x:v>58</x:v></x:c><x:c r="T1" t="s"><x:v>59</x:v></x:c><x:c r="U1" t="s"><x:v>16</x:v></x:c><x:c r="V1" t="s"><x:v>17</x:v></x:c><x:c r="W1" t="s"><x:v>60</x:v></x:c></x:row><x:row r="2"><x:c r="A2" t="s"><x:v>61</x:v></x:c><x:c r="B2" t="s"><x:v>18</x:v></x:c><x:c r="C2" t="s"><x:v>20</x:v></x:c><x:c r="D2"><x:v>200</x:v></x:c><x:c r="E2"><x:v>5</x:v></x:c><x:c r="F2" t="s"><x:v>62</x:v></x:c><x:c r="G2" t="s"><x:v>63</x:v></x:c><x:c r="H2" t="s"><x:v>64</x:v></x:c><x:c r="I2"><x:v>0</x:v></x:c><x:c r="J2"><x:v>0</x:v></x:c><x:c r="K2"><x:v>40</x:v></x:c><x:c r="L2"><x:v>36</x:v></x:c><x:c r="M2"><x:v>1</x:v></x:c><x:c r="N2"><x:v>1</x:v></x:c><x:c r="O2"><x:v>40</x:v></x:c><x:c r="P2"><x:v>48</x:v></x:c><x:c r="Q2"><x:v>0</x:v></x:c><x:c r="R2"><x:v>0</x:v></x:c><x:c r="S2"><x:v>0</x:v></x:c><x:c r="U2" t="s"><x:v>65</x:v></x:c><x:c r="V2" t="s"><x:v>24</x:v></x:c></x:row><x:row r="3"><x:c r="A3" t="s"><x:v>66</x:v></x:c><x:c r="B3" t="s"><x:v>67</x:v></x:c><x:c r="C3" t="s"><x:v>20</x:v></x:c><x:c r="D3"><x:v>100</x:v></x:c><x:c r="E3"><x:v>1</x:v></x:c><x:c r="F3" t="s"><x:v>68</x:v></x:c><x:c r="G3" t="s"><x:v>69</x:v></x:c><x:c r="H3" t="s"><x:v>70</x:v></x:c><x:c r="I3"><x:v>0</x:v></x:c><x:c r="J3"><x:v>0</x:v></x:c><x:c r="K3"><x:v>5</x:v></x:c><x:c r="L3"><x:v>4</x:v></x:c><x:c r="M3"><x:v>1</x:v></x:c><x:c r="N3"><x:v>1</x:v></x:c><x:c r="O3"><x:v>100</x:v></x:c><x:c r="P3"><x:v>105</x:v></x:c><x:c r="Q3"><x:v>0</x:v></x:c><x:c r="R3"><x:v>0</x:v></x:c><x:c r="S3"><x:v>0</x:v></x:c><x:c r="U3" t="s"><x:v>71</x:v></x:c><x:c r="V3" t="s"><x:v>72</x:v></x:c></x:row></x:sheetData></x:worksheet>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?><x:worksheet><x:sheetData><x:row r="1"><x:c r="A1" t="s"><x:v>35</x:v></x:c><x:c r="B1" t="s"><x:v>36</x:v></x:c><x:c r="C1" t="s"><x:v>37</x:v></x:c><x:c r="D1" t="s"><x:v>38</x:v></x:c><x:c r="E1" t="s"><x:v>39</x:v></x:c><x:c r="F1" t="s"><x:v>40</x:v></x:c><x:c r="G1" t="s"><x:v>41</x:v></x:c><x:c r="H1" t="s"><x:v>42</x:v></x:c><x:c r="I1" t="s"><x:v>43</x:v></x:c><x:c r="J1" t="s"><x:v>44</x:v></x:c><x:c r="K1" t="s"><x:v>45</x:v></x:c><x:c r="L1" t="s"><x:v>46</x:v></x:c><x:c r="M1" t="s"><x:v>47</x:v></x:c><x:c r="N1" t="s"><x:v>48</x:v></x:c><x:c r="O1" t="s"><x:v>49</x:v></x:c><x:c r="P1" t="s"><x:v>50</x:v></x:c><x:c r="Q1" t="s"><x:v>51</x:v></x:c><x:c r="R1" t="s"><x:v>52</x:v></x:c><x:c r="S1" t="s"><x:v>53</x:v></x:c><x:c r="T1" t="s"><x:v>54</x:v></x:c><x:c r="U1" t="s"><x:v>16</x:v></x:c><x:c r="V1" t="s"><x:v>17</x:v></x:c><x:c r="W1" t="s"><x:v>55</x:v></x:c></x:row><x:row r="2"><x:c r="A2" t="s"><x:v>56</x:v></x:c><x:c r="B2" t="s"><x:v>57</x:v></x:c><x:c r="C2" t="s"><x:v>20</x:v></x:c><x:c r="D2"><x:v>200</x:v></x:c><x:c r="E2"><x:v>5</x:v></x:c><x:c r="F2" t="s"><x:v>58</x:v></x:c><x:c r="G2" t="s"><x:v>59</x:v></x:c><x:c r="H2" t="s"><x:v>60</x:v></x:c><x:c r="I2"><x:v>0</x:v></x:c><x:c r="J2"><x:v>0</x:v></x:c><x:c r="K2"><x:v>40</x:v></x:c><x:c r="L2"><x:v>36</x:v></x:c><x:c r="M2"><x:v>1</x:v></x:c><x:c r="N2"><x:v>1</x:v></x:c><x:c r="O2"><x:v>40</x:v></x:c><x:c r="P2"><x:v>48</x:v></x:c><x:c r="Q2"><x:v>0</x:v></x:c><x:c r="R2"><x:v>0</x:v></x:c><x:c r="S2"><x:v>0</x:v></x:c><x:c r="U2" t="s"><x:v>61</x:v></x:c><x:c r="V2" t="s"><x:v>24</x:v></x:c></x:row><x:row r="3"><x:c r="A3" t="s"><x:v>62</x:v></x:c><x:c r="B3" t="s"><x:v>63</x:v></x:c><x:c r="C3" t="s"><x:v>20</x:v></x:c><x:c r="D3"><x:v>100</x:v></x:c><x:c r="E3"><x:v>1</x:v></x:c><x:c r="F3" t="s"><x:v>64</x:v></x:c><x:c r="G3" t="s"><x:v>65</x:v></x:c><x:c r="H3" t="s"><x:v>66</x:v></x:c><x:c r="I3"><x:v>0</x:v></x:c><x:c r="J3"><x:v>0</x:v></x:c><x:c r="K3"><x:v>5</x:v></x:c><x:c r="L3"><x:v>4</x:v></x:c><x:c r="M3"><x:v>1</x:v></x:c><x:c r="N3"><x:v>1</x:v></x:c><x:c r="O3"><x:v>100</x:v></x:c><x:c r="P3"><x:v>105</x:v></x:c><x:c r="Q3"><x:v>0</x:v></x:c><x:c r="R3"><x:v>0</x:v></x:c><x:c r="S3"><x:v>0</x:v></x:c><x:c r="U3" t="s"><x:v>67</x:v></x:c><x:c r="V3" t="s"><x:v>68</x:v></x:c></x:row></x:sheetData></x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?><x:worksheet><x:sheetData><x:row r="1"><x:c r="A1" t="s"><x:v>73</x:v></x:c><x:c r="B1" t="s"><x:v>16</x:v></x:c><x:c r="C1" t="s"><x:v>74</x:v></x:c><x:c r="D1" t="s"><x:v>43</x:v></x:c><x:c r="E1" t="s"><x:v>44</x:v></x:c><x:c r="F1" t="s"><x:v>75</x:v></x:c><x:c r="G1" t="s"><x:v>76</x:v></x:c><x:c r="H1" t="s"><x:v>77</x:v></x:c><x:c r="I1" t="s"><x:v>40</x:v></x:c><x:c r="J1" t="s"><x:v>78</x:v></x:c><x:c r="K1" t="s"><x:v>79</x:v></x:c></x:row><x:row r="2"><x:c r="A2" t="s"><x:v>80</x:v></x:c><x:c r="B2" t="s"><x:v>81</x:v></x:c><x:c r="C2" t="s"><x:v>82</x:v></x:c><x:c r="D2"><x:v>5000</x:v></x:c><x:c r="E2" t="s"><x:v>34</x:v></x:c><x:c r="F2"><x:v>0</x:v></x:c><x:c r="G2"><x:v>0</x:v></x:c><x:c r="H2"><x:v>5000</x:v></x:c><x:c r="J2" t="s"><x:v>34</x:v></x:c><x:c r="K2"><x:v>0</x:v></x:c></x:row><x:row r="3"><x:c r="A3" t="s"><x:v>21</x:v></x:c><x:c r="B3" t="s"><x:v>83</x:v></x:c><x:c r="C3" t="s"><x:v>18</x:v></x:c><x:c r="D3"><x:v>400</x:v></x:c><x:c r="E3"><x:v>10</x:v></x:c><x:c r="F3"><x:v>0</x:v></x:c><x:c r="G3"><x:v>0</x:v></x:c><x:c r="H3"><x:v>4600</x:v></x:c><x:c r="I3" t="s"><x:v>19</x:v></x:c><x:c r="J3" t="s"><x:v>65</x:v></x:c><x:c r="K3"><x:v>0</x:v></x:c></x:row><x:row r="4"><x:c r="A4" t="s"><x:v>27</x:v></x:c><x:c r="B4" t="s"><x:v>83</x:v></x:c><x:c r="C4" t="s"><x:v>25</x:v></x:c><x:c r="D4"><x:v>450</x:v></x:c><x:c r="E4"><x:v>5</x:v></x:c><x:c r="F4"><x:v>0</x:v></x:c><x:c r="G4"><x:v>0</x:v></x:c><x:c r="H4"><x:v>4150</x:v></x:c><x:c r="I4" t="s"><x:v>26</x:v></x:c><x:c r="J4" t="s"><x:v>28</x:v></x:c><x:c r="K4"><x:v>0</x:v></x:c></x:row><x:row r="5"><x:c r="A5" t="s"><x:v>32</x:v></x:c><x:c r="B5" t="s"><x:v>83</x:v></x:c><x:c r="C5" t="s"><x:v>30</x:v></x:c><x:c r="D5"><x:v>600</x:v></x:c><x:c r="E5"><x:v>2</x:v></x:c><x:c r="F5"><x:v>0</x:v></x:c><x:c r="G5"><x:v>0</x:v></x:c><x:c r="H5"><x:v>3550</x:v></x:c><x:c r="I5" t="s"><x:v>31</x:v></x:c><x:c r="J5" t="s"><x:v>84</x:v></x:c><x:c r="K5"><x:v>0</x:v></x:c></x:row><x:row r="6"><x:c r="A6" t="s"><x:v>37</x:v></x:c><x:c r="B6" t="s"><x:v>83</x:v></x:c><x:c r="C6" t="s"><x:v>35</x:v></x:c><x:c r="D6"><x:v>60</x:v></x:c><x:c r="E6"><x:v>3</x:v></x:c><x:c r="F6"><x:v>0</x:v></x:c><x:c r="G6"><x:v>0</x:v></x:c><x:c r="H6"><x:v>3490</x:v></x:c><x:c r="I6" t="s"><x:v>36</x:v></x:c><x:c r="J6" t="s"><x:v>65</x:v></x:c><x:c r="K6"><x:v>0</x:v></x:c></x:row><x:row r="7"><x:c r="A7" t="s"><x:v>85</x:v></x:c><x:c r="B7" t="s"><x:v>86</x:v></x:c><x:c r="C7" t="s"><x:v>35</x:v></x:c><x:c r="D7"><x:v>-2</x:v></x:c><x:c r="E7" t="s"><x:v>34</x:v></x:c><x:c r="F7"><x:v>0</x:v></x:c><x:c r="G7"><x:v>0</x:v></x:c><x:c r="H7"><x:v>3488</x:v></x:c><x:c r="I7" t="s"><x:v>36</x:v></x:c><x:c r="J7" t="s"><x:v>65</x:v></x:c><x:c r="K7"><x:v>0</x:v></x:c></x:row></x:sheetData></x:worksheet>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?><x:worksheet><x:sheetData><x:row r="1"><x:c r="A1" t="s"><x:v>69</x:v></x:c><x:c r="B1" t="s"><x:v>16</x:v></x:c><x:c r="C1" t="s"><x:v>70</x:v></x:c><x:c r="D1" t="s"><x:v>38</x:v></x:c><x:c r="E1" t="s"><x:v>39</x:v></x:c><x:c r="F1" t="s"><x:v>71</x:v></x:c><x:c r="G1" t="s"><x:v>72</x:v></x:c><x:c r="H1" t="s"><x:v>73</x:v></x:c><x:c r="I1" t="s"><x:v>35</x:v></x:c><x:c r="J1" t="s"><x:v>74</x:v></x:c><x:c r="K1" t="s"><x:v>75</x:v></x:c></x:row><x:row r="2"><x:c r="A2" t="s"><x:v>76</x:v></x:c><x:c r="B2" t="s"><x:v>77</x:v></x:c><x:c r="C2" t="s"><x:v>78</x:v></x:c><x:c r="D2"><x:v>5000</x:v></x:c><x:c r="E2" t="s"><x:v>34</x:v></x:c><x:c r="F2"><x:v>0</x:v></x:c><x:c r="G2"><x:v>0</x:v></x:c><x:c r="H2"><x:v>5000</x:v></x:c><x:c r="J2" t="s"><x:v>34</x:v></x:c><x:c r="K2"><x:v>0</x:v></x:c></x:row><x:row r="3"><x:c r="A3" t="s"><x:v>58</x:v></x:c><x:c r="B3" t="s"><x:v>79</x:v></x:c><x:c r="C3" t="s"><x:v>80</x:v></x:c><x:c r="D3"><x:v>200</x:v></x:c><x:c r="E3"><x:v>5</x:v></x:c><x:c r="F3"><x:v>0</x:v></x:c><x:c r="G3"><x:v>0</x:v></x:c><x:c r="H3"><x:v>4800</x:v></x:c><x:c r="I3" t="s"><x:v>56</x:v></x:c><x:c r="J3" t="s"><x:v>61</x:v></x:c><x:c r="K3"><x:v>0</x:v></x:c></x:row><x:row r="4"><x:c r="A4" t="s"><x:v>21</x:v></x:c><x:c r="B4" t="s"><x:v>79</x:v></x:c><x:c r="C4" t="s"><x:v>80</x:v></x:c><x:c r="D4"><x:v>400</x:v></x:c><x:c r="E4"><x:v>10</x:v></x:c><x:c r="F4"><x:v>0</x:v></x:c><x:c r="G4"><x:v>0</x:v></x:c><x:c r="H4"><x:v>4600</x:v></x:c><x:c r="I4" t="s"><x:v>19</x:v></x:c><x:c r="J4" t="s"><x:v>61</x:v></x:c><x:c r="K4"><x:v>0</x:v></x:c></x:row><x:row r="5"><x:c r="A5" t="s"><x:v>27</x:v></x:c><x:c r="B5" t="s"><x:v>79</x:v></x:c><x:c r="C5" t="s"><x:v>81</x:v></x:c><x:c r="D5"><x:v>450</x:v></x:c><x:c r="E5"><x:v>5</x:v></x:c><x:c r="F5"><x:v>0</x:v></x:c><x:c r="G5"><x:v>0</x:v></x:c><x:c r="H5"><x:v>4150</x:v></x:c><x:c r="I5" t="s"><x:v>26</x:v></x:c><x:c r="J5" t="s"><x:v>28</x:v></x:c><x:c r="K5"><x:v>0</x:v></x:c></x:row><x:row r="6"><x:c r="A6" t="s"><x:v>32</x:v></x:c><x:c r="B6" t="s"><x:v>79</x:v></x:c><x:c r="C6" t="s"><x:v>82</x:v></x:c><x:c r="D6"><x:v>600</x:v></x:c><x:c r="E6"><x:v>2</x:v></x:c><x:c r="F6"><x:v>0</x:v></x:c><x:c r="G6"><x:v>0</x:v></x:c><x:c r="H6"><x:v>3550</x:v></x:c><x:c r="I6" t="s"><x:v>31</x:v></x:c><x:c r="J6" t="s"><x:v>83</x:v></x:c><x:c r="K6"><x:v>0</x:v></x:c></x:row><x:row r="7"><x:c r="A7" t="s"><x:v>84</x:v></x:c><x:c r="B7" t="s"><x:v>79</x:v></x:c><x:c r="C7" t="s"><x:v>85</x:v></x:c><x:c r="D7"><x:v>60</x:v></x:c><x:c r="E7"><x:v>3</x:v></x:c><x:c r="F7"><x:v>0</x:v></x:c><x:c r="G7"><x:v>0</x:v></x:c><x:c r="H7"><x:v>3490</x:v></x:c><x:c r="I7" t="s"><x:v>86</x:v></x:c><x:c r="J7" t="s"><x:v>67</x:v></x:c><x:c r="K7"><x:v>0</x:v></x:c></x:row><x:row r="8"><x:c r="A8" t="s"><x:v>87</x:v></x:c><x:c r="B8" t="s"><x:v>88</x:v></x:c><x:c r="C8" t="s"><x:v>85</x:v></x:c><x:c r="D8"><x:v>-2</x:v></x:c><x:c r="E8" t="s"><x:v>34</x:v></x:c><x:c r="F8"><x:v>0</x:v></x:c><x:c r="G8"><x:v>0</x:v></x:c><x:c r="H8"><x:v>3488</x:v></x:c><x:c r="I8" t="s"><x:v>86</x:v></x:c><x:c r="J8" t="s"><x:v>67</x:v></x:c><x:c r="K8"><x:v>0</x:v></x:c></x:row><x:row r="9"><x:c r="A9" t="s"><x:v>89</x:v></x:c><x:c r="B9" t="s"><x:v>79</x:v></x:c><x:c r="C9" t="s"><x:v>90</x:v></x:c><x:c r="D9"><x:v>300</x:v></x:c><x:c r="E9"><x:v>4</x:v></x:c><x:c r="F9"><x:v>0</x:v></x:c><x:c r="G9"><x:v>0</x:v></x:c><x:c r="H9"><x:v>3190</x:v></x:c><x:c r="I9" t="s"><x:v>91</x:v></x:c><x:c r="J9" t="s"><x:v>61</x:v></x:c><x:c r="K9"><x:v>0</x:v></x:c></x:row></x:sheetData></x:worksheet>
 </file>
--- a/tests/fixtures/etoro/releve-demo.xlsx
+++ b/tests/fixtures/etoro/releve-demo.xlsx
@@ -10,7 +10,7 @@
 </x:workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?><x:sst count="92"><x:si><x:r><x:t xml:space="preserve">No</x:t></x:r><x:r><x:t xml:space="preserve">m</x:t></x:r></x:si><x:si><x:t>Totaux</x:t></x:si><x:si><x:t>Deposits</x:t></x:si><x:si><x:t>Récapitulatif du compte (USD)</x:t></x:si><x:si><x:t>Total&#10; en (USD)</x:t></x:si><x:si><x:t>Snapshot Date</x:t></x:si><x:si><x:t>Asset</x:t></x:si><x:si><x:t>Position ID</x:t></x:si><x:si><x:t>Direction</x:t></x:si><x:si><x:t>Open Date</x:t></x:si><x:si><x:t>Leverage</x:t></x:si><x:si><x:t>Open Rate</x:t></x:si><x:si><x:t>Units</x:t></x:si><x:si><x:t>Current Rate</x:t></x:si><x:si><x:t>Value in USD</x:t></x:si><x:si><x:t>Value in EUR</x:t></x:si><x:si><x:t>Type</x:t></x:si><x:si><x:t>ISIN</x:t></x:si><x:si><x:t>Demo Industries Inc.</x:t></x:si><x:si><x:t>p-101</x:t></x:si><x:si><x:t>Long</x:t></x:si><x:si><x:t>12/02/2025 09:30:00</x:t></x:si><x:si><x:t>X1</x:t></x:si><x:si><x:t>Stocks</x:t></x:si><x:si><x:t>XX0000000001</x:t></x:si><x:si><x:t>Indice Monde UCITS ETF</x:t></x:si><x:si><x:t>p-102</x:t></x:si><x:si><x:t>03/03/2025 11:00:00</x:t></x:si><x:si><x:t>ETF</x:t></x:si><x:si><x:t>XX0000000002</x:t></x:si><x:si><x:t>Bitcoin</x:t></x:si><x:si><x:t>p-103</x:t></x:si><x:si><x:t>20/05/2025 16:45:00</x:t></x:si><x:si><x:t>Crypto Currencies</x:t></x:si><x:si><x:t>-</x:t></x:si><x:si><x:t>Identifiant de position</x:t></x:si><x:si><x:t>Action</x:t></x:si><x:si><x:t>Long / Short</x:t></x:si><x:si><x:t>Montant</x:t></x:si><x:si><x:t>Unités</x:t></x:si><x:si><x:t>Date d'ouverture</x:t></x:si><x:si><x:t>Date de clôture</x:t></x:si><x:si><x:t>Effet de levier</x:t></x:si><x:si><x:t>Frais de spread (USD)</x:t></x:si><x:si><x:t>Spread du marché (USD)</x:t></x:si><x:si><x:t>Profit (USD)</x:t></x:si><x:si><x:t>Profit (EUR)</x:t></x:si><x:si><x:t>Taux de change à l'ouverture (USD)</x:t></x:si><x:si><x:t>Taux de change à la clôture (USD)</x:t></x:si><x:si><x:t>Taux à l'ouverture</x:t></x:si><x:si><x:t>Taux à la clôture</x:t></x:si><x:si><x:t>Taux Take Profit</x:t></x:si><x:si><x:t>Taux Stop Loss</x:t></x:si><x:si><x:t>Frais overnight et dividendes</x:t></x:si><x:si><x:t>Copie de</x:t></x:si><x:si><x:t>Remarques</x:t></x:si><x:si><x:t>p-201</x:t></x:si><x:si><x:t>Demo Industries Inc. (DEMO)</x:t></x:si><x:si><x:t>05/01/2025 10:00:00</x:t></x:si><x:si><x:t>10/04/2025 15:00:00</x:t></x:si><x:si><x:t>1</x:t></x:si><x:si><x:t>Actions</x:t></x:si><x:si><x:t>p-202</x:t></x:si><x:si><x:t>Pétrole (OIL)</x:t></x:si><x:si><x:t>06/01/2025 10:00:00</x:t></x:si><x:si><x:t>11/04/2025 15:00:00</x:t></x:si><x:si><x:t>2</x:t></x:si><x:si><x:t>CFD</x:t></x:si><x:si><x:t>XX0000000005</x:t></x:si><x:si><x:t>Date</x:t></x:si><x:si><x:t>Détails</x:t></x:si><x:si><x:t>Variation Fonds propres réalisés</x:t></x:si><x:si><x:t>Équité réalisée</x:t></x:si><x:si><x:t>Solde</x:t></x:si><x:si><x:t>Type d'actif</x:t></x:si><x:si><x:t>NWA (fonds non retirables)</x:t></x:si><x:si><x:t>01/02/2025 08:00:00</x:t></x:si><x:si><x:t>Dépôt</x:t></x:si><x:si><x:t>Virement</x:t></x:si><x:si><x:t>Position ouverte</x:t></x:si><x:si><x:t>DEMO/USD</x:t></x:si><x:si><x:t>IDX.DE/EUR</x:t></x:si><x:si><x:t>BTC/USD</x:t></x:si><x:si><x:t>Crypto-monnaies</x:t></x:si><x:si><x:t>02/06/2025 10:00:00</x:t></x:si><x:si><x:t>OIL/USD</x:t></x:si><x:si><x:t>p-104</x:t></x:si><x:si><x:t>15/07/2025 12:00:00</x:t></x:si><x:si><x:t>Frais overnight</x:t></x:si><x:si><x:t>14/04/2026 14:20:00</x:t></x:si><x:si><x:t>NEWCO/USD</x:t></x:si><x:si><x:t>p-301</x:t></x:si></x:sst>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?><x:sst count="95"><x:si><x:r><x:t xml:space="preserve">No</x:t></x:r><x:r><x:t xml:space="preserve">m</x:t></x:r></x:si><x:si><x:t>Totaux</x:t></x:si><x:si><x:t>Deposits</x:t></x:si><x:si><x:t>Récapitulatif du compte (USD)</x:t></x:si><x:si><x:t>Total&#10; en (USD)</x:t></x:si><x:si><x:t>Snapshot Date</x:t></x:si><x:si><x:t>Asset</x:t></x:si><x:si><x:t>Position ID</x:t></x:si><x:si><x:t>Direction</x:t></x:si><x:si><x:t>Open Date</x:t></x:si><x:si><x:t>Leverage</x:t></x:si><x:si><x:t>Open Rate</x:t></x:si><x:si><x:t>Units</x:t></x:si><x:si><x:t>Current Rate</x:t></x:si><x:si><x:t>Value in USD</x:t></x:si><x:si><x:t>Value in EUR</x:t></x:si><x:si><x:t>Type</x:t></x:si><x:si><x:t>ISIN</x:t></x:si><x:si><x:t>Demo Industries Inc.</x:t></x:si><x:si><x:t>p-101</x:t></x:si><x:si><x:t>Long</x:t></x:si><x:si><x:t>12/02/2025 09:30:00</x:t></x:si><x:si><x:t>X1</x:t></x:si><x:si><x:t>Stocks</x:t></x:si><x:si><x:t>XX0000000001</x:t></x:si><x:si><x:t>Indice Monde UCITS ETF</x:t></x:si><x:si><x:t>p-102</x:t></x:si><x:si><x:t>03/03/2025 11:00:00</x:t></x:si><x:si><x:t>ETF</x:t></x:si><x:si><x:t>XX0000000002</x:t></x:si><x:si><x:t>Bitcoin</x:t></x:si><x:si><x:t>p-103</x:t></x:si><x:si><x:t>20/05/2025 16:45:00</x:t></x:si><x:si><x:t>Crypto Currencies</x:t></x:si><x:si><x:t>-</x:t></x:si><x:si><x:t>Identifiant de position</x:t></x:si><x:si><x:t>Action</x:t></x:si><x:si><x:t>Long / Short</x:t></x:si><x:si><x:t>Montant</x:t></x:si><x:si><x:t>Unités</x:t></x:si><x:si><x:t>Date d'ouverture</x:t></x:si><x:si><x:t>Date de clôture</x:t></x:si><x:si><x:t>Effet de levier</x:t></x:si><x:si><x:t>Frais de spread (USD)</x:t></x:si><x:si><x:t>Spread du marché (USD)</x:t></x:si><x:si><x:t>Profit (USD)</x:t></x:si><x:si><x:t>Profit (EUR)</x:t></x:si><x:si><x:t>Taux de change à l'ouverture (USD)</x:t></x:si><x:si><x:t>Taux de change à la clôture (USD)</x:t></x:si><x:si><x:t>Taux à l'ouverture</x:t></x:si><x:si><x:t>Taux à la clôture</x:t></x:si><x:si><x:t>Taux Take Profit</x:t></x:si><x:si><x:t>Taux Stop Loss</x:t></x:si><x:si><x:t>Frais overnight et dividendes</x:t></x:si><x:si><x:t>Copie de</x:t></x:si><x:si><x:t>Remarques</x:t></x:si><x:si><x:t>p-201</x:t></x:si><x:si><x:t>Demo Industries Inc. (DEMO)</x:t></x:si><x:si><x:t>05/01/2025 10:00:00</x:t></x:si><x:si><x:t>10/04/2025 15:00:00</x:t></x:si><x:si><x:t>1</x:t></x:si><x:si><x:t>Actions</x:t></x:si><x:si><x:t>p-202</x:t></x:si><x:si><x:t>Pétrole (OIL)</x:t></x:si><x:si><x:t>06/01/2025 10:00:00</x:t></x:si><x:si><x:t>11/04/2025 15:00:00</x:t></x:si><x:si><x:t>2</x:t></x:si><x:si><x:t>CFD</x:t></x:si><x:si><x:t>XX0000000005</x:t></x:si><x:si><x:t>Date</x:t></x:si><x:si><x:t>Détails</x:t></x:si><x:si><x:t>Variation Fonds propres réalisés</x:t></x:si><x:si><x:t>Équité réalisée</x:t></x:si><x:si><x:t>Solde</x:t></x:si><x:si><x:t>Type d'actif</x:t></x:si><x:si><x:t>NWA (fonds non retirables)</x:t></x:si><x:si><x:t>01/02/2025 08:00:00</x:t></x:si><x:si><x:t>Dépôt</x:t></x:si><x:si><x:t>Virement</x:t></x:si><x:si><x:t>Position ouverte</x:t></x:si><x:si><x:t>DEMO/USD</x:t></x:si><x:si><x:t>IDX.DE/EUR</x:t></x:si><x:si><x:t>BTC/USD</x:t></x:si><x:si><x:t>Crypto-monnaies</x:t></x:si><x:si><x:t>02/06/2025 10:00:00</x:t></x:si><x:si><x:t>OIL/USD</x:t></x:si><x:si><x:t>p-104</x:t></x:si><x:si><x:t>15/07/2025 12:00:00</x:t></x:si><x:si><x:t>Frais overnight</x:t></x:si><x:si><x:t>30/06/2026 06:00:00</x:t></x:si><x:si><x:t>corp action: Split</x:t></x:si><x:si><x:t>DEMO/USD 1:2</x:t></x:si><x:si><x:t>14/04/2026 14:20:00</x:t></x:si><x:si><x:t>NEWCO/USD</x:t></x:si><x:si><x:t>p-301</x:t></x:si></x:sst>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?><x:worksheet><x:sheetData><x:row r="1"><x:c r="A1" t="s"><x:v>0</x:v></x:c><x:c r="B1" t="s"><x:v>1</x:v></x:c></x:row><x:row r="2"><x:c r="A2" t="s"><x:v>2</x:v></x:c><x:c r="B2"><x:v>5000</x:v></x:c></x:row><x:row r="3"><x:c r="A3" t="s"><x:v>3</x:v></x:c><x:c r="B3" t="s"><x:v>4</x:v></x:c></x:row></x:sheetData></x:worksheet>
@@ -22,5 +22,5 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?><x:worksheet><x:sheetData><x:row r="1"><x:c r="A1" t="s"><x:v>35</x:v></x:c><x:c r="B1" t="s"><x:v>36</x:v></x:c><x:c r="C1" t="s"><x:v>37</x:v></x:c><x:c r="D1" t="s"><x:v>38</x:v></x:c><x:c r="E1" t="s"><x:v>39</x:v></x:c><x:c r="F1" t="s"><x:v>40</x:v></x:c><x:c r="G1" t="s"><x:v>41</x:v></x:c><x:c r="H1" t="s"><x:v>42</x:v></x:c><x:c r="I1" t="s"><x:v>43</x:v></x:c><x:c r="J1" t="s"><x:v>44</x:v></x:c><x:c r="K1" t="s"><x:v>45</x:v></x:c><x:c r="L1" t="s"><x:v>46</x:v></x:c><x:c r="M1" t="s"><x:v>47</x:v></x:c><x:c r="N1" t="s"><x:v>48</x:v></x:c><x:c r="O1" t="s"><x:v>49</x:v></x:c><x:c r="P1" t="s"><x:v>50</x:v></x:c><x:c r="Q1" t="s"><x:v>51</x:v></x:c><x:c r="R1" t="s"><x:v>52</x:v></x:c><x:c r="S1" t="s"><x:v>53</x:v></x:c><x:c r="T1" t="s"><x:v>54</x:v></x:c><x:c r="U1" t="s"><x:v>16</x:v></x:c><x:c r="V1" t="s"><x:v>17</x:v></x:c><x:c r="W1" t="s"><x:v>55</x:v></x:c></x:row><x:row r="2"><x:c r="A2" t="s"><x:v>56</x:v></x:c><x:c r="B2" t="s"><x:v>57</x:v></x:c><x:c r="C2" t="s"><x:v>20</x:v></x:c><x:c r="D2"><x:v>200</x:v></x:c><x:c r="E2"><x:v>5</x:v></x:c><x:c r="F2" t="s"><x:v>58</x:v></x:c><x:c r="G2" t="s"><x:v>59</x:v></x:c><x:c r="H2" t="s"><x:v>60</x:v></x:c><x:c r="I2"><x:v>0</x:v></x:c><x:c r="J2"><x:v>0</x:v></x:c><x:c r="K2"><x:v>40</x:v></x:c><x:c r="L2"><x:v>36</x:v></x:c><x:c r="M2"><x:v>1</x:v></x:c><x:c r="N2"><x:v>1</x:v></x:c><x:c r="O2"><x:v>40</x:v></x:c><x:c r="P2"><x:v>48</x:v></x:c><x:c r="Q2"><x:v>0</x:v></x:c><x:c r="R2"><x:v>0</x:v></x:c><x:c r="S2"><x:v>0</x:v></x:c><x:c r="U2" t="s"><x:v>61</x:v></x:c><x:c r="V2" t="s"><x:v>24</x:v></x:c></x:row><x:row r="3"><x:c r="A3" t="s"><x:v>62</x:v></x:c><x:c r="B3" t="s"><x:v>63</x:v></x:c><x:c r="C3" t="s"><x:v>20</x:v></x:c><x:c r="D3"><x:v>100</x:v></x:c><x:c r="E3"><x:v>1</x:v></x:c><x:c r="F3" t="s"><x:v>64</x:v></x:c><x:c r="G3" t="s"><x:v>65</x:v></x:c><x:c r="H3" t="s"><x:v>66</x:v></x:c><x:c r="I3"><x:v>0</x:v></x:c><x:c r="J3"><x:v>0</x:v></x:c><x:c r="K3"><x:v>5</x:v></x:c><x:c r="L3"><x:v>4</x:v></x:c><x:c r="M3"><x:v>1</x:v></x:c><x:c r="N3"><x:v>1</x:v></x:c><x:c r="O3"><x:v>100</x:v></x:c><x:c r="P3"><x:v>105</x:v></x:c><x:c r="Q3"><x:v>0</x:v></x:c><x:c r="R3"><x:v>0</x:v></x:c><x:c r="S3"><x:v>0</x:v></x:c><x:c r="U3" t="s"><x:v>67</x:v></x:c><x:c r="V3" t="s"><x:v>68</x:v></x:c></x:row></x:sheetData></x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?><x:worksheet><x:sheetData><x:row r="1"><x:c r="A1" t="s"><x:v>69</x:v></x:c><x:c r="B1" t="s"><x:v>16</x:v></x:c><x:c r="C1" t="s"><x:v>70</x:v></x:c><x:c r="D1" t="s"><x:v>38</x:v></x:c><x:c r="E1" t="s"><x:v>39</x:v></x:c><x:c r="F1" t="s"><x:v>71</x:v></x:c><x:c r="G1" t="s"><x:v>72</x:v></x:c><x:c r="H1" t="s"><x:v>73</x:v></x:c><x:c r="I1" t="s"><x:v>35</x:v></x:c><x:c r="J1" t="s"><x:v>74</x:v></x:c><x:c r="K1" t="s"><x:v>75</x:v></x:c></x:row><x:row r="2"><x:c r="A2" t="s"><x:v>76</x:v></x:c><x:c r="B2" t="s"><x:v>77</x:v></x:c><x:c r="C2" t="s"><x:v>78</x:v></x:c><x:c r="D2"><x:v>5000</x:v></x:c><x:c r="E2" t="s"><x:v>34</x:v></x:c><x:c r="F2"><x:v>0</x:v></x:c><x:c r="G2"><x:v>0</x:v></x:c><x:c r="H2"><x:v>5000</x:v></x:c><x:c r="J2" t="s"><x:v>34</x:v></x:c><x:c r="K2"><x:v>0</x:v></x:c></x:row><x:row r="3"><x:c r="A3" t="s"><x:v>58</x:v></x:c><x:c r="B3" t="s"><x:v>79</x:v></x:c><x:c r="C3" t="s"><x:v>80</x:v></x:c><x:c r="D3"><x:v>200</x:v></x:c><x:c r="E3"><x:v>5</x:v></x:c><x:c r="F3"><x:v>0</x:v></x:c><x:c r="G3"><x:v>0</x:v></x:c><x:c r="H3"><x:v>4800</x:v></x:c><x:c r="I3" t="s"><x:v>56</x:v></x:c><x:c r="J3" t="s"><x:v>61</x:v></x:c><x:c r="K3"><x:v>0</x:v></x:c></x:row><x:row r="4"><x:c r="A4" t="s"><x:v>21</x:v></x:c><x:c r="B4" t="s"><x:v>79</x:v></x:c><x:c r="C4" t="s"><x:v>80</x:v></x:c><x:c r="D4"><x:v>400</x:v></x:c><x:c r="E4"><x:v>10</x:v></x:c><x:c r="F4"><x:v>0</x:v></x:c><x:c r="G4"><x:v>0</x:v></x:c><x:c r="H4"><x:v>4600</x:v></x:c><x:c r="I4" t="s"><x:v>19</x:v></x:c><x:c r="J4" t="s"><x:v>61</x:v></x:c><x:c r="K4"><x:v>0</x:v></x:c></x:row><x:row r="5"><x:c r="A5" t="s"><x:v>27</x:v></x:c><x:c r="B5" t="s"><x:v>79</x:v></x:c><x:c r="C5" t="s"><x:v>81</x:v></x:c><x:c r="D5"><x:v>450</x:v></x:c><x:c r="E5"><x:v>5</x:v></x:c><x:c r="F5"><x:v>0</x:v></x:c><x:c r="G5"><x:v>0</x:v></x:c><x:c r="H5"><x:v>4150</x:v></x:c><x:c r="I5" t="s"><x:v>26</x:v></x:c><x:c r="J5" t="s"><x:v>28</x:v></x:c><x:c r="K5"><x:v>0</x:v></x:c></x:row><x:row r="6"><x:c r="A6" t="s"><x:v>32</x:v></x:c><x:c r="B6" t="s"><x:v>79</x:v></x:c><x:c r="C6" t="s"><x:v>82</x:v></x:c><x:c r="D6"><x:v>600</x:v></x:c><x:c r="E6"><x:v>2</x:v></x:c><x:c r="F6"><x:v>0</x:v></x:c><x:c r="G6"><x:v>0</x:v></x:c><x:c r="H6"><x:v>3550</x:v></x:c><x:c r="I6" t="s"><x:v>31</x:v></x:c><x:c r="J6" t="s"><x:v>83</x:v></x:c><x:c r="K6"><x:v>0</x:v></x:c></x:row><x:row r="7"><x:c r="A7" t="s"><x:v>84</x:v></x:c><x:c r="B7" t="s"><x:v>79</x:v></x:c><x:c r="C7" t="s"><x:v>85</x:v></x:c><x:c r="D7"><x:v>60</x:v></x:c><x:c r="E7"><x:v>3</x:v></x:c><x:c r="F7"><x:v>0</x:v></x:c><x:c r="G7"><x:v>0</x:v></x:c><x:c r="H7"><x:v>3490</x:v></x:c><x:c r="I7" t="s"><x:v>86</x:v></x:c><x:c r="J7" t="s"><x:v>67</x:v></x:c><x:c r="K7"><x:v>0</x:v></x:c></x:row><x:row r="8"><x:c r="A8" t="s"><x:v>87</x:v></x:c><x:c r="B8" t="s"><x:v>88</x:v></x:c><x:c r="C8" t="s"><x:v>85</x:v></x:c><x:c r="D8"><x:v>-2</x:v></x:c><x:c r="E8" t="s"><x:v>34</x:v></x:c><x:c r="F8"><x:v>0</x:v></x:c><x:c r="G8"><x:v>0</x:v></x:c><x:c r="H8"><x:v>3488</x:v></x:c><x:c r="I8" t="s"><x:v>86</x:v></x:c><x:c r="J8" t="s"><x:v>67</x:v></x:c><x:c r="K8"><x:v>0</x:v></x:c></x:row><x:row r="9"><x:c r="A9" t="s"><x:v>89</x:v></x:c><x:c r="B9" t="s"><x:v>79</x:v></x:c><x:c r="C9" t="s"><x:v>90</x:v></x:c><x:c r="D9"><x:v>300</x:v></x:c><x:c r="E9"><x:v>4</x:v></x:c><x:c r="F9"><x:v>0</x:v></x:c><x:c r="G9"><x:v>0</x:v></x:c><x:c r="H9"><x:v>3190</x:v></x:c><x:c r="I9" t="s"><x:v>91</x:v></x:c><x:c r="J9" t="s"><x:v>61</x:v></x:c><x:c r="K9"><x:v>0</x:v></x:c></x:row></x:sheetData></x:worksheet>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?><x:worksheet><x:sheetData><x:row r="1"><x:c r="A1" t="s"><x:v>69</x:v></x:c><x:c r="B1" t="s"><x:v>16</x:v></x:c><x:c r="C1" t="s"><x:v>70</x:v></x:c><x:c r="D1" t="s"><x:v>38</x:v></x:c><x:c r="E1" t="s"><x:v>39</x:v></x:c><x:c r="F1" t="s"><x:v>71</x:v></x:c><x:c r="G1" t="s"><x:v>72</x:v></x:c><x:c r="H1" t="s"><x:v>73</x:v></x:c><x:c r="I1" t="s"><x:v>35</x:v></x:c><x:c r="J1" t="s"><x:v>74</x:v></x:c><x:c r="K1" t="s"><x:v>75</x:v></x:c></x:row><x:row r="2"><x:c r="A2" t="s"><x:v>76</x:v></x:c><x:c r="B2" t="s"><x:v>77</x:v></x:c><x:c r="C2" t="s"><x:v>78</x:v></x:c><x:c r="D2"><x:v>5000</x:v></x:c><x:c r="E2" t="s"><x:v>34</x:v></x:c><x:c r="F2"><x:v>0</x:v></x:c><x:c r="G2"><x:v>0</x:v></x:c><x:c r="H2"><x:v>5000</x:v></x:c><x:c r="J2" t="s"><x:v>34</x:v></x:c><x:c r="K2"><x:v>0</x:v></x:c></x:row><x:row r="3"><x:c r="A3" t="s"><x:v>58</x:v></x:c><x:c r="B3" t="s"><x:v>79</x:v></x:c><x:c r="C3" t="s"><x:v>80</x:v></x:c><x:c r="D3"><x:v>200</x:v></x:c><x:c r="E3"><x:v>5</x:v></x:c><x:c r="F3"><x:v>0</x:v></x:c><x:c r="G3"><x:v>0</x:v></x:c><x:c r="H3"><x:v>4800</x:v></x:c><x:c r="I3" t="s"><x:v>56</x:v></x:c><x:c r="J3" t="s"><x:v>61</x:v></x:c><x:c r="K3"><x:v>0</x:v></x:c></x:row><x:row r="4"><x:c r="A4" t="s"><x:v>21</x:v></x:c><x:c r="B4" t="s"><x:v>79</x:v></x:c><x:c r="C4" t="s"><x:v>80</x:v></x:c><x:c r="D4"><x:v>400</x:v></x:c><x:c r="E4"><x:v>10</x:v></x:c><x:c r="F4"><x:v>0</x:v></x:c><x:c r="G4"><x:v>0</x:v></x:c><x:c r="H4"><x:v>4600</x:v></x:c><x:c r="I4" t="s"><x:v>19</x:v></x:c><x:c r="J4" t="s"><x:v>61</x:v></x:c><x:c r="K4"><x:v>0</x:v></x:c></x:row><x:row r="5"><x:c r="A5" t="s"><x:v>27</x:v></x:c><x:c r="B5" t="s"><x:v>79</x:v></x:c><x:c r="C5" t="s"><x:v>81</x:v></x:c><x:c r="D5"><x:v>450</x:v></x:c><x:c r="E5"><x:v>5</x:v></x:c><x:c r="F5"><x:v>0</x:v></x:c><x:c r="G5"><x:v>0</x:v></x:c><x:c r="H5"><x:v>4150</x:v></x:c><x:c r="I5" t="s"><x:v>26</x:v></x:c><x:c r="J5" t="s"><x:v>28</x:v></x:c><x:c r="K5"><x:v>0</x:v></x:c></x:row><x:row r="6"><x:c r="A6" t="s"><x:v>32</x:v></x:c><x:c r="B6" t="s"><x:v>79</x:v></x:c><x:c r="C6" t="s"><x:v>82</x:v></x:c><x:c r="D6"><x:v>600</x:v></x:c><x:c r="E6"><x:v>2</x:v></x:c><x:c r="F6"><x:v>0</x:v></x:c><x:c r="G6"><x:v>0</x:v></x:c><x:c r="H6"><x:v>3550</x:v></x:c><x:c r="I6" t="s"><x:v>31</x:v></x:c><x:c r="J6" t="s"><x:v>83</x:v></x:c><x:c r="K6"><x:v>0</x:v></x:c></x:row><x:row r="7"><x:c r="A7" t="s"><x:v>84</x:v></x:c><x:c r="B7" t="s"><x:v>79</x:v></x:c><x:c r="C7" t="s"><x:v>85</x:v></x:c><x:c r="D7"><x:v>60</x:v></x:c><x:c r="E7"><x:v>3</x:v></x:c><x:c r="F7"><x:v>0</x:v></x:c><x:c r="G7"><x:v>0</x:v></x:c><x:c r="H7"><x:v>3490</x:v></x:c><x:c r="I7" t="s"><x:v>86</x:v></x:c><x:c r="J7" t="s"><x:v>67</x:v></x:c><x:c r="K7"><x:v>0</x:v></x:c></x:row><x:row r="8"><x:c r="A8" t="s"><x:v>87</x:v></x:c><x:c r="B8" t="s"><x:v>88</x:v></x:c><x:c r="C8" t="s"><x:v>85</x:v></x:c><x:c r="D8"><x:v>-2</x:v></x:c><x:c r="E8" t="s"><x:v>34</x:v></x:c><x:c r="F8"><x:v>0</x:v></x:c><x:c r="G8"><x:v>0</x:v></x:c><x:c r="H8"><x:v>3488</x:v></x:c><x:c r="I8" t="s"><x:v>86</x:v></x:c><x:c r="J8" t="s"><x:v>67</x:v></x:c><x:c r="K8"><x:v>0</x:v></x:c></x:row><x:row r="9"><x:c r="A9" t="s"><x:v>89</x:v></x:c><x:c r="B9" t="s"><x:v>90</x:v></x:c><x:c r="C9" t="s"><x:v>91</x:v></x:c><x:c r="D9"><x:v>0</x:v></x:c><x:c r="E9" t="s"><x:v>34</x:v></x:c><x:c r="F9"><x:v>0</x:v></x:c><x:c r="G9"><x:v>0</x:v></x:c><x:c r="H9"><x:v>0</x:v></x:c><x:c r="I9" t="s"><x:v>19</x:v></x:c><x:c r="J9" t="s"><x:v>61</x:v></x:c><x:c r="K9"><x:v>0</x:v></x:c></x:row><x:row r="10"><x:c r="A10" t="s"><x:v>92</x:v></x:c><x:c r="B10" t="s"><x:v>79</x:v></x:c><x:c r="C10" t="s"><x:v>93</x:v></x:c><x:c r="D10"><x:v>300</x:v></x:c><x:c r="E10"><x:v>4</x:v></x:c><x:c r="F10"><x:v>0</x:v></x:c><x:c r="G10"><x:v>0</x:v></x:c><x:c r="H10"><x:v>3190</x:v></x:c><x:c r="I10" t="s"><x:v>94</x:v></x:c><x:c r="J10" t="s"><x:v>61</x:v></x:c><x:c r="K10"><x:v>0</x:v></x:c></x:row></x:sheetData></x:worksheet>
 </file>
--- a/tests/fixtures/etoro/releve-demo.xlsx
+++ b/tests/fixtures/etoro/releve-demo.xlsx
@@ -10,7 +10,7 @@
 </x:workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?><x:sst count="95"><x:si><x:r><x:t xml:space="preserve">No</x:t></x:r><x:r><x:t xml:space="preserve">m</x:t></x:r></x:si><x:si><x:t>Totaux</x:t></x:si><x:si><x:t>Deposits</x:t></x:si><x:si><x:t>Récapitulatif du compte (USD)</x:t></x:si><x:si><x:t>Total&#10; en (USD)</x:t></x:si><x:si><x:t>Snapshot Date</x:t></x:si><x:si><x:t>Asset</x:t></x:si><x:si><x:t>Position ID</x:t></x:si><x:si><x:t>Direction</x:t></x:si><x:si><x:t>Open Date</x:t></x:si><x:si><x:t>Leverage</x:t></x:si><x:si><x:t>Open Rate</x:t></x:si><x:si><x:t>Units</x:t></x:si><x:si><x:t>Current Rate</x:t></x:si><x:si><x:t>Value in USD</x:t></x:si><x:si><x:t>Value in EUR</x:t></x:si><x:si><x:t>Type</x:t></x:si><x:si><x:t>ISIN</x:t></x:si><x:si><x:t>Demo Industries Inc.</x:t></x:si><x:si><x:t>p-101</x:t></x:si><x:si><x:t>Long</x:t></x:si><x:si><x:t>12/02/2025 09:30:00</x:t></x:si><x:si><x:t>X1</x:t></x:si><x:si><x:t>Stocks</x:t></x:si><x:si><x:t>XX0000000001</x:t></x:si><x:si><x:t>Indice Monde UCITS ETF</x:t></x:si><x:si><x:t>p-102</x:t></x:si><x:si><x:t>03/03/2025 11:00:00</x:t></x:si><x:si><x:t>ETF</x:t></x:si><x:si><x:t>XX0000000002</x:t></x:si><x:si><x:t>Bitcoin</x:t></x:si><x:si><x:t>p-103</x:t></x:si><x:si><x:t>20/05/2025 16:45:00</x:t></x:si><x:si><x:t>Crypto Currencies</x:t></x:si><x:si><x:t>-</x:t></x:si><x:si><x:t>Identifiant de position</x:t></x:si><x:si><x:t>Action</x:t></x:si><x:si><x:t>Long / Short</x:t></x:si><x:si><x:t>Montant</x:t></x:si><x:si><x:t>Unités</x:t></x:si><x:si><x:t>Date d'ouverture</x:t></x:si><x:si><x:t>Date de clôture</x:t></x:si><x:si><x:t>Effet de levier</x:t></x:si><x:si><x:t>Frais de spread (USD)</x:t></x:si><x:si><x:t>Spread du marché (USD)</x:t></x:si><x:si><x:t>Profit (USD)</x:t></x:si><x:si><x:t>Profit (EUR)</x:t></x:si><x:si><x:t>Taux de change à l'ouverture (USD)</x:t></x:si><x:si><x:t>Taux de change à la clôture (USD)</x:t></x:si><x:si><x:t>Taux à l'ouverture</x:t></x:si><x:si><x:t>Taux à la clôture</x:t></x:si><x:si><x:t>Taux Take Profit</x:t></x:si><x:si><x:t>Taux Stop Loss</x:t></x:si><x:si><x:t>Frais overnight et dividendes</x:t></x:si><x:si><x:t>Copie de</x:t></x:si><x:si><x:t>Remarques</x:t></x:si><x:si><x:t>p-201</x:t></x:si><x:si><x:t>Demo Industries Inc. (DEMO)</x:t></x:si><x:si><x:t>05/01/2025 10:00:00</x:t></x:si><x:si><x:t>10/04/2025 15:00:00</x:t></x:si><x:si><x:t>1</x:t></x:si><x:si><x:t>Actions</x:t></x:si><x:si><x:t>p-202</x:t></x:si><x:si><x:t>Pétrole (OIL)</x:t></x:si><x:si><x:t>06/01/2025 10:00:00</x:t></x:si><x:si><x:t>11/04/2025 15:00:00</x:t></x:si><x:si><x:t>2</x:t></x:si><x:si><x:t>CFD</x:t></x:si><x:si><x:t>XX0000000005</x:t></x:si><x:si><x:t>Date</x:t></x:si><x:si><x:t>Détails</x:t></x:si><x:si><x:t>Variation Fonds propres réalisés</x:t></x:si><x:si><x:t>Équité réalisée</x:t></x:si><x:si><x:t>Solde</x:t></x:si><x:si><x:t>Type d'actif</x:t></x:si><x:si><x:t>NWA (fonds non retirables)</x:t></x:si><x:si><x:t>01/02/2025 08:00:00</x:t></x:si><x:si><x:t>Dépôt</x:t></x:si><x:si><x:t>Virement</x:t></x:si><x:si><x:t>Position ouverte</x:t></x:si><x:si><x:t>DEMO/USD</x:t></x:si><x:si><x:t>IDX.DE/EUR</x:t></x:si><x:si><x:t>BTC/USD</x:t></x:si><x:si><x:t>Crypto-monnaies</x:t></x:si><x:si><x:t>02/06/2025 10:00:00</x:t></x:si><x:si><x:t>OIL/USD</x:t></x:si><x:si><x:t>p-104</x:t></x:si><x:si><x:t>15/07/2025 12:00:00</x:t></x:si><x:si><x:t>Frais overnight</x:t></x:si><x:si><x:t>30/06/2026 06:00:00</x:t></x:si><x:si><x:t>corp action: Split</x:t></x:si><x:si><x:t>DEMO/USD 1:2</x:t></x:si><x:si><x:t>14/04/2026 14:20:00</x:t></x:si><x:si><x:t>NEWCO/USD</x:t></x:si><x:si><x:t>p-301</x:t></x:si></x:sst>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?><x:sst count="101"><x:si><x:r><x:t xml:space="preserve">No</x:t></x:r><x:r><x:t xml:space="preserve">m</x:t></x:r></x:si><x:si><x:t>Totaux</x:t></x:si><x:si><x:t>Deposits</x:t></x:si><x:si><x:t>Récapitulatif du compte (USD)</x:t></x:si><x:si><x:t>Total&#10; en (USD)</x:t></x:si><x:si><x:t>Snapshot Date</x:t></x:si><x:si><x:t>Asset</x:t></x:si><x:si><x:t>Position ID</x:t></x:si><x:si><x:t>Direction</x:t></x:si><x:si><x:t>Open Date</x:t></x:si><x:si><x:t>Leverage</x:t></x:si><x:si><x:t>Open Rate</x:t></x:si><x:si><x:t>Units</x:t></x:si><x:si><x:t>Current Rate</x:t></x:si><x:si><x:t>Value in USD</x:t></x:si><x:si><x:t>Value in EUR</x:t></x:si><x:si><x:t>Type</x:t></x:si><x:si><x:t>ISIN</x:t></x:si><x:si><x:t>Demo Industries Inc.</x:t></x:si><x:si><x:t>p-101</x:t></x:si><x:si><x:t>Long</x:t></x:si><x:si><x:t>12/02/2025 09:30:00</x:t></x:si><x:si><x:t>X1</x:t></x:si><x:si><x:t>Stocks</x:t></x:si><x:si><x:t>XX0000000001</x:t></x:si><x:si><x:t>Indice Monde UCITS ETF</x:t></x:si><x:si><x:t>p-102</x:t></x:si><x:si><x:t>03/03/2025 11:00:00</x:t></x:si><x:si><x:t>ETF</x:t></x:si><x:si><x:t>XX0000000002</x:t></x:si><x:si><x:t>Bitcoin</x:t></x:si><x:si><x:t>p-103</x:t></x:si><x:si><x:t>20/05/2025 16:45:00</x:t></x:si><x:si><x:t>Crypto Currencies</x:t></x:si><x:si><x:t>-</x:t></x:si><x:si><x:t>Identifiant de position</x:t></x:si><x:si><x:t>Action</x:t></x:si><x:si><x:t>Long / Short</x:t></x:si><x:si><x:t>Montant</x:t></x:si><x:si><x:t>Unités</x:t></x:si><x:si><x:t>Date d'ouverture</x:t></x:si><x:si><x:t>Date de clôture</x:t></x:si><x:si><x:t>Effet de levier</x:t></x:si><x:si><x:t>Frais de spread (USD)</x:t></x:si><x:si><x:t>Spread du marché (USD)</x:t></x:si><x:si><x:t>Profit (USD)</x:t></x:si><x:si><x:t>Profit (EUR)</x:t></x:si><x:si><x:t>Taux de change à l'ouverture (USD)</x:t></x:si><x:si><x:t>Taux de change à la clôture (USD)</x:t></x:si><x:si><x:t>Taux à l'ouverture</x:t></x:si><x:si><x:t>Taux à la clôture</x:t></x:si><x:si><x:t>Taux Take Profit</x:t></x:si><x:si><x:t>Taux Stop Loss</x:t></x:si><x:si><x:t>Frais overnight et dividendes</x:t></x:si><x:si><x:t>Copie de</x:t></x:si><x:si><x:t>Remarques</x:t></x:si><x:si><x:t>p-201</x:t></x:si><x:si><x:t>Demo Industries Inc. (DEMO)</x:t></x:si><x:si><x:t>05/01/2025 10:00:00</x:t></x:si><x:si><x:t>10/04/2025 15:00:00</x:t></x:si><x:si><x:t>1</x:t></x:si><x:si><x:t>Actions</x:t></x:si><x:si><x:t>p-202</x:t></x:si><x:si><x:t>Pétrole (OIL)</x:t></x:si><x:si><x:t>06/01/2025 10:00:00</x:t></x:si><x:si><x:t>11/04/2025 15:00:00</x:t></x:si><x:si><x:t>2</x:t></x:si><x:si><x:t>CFD</x:t></x:si><x:si><x:t>XX0000000005</x:t></x:si><x:si><x:t>Date</x:t></x:si><x:si><x:t>Détails</x:t></x:si><x:si><x:t>Variation Fonds propres réalisés</x:t></x:si><x:si><x:t>Équité réalisée</x:t></x:si><x:si><x:t>Solde</x:t></x:si><x:si><x:t>Type d'actif</x:t></x:si><x:si><x:t>NWA (fonds non retirables)</x:t></x:si><x:si><x:t>01/02/2025 08:00:00</x:t></x:si><x:si><x:t>Dépôt</x:t></x:si><x:si><x:t>Virement</x:t></x:si><x:si><x:t>Position ouverte</x:t></x:si><x:si><x:t>DEMO/USD</x:t></x:si><x:si><x:t>IDX.DE/EUR</x:t></x:si><x:si><x:t>BTC/USD</x:t></x:si><x:si><x:t>Crypto-monnaies</x:t></x:si><x:si><x:t>02/06/2025 10:00:00</x:t></x:si><x:si><x:t>OIL/USD</x:t></x:si><x:si><x:t>p-104</x:t></x:si><x:si><x:t>15/07/2025 12:00:00</x:t></x:si><x:si><x:t>Frais overnight</x:t></x:si><x:si><x:t>Spread d’ouverture et de clôture</x:t></x:si><x:si><x:t>À l'ouverture</x:t></x:si><x:si><x:t>18/08/2025 15:00:00</x:t></x:si><x:si><x:t>À la fermeture</x:t></x:si><x:si><x:t>01/03/2025 09:00:00</x:t></x:si><x:si><x:t>Paiement des intérêts</x:t></x:si><x:si><x:t>30/06/2026 06:00:00</x:t></x:si><x:si><x:t>corp action: Split</x:t></x:si><x:si><x:t>DEMO/USD 1:2</x:t></x:si><x:si><x:t>14/04/2026 14:20:00</x:t></x:si><x:si><x:t>NEWCO/USD</x:t></x:si><x:si><x:t>p-301</x:t></x:si></x:sst>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?><x:worksheet><x:sheetData><x:row r="1"><x:c r="A1" t="s"><x:v>0</x:v></x:c><x:c r="B1" t="s"><x:v>1</x:v></x:c></x:row><x:row r="2"><x:c r="A2" t="s"><x:v>2</x:v></x:c><x:c r="B2"><x:v>5000</x:v></x:c></x:row><x:row r="3"><x:c r="A3" t="s"><x:v>3</x:v></x:c><x:c r="B3" t="s"><x:v>4</x:v></x:c></x:row></x:sheetData></x:worksheet>
@@ -22,5 +22,5 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?><x:worksheet><x:sheetData><x:row r="1"><x:c r="A1" t="s"><x:v>35</x:v></x:c><x:c r="B1" t="s"><x:v>36</x:v></x:c><x:c r="C1" t="s"><x:v>37</x:v></x:c><x:c r="D1" t="s"><x:v>38</x:v></x:c><x:c r="E1" t="s"><x:v>39</x:v></x:c><x:c r="F1" t="s"><x:v>40</x:v></x:c><x:c r="G1" t="s"><x:v>41</x:v></x:c><x:c r="H1" t="s"><x:v>42</x:v></x:c><x:c r="I1" t="s"><x:v>43</x:v></x:c><x:c r="J1" t="s"><x:v>44</x:v></x:c><x:c r="K1" t="s"><x:v>45</x:v></x:c><x:c r="L1" t="s"><x:v>46</x:v></x:c><x:c r="M1" t="s"><x:v>47</x:v></x:c><x:c r="N1" t="s"><x:v>48</x:v></x:c><x:c r="O1" t="s"><x:v>49</x:v></x:c><x:c r="P1" t="s"><x:v>50</x:v></x:c><x:c r="Q1" t="s"><x:v>51</x:v></x:c><x:c r="R1" t="s"><x:v>52</x:v></x:c><x:c r="S1" t="s"><x:v>53</x:v></x:c><x:c r="T1" t="s"><x:v>54</x:v></x:c><x:c r="U1" t="s"><x:v>16</x:v></x:c><x:c r="V1" t="s"><x:v>17</x:v></x:c><x:c r="W1" t="s"><x:v>55</x:v></x:c></x:row><x:row r="2"><x:c r="A2" t="s"><x:v>56</x:v></x:c><x:c r="B2" t="s"><x:v>57</x:v></x:c><x:c r="C2" t="s"><x:v>20</x:v></x:c><x:c r="D2"><x:v>200</x:v></x:c><x:c r="E2"><x:v>5</x:v></x:c><x:c r="F2" t="s"><x:v>58</x:v></x:c><x:c r="G2" t="s"><x:v>59</x:v></x:c><x:c r="H2" t="s"><x:v>60</x:v></x:c><x:c r="I2"><x:v>0</x:v></x:c><x:c r="J2"><x:v>0</x:v></x:c><x:c r="K2"><x:v>40</x:v></x:c><x:c r="L2"><x:v>36</x:v></x:c><x:c r="M2"><x:v>1</x:v></x:c><x:c r="N2"><x:v>1</x:v></x:c><x:c r="O2"><x:v>40</x:v></x:c><x:c r="P2"><x:v>48</x:v></x:c><x:c r="Q2"><x:v>0</x:v></x:c><x:c r="R2"><x:v>0</x:v></x:c><x:c r="S2"><x:v>0</x:v></x:c><x:c r="U2" t="s"><x:v>61</x:v></x:c><x:c r="V2" t="s"><x:v>24</x:v></x:c></x:row><x:row r="3"><x:c r="A3" t="s"><x:v>62</x:v></x:c><x:c r="B3" t="s"><x:v>63</x:v></x:c><x:c r="C3" t="s"><x:v>20</x:v></x:c><x:c r="D3"><x:v>100</x:v></x:c><x:c r="E3"><x:v>1</x:v></x:c><x:c r="F3" t="s"><x:v>64</x:v></x:c><x:c r="G3" t="s"><x:v>65</x:v></x:c><x:c r="H3" t="s"><x:v>66</x:v></x:c><x:c r="I3"><x:v>0</x:v></x:c><x:c r="J3"><x:v>0</x:v></x:c><x:c r="K3"><x:v>5</x:v></x:c><x:c r="L3"><x:v>4</x:v></x:c><x:c r="M3"><x:v>1</x:v></x:c><x:c r="N3"><x:v>1</x:v></x:c><x:c r="O3"><x:v>100</x:v></x:c><x:c r="P3"><x:v>105</x:v></x:c><x:c r="Q3"><x:v>0</x:v></x:c><x:c r="R3"><x:v>0</x:v></x:c><x:c r="S3"><x:v>0</x:v></x:c><x:c r="U3" t="s"><x:v>67</x:v></x:c><x:c r="V3" t="s"><x:v>68</x:v></x:c></x:row></x:sheetData></x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?><x:worksheet><x:sheetData><x:row r="1"><x:c r="A1" t="s"><x:v>69</x:v></x:c><x:c r="B1" t="s"><x:v>16</x:v></x:c><x:c r="C1" t="s"><x:v>70</x:v></x:c><x:c r="D1" t="s"><x:v>38</x:v></x:c><x:c r="E1" t="s"><x:v>39</x:v></x:c><x:c r="F1" t="s"><x:v>71</x:v></x:c><x:c r="G1" t="s"><x:v>72</x:v></x:c><x:c r="H1" t="s"><x:v>73</x:v></x:c><x:c r="I1" t="s"><x:v>35</x:v></x:c><x:c r="J1" t="s"><x:v>74</x:v></x:c><x:c r="K1" t="s"><x:v>75</x:v></x:c></x:row><x:row r="2"><x:c r="A2" t="s"><x:v>76</x:v></x:c><x:c r="B2" t="s"><x:v>77</x:v></x:c><x:c r="C2" t="s"><x:v>78</x:v></x:c><x:c r="D2"><x:v>5000</x:v></x:c><x:c r="E2" t="s"><x:v>34</x:v></x:c><x:c r="F2"><x:v>0</x:v></x:c><x:c r="G2"><x:v>0</x:v></x:c><x:c r="H2"><x:v>5000</x:v></x:c><x:c r="J2" t="s"><x:v>34</x:v></x:c><x:c r="K2"><x:v>0</x:v></x:c></x:row><x:row r="3"><x:c r="A3" t="s"><x:v>58</x:v></x:c><x:c r="B3" t="s"><x:v>79</x:v></x:c><x:c r="C3" t="s"><x:v>80</x:v></x:c><x:c r="D3"><x:v>200</x:v></x:c><x:c r="E3"><x:v>5</x:v></x:c><x:c r="F3"><x:v>0</x:v></x:c><x:c r="G3"><x:v>0</x:v></x:c><x:c r="H3"><x:v>4800</x:v></x:c><x:c r="I3" t="s"><x:v>56</x:v></x:c><x:c r="J3" t="s"><x:v>61</x:v></x:c><x:c r="K3"><x:v>0</x:v></x:c></x:row><x:row r="4"><x:c r="A4" t="s"><x:v>21</x:v></x:c><x:c r="B4" t="s"><x:v>79</x:v></x:c><x:c r="C4" t="s"><x:v>80</x:v></x:c><x:c r="D4"><x:v>400</x:v></x:c><x:c r="E4"><x:v>10</x:v></x:c><x:c r="F4"><x:v>0</x:v></x:c><x:c r="G4"><x:v>0</x:v></x:c><x:c r="H4"><x:v>4600</x:v></x:c><x:c r="I4" t="s"><x:v>19</x:v></x:c><x:c r="J4" t="s"><x:v>61</x:v></x:c><x:c r="K4"><x:v>0</x:v></x:c></x:row><x:row r="5"><x:c r="A5" t="s"><x:v>27</x:v></x:c><x:c r="B5" t="s"><x:v>79</x:v></x:c><x:c r="C5" t="s"><x:v>81</x:v></x:c><x:c r="D5"><x:v>450</x:v></x:c><x:c r="E5"><x:v>5</x:v></x:c><x:c r="F5"><x:v>0</x:v></x:c><x:c r="G5"><x:v>0</x:v></x:c><x:c r="H5"><x:v>4150</x:v></x:c><x:c r="I5" t="s"><x:v>26</x:v></x:c><x:c r="J5" t="s"><x:v>28</x:v></x:c><x:c r="K5"><x:v>0</x:v></x:c></x:row><x:row r="6"><x:c r="A6" t="s"><x:v>32</x:v></x:c><x:c r="B6" t="s"><x:v>79</x:v></x:c><x:c r="C6" t="s"><x:v>82</x:v></x:c><x:c r="D6"><x:v>600</x:v></x:c><x:c r="E6"><x:v>2</x:v></x:c><x:c r="F6"><x:v>0</x:v></x:c><x:c r="G6"><x:v>0</x:v></x:c><x:c r="H6"><x:v>3550</x:v></x:c><x:c r="I6" t="s"><x:v>31</x:v></x:c><x:c r="J6" t="s"><x:v>83</x:v></x:c><x:c r="K6"><x:v>0</x:v></x:c></x:row><x:row r="7"><x:c r="A7" t="s"><x:v>84</x:v></x:c><x:c r="B7" t="s"><x:v>79</x:v></x:c><x:c r="C7" t="s"><x:v>85</x:v></x:c><x:c r="D7"><x:v>60</x:v></x:c><x:c r="E7"><x:v>3</x:v></x:c><x:c r="F7"><x:v>0</x:v></x:c><x:c r="G7"><x:v>0</x:v></x:c><x:c r="H7"><x:v>3490</x:v></x:c><x:c r="I7" t="s"><x:v>86</x:v></x:c><x:c r="J7" t="s"><x:v>67</x:v></x:c><x:c r="K7"><x:v>0</x:v></x:c></x:row><x:row r="8"><x:c r="A8" t="s"><x:v>87</x:v></x:c><x:c r="B8" t="s"><x:v>88</x:v></x:c><x:c r="C8" t="s"><x:v>85</x:v></x:c><x:c r="D8"><x:v>-2</x:v></x:c><x:c r="E8" t="s"><x:v>34</x:v></x:c><x:c r="F8"><x:v>0</x:v></x:c><x:c r="G8"><x:v>0</x:v></x:c><x:c r="H8"><x:v>3488</x:v></x:c><x:c r="I8" t="s"><x:v>86</x:v></x:c><x:c r="J8" t="s"><x:v>67</x:v></x:c><x:c r="K8"><x:v>0</x:v></x:c></x:row><x:row r="9"><x:c r="A9" t="s"><x:v>89</x:v></x:c><x:c r="B9" t="s"><x:v>90</x:v></x:c><x:c r="C9" t="s"><x:v>91</x:v></x:c><x:c r="D9"><x:v>0</x:v></x:c><x:c r="E9" t="s"><x:v>34</x:v></x:c><x:c r="F9"><x:v>0</x:v></x:c><x:c r="G9"><x:v>0</x:v></x:c><x:c r="H9"><x:v>0</x:v></x:c><x:c r="I9" t="s"><x:v>19</x:v></x:c><x:c r="J9" t="s"><x:v>61</x:v></x:c><x:c r="K9"><x:v>0</x:v></x:c></x:row><x:row r="10"><x:c r="A10" t="s"><x:v>92</x:v></x:c><x:c r="B10" t="s"><x:v>79</x:v></x:c><x:c r="C10" t="s"><x:v>93</x:v></x:c><x:c r="D10"><x:v>300</x:v></x:c><x:c r="E10"><x:v>4</x:v></x:c><x:c r="F10"><x:v>0</x:v></x:c><x:c r="G10"><x:v>0</x:v></x:c><x:c r="H10"><x:v>3190</x:v></x:c><x:c r="I10" t="s"><x:v>94</x:v></x:c><x:c r="J10" t="s"><x:v>61</x:v></x:c><x:c r="K10"><x:v>0</x:v></x:c></x:row></x:sheetData></x:worksheet>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?><x:worksheet><x:sheetData><x:row r="1"><x:c r="A1" t="s"><x:v>69</x:v></x:c><x:c r="B1" t="s"><x:v>16</x:v></x:c><x:c r="C1" t="s"><x:v>70</x:v></x:c><x:c r="D1" t="s"><x:v>38</x:v></x:c><x:c r="E1" t="s"><x:v>39</x:v></x:c><x:c r="F1" t="s"><x:v>71</x:v></x:c><x:c r="G1" t="s"><x:v>72</x:v></x:c><x:c r="H1" t="s"><x:v>73</x:v></x:c><x:c r="I1" t="s"><x:v>35</x:v></x:c><x:c r="J1" t="s"><x:v>74</x:v></x:c><x:c r="K1" t="s"><x:v>75</x:v></x:c></x:row><x:row r="2"><x:c r="A2" t="s"><x:v>76</x:v></x:c><x:c r="B2" t="s"><x:v>77</x:v></x:c><x:c r="C2" t="s"><x:v>78</x:v></x:c><x:c r="D2"><x:v>5000</x:v></x:c><x:c r="E2" t="s"><x:v>34</x:v></x:c><x:c r="F2"><x:v>0</x:v></x:c><x:c r="G2"><x:v>0</x:v></x:c><x:c r="H2"><x:v>5000</x:v></x:c><x:c r="J2" t="s"><x:v>34</x:v></x:c><x:c r="K2"><x:v>0</x:v></x:c></x:row><x:row r="3"><x:c r="A3" t="s"><x:v>58</x:v></x:c><x:c r="B3" t="s"><x:v>79</x:v></x:c><x:c r="C3" t="s"><x:v>80</x:v></x:c><x:c r="D3"><x:v>200</x:v></x:c><x:c r="E3"><x:v>5</x:v></x:c><x:c r="F3"><x:v>0</x:v></x:c><x:c r="G3"><x:v>0</x:v></x:c><x:c r="H3"><x:v>4800</x:v></x:c><x:c r="I3" t="s"><x:v>56</x:v></x:c><x:c r="J3" t="s"><x:v>61</x:v></x:c><x:c r="K3"><x:v>0</x:v></x:c></x:row><x:row r="4"><x:c r="A4" t="s"><x:v>21</x:v></x:c><x:c r="B4" t="s"><x:v>79</x:v></x:c><x:c r="C4" t="s"><x:v>80</x:v></x:c><x:c r="D4"><x:v>400</x:v></x:c><x:c r="E4"><x:v>10</x:v></x:c><x:c r="F4"><x:v>0</x:v></x:c><x:c r="G4"><x:v>0</x:v></x:c><x:c r="H4"><x:v>4600</x:v></x:c><x:c r="I4" t="s"><x:v>19</x:v></x:c><x:c r="J4" t="s"><x:v>61</x:v></x:c><x:c r="K4"><x:v>0</x:v></x:c></x:row><x:row r="5"><x:c r="A5" t="s"><x:v>27</x:v></x:c><x:c r="B5" t="s"><x:v>79</x:v></x:c><x:c r="C5" t="s"><x:v>81</x:v></x:c><x:c r="D5"><x:v>450</x:v></x:c><x:c r="E5"><x:v>5</x:v></x:c><x:c r="F5"><x:v>0</x:v></x:c><x:c r="G5"><x:v>0</x:v></x:c><x:c r="H5"><x:v>4150</x:v></x:c><x:c r="I5" t="s"><x:v>26</x:v></x:c><x:c r="J5" t="s"><x:v>28</x:v></x:c><x:c r="K5"><x:v>0</x:v></x:c></x:row><x:row r="6"><x:c r="A6" t="s"><x:v>32</x:v></x:c><x:c r="B6" t="s"><x:v>79</x:v></x:c><x:c r="C6" t="s"><x:v>82</x:v></x:c><x:c r="D6"><x:v>600</x:v></x:c><x:c r="E6"><x:v>2</x:v></x:c><x:c r="F6"><x:v>0</x:v></x:c><x:c r="G6"><x:v>0</x:v></x:c><x:c r="H6"><x:v>3550</x:v></x:c><x:c r="I6" t="s"><x:v>31</x:v></x:c><x:c r="J6" t="s"><x:v>83</x:v></x:c><x:c r="K6"><x:v>0</x:v></x:c></x:row><x:row r="7"><x:c r="A7" t="s"><x:v>84</x:v></x:c><x:c r="B7" t="s"><x:v>79</x:v></x:c><x:c r="C7" t="s"><x:v>85</x:v></x:c><x:c r="D7"><x:v>60</x:v></x:c><x:c r="E7"><x:v>3</x:v></x:c><x:c r="F7"><x:v>0</x:v></x:c><x:c r="G7"><x:v>0</x:v></x:c><x:c r="H7"><x:v>3490</x:v></x:c><x:c r="I7" t="s"><x:v>86</x:v></x:c><x:c r="J7" t="s"><x:v>67</x:v></x:c><x:c r="K7"><x:v>0</x:v></x:c></x:row><x:row r="8"><x:c r="A8" t="s"><x:v>87</x:v></x:c><x:c r="B8" t="s"><x:v>88</x:v></x:c><x:c r="C8" t="s"><x:v>85</x:v></x:c><x:c r="D8"><x:v>-2</x:v></x:c><x:c r="E8" t="s"><x:v>34</x:v></x:c><x:c r="F8"><x:v>0</x:v></x:c><x:c r="G8"><x:v>0</x:v></x:c><x:c r="H8"><x:v>3488</x:v></x:c><x:c r="I8" t="s"><x:v>86</x:v></x:c><x:c r="J8" t="s"><x:v>67</x:v></x:c><x:c r="K8"><x:v>0</x:v></x:c></x:row><x:row r="9"><x:c r="A9" t="s"><x:v>21</x:v></x:c><x:c r="B9" t="s"><x:v>89</x:v></x:c><x:c r="C9" t="s"><x:v>90</x:v></x:c><x:c r="D9"><x:v>-4</x:v></x:c><x:c r="E9" t="s"><x:v>34</x:v></x:c><x:c r="F9"><x:v>0</x:v></x:c><x:c r="G9"><x:v>0</x:v></x:c><x:c r="H9"><x:v>4596</x:v></x:c><x:c r="I9" t="s"><x:v>19</x:v></x:c><x:c r="J9" t="s"><x:v>61</x:v></x:c><x:c r="K9"><x:v>0</x:v></x:c></x:row><x:row r="10"><x:c r="A10" t="s"><x:v>91</x:v></x:c><x:c r="B10" t="s"><x:v>89</x:v></x:c><x:c r="C10" t="s"><x:v>92</x:v></x:c><x:c r="D10"><x:v>-3</x:v></x:c><x:c r="E10" t="s"><x:v>34</x:v></x:c><x:c r="F10"><x:v>0</x:v></x:c><x:c r="G10"><x:v>0</x:v></x:c><x:c r="H10"><x:v>4593</x:v></x:c><x:c r="I10" t="s"><x:v>56</x:v></x:c><x:c r="J10" t="s"><x:v>61</x:v></x:c><x:c r="K10"><x:v>0</x:v></x:c></x:row><x:row r="11"><x:c r="A11" t="s"><x:v>84</x:v></x:c><x:c r="B11" t="s"><x:v>89</x:v></x:c><x:c r="C11" t="s"><x:v>90</x:v></x:c><x:c r="D11"><x:v>-1</x:v></x:c><x:c r="E11" t="s"><x:v>34</x:v></x:c><x:c r="F11"><x:v>0</x:v></x:c><x:c r="G11"><x:v>0</x:v></x:c><x:c r="H11"><x:v>3489</x:v></x:c><x:c r="I11" t="s"><x:v>86</x:v></x:c><x:c r="J11" t="s"><x:v>67</x:v></x:c><x:c r="K11"><x:v>0</x:v></x:c></x:row><x:row r="12"><x:c r="A12" t="s"><x:v>93</x:v></x:c><x:c r="B12" t="s"><x:v>94</x:v></x:c><x:c r="C12" t="s"><x:v>34</x:v></x:c><x:c r="D12"><x:v>1.5</x:v></x:c><x:c r="E12" t="s"><x:v>34</x:v></x:c><x:c r="F12"><x:v>1.5</x:v></x:c><x:c r="G12"><x:v>0</x:v></x:c><x:c r="H12"><x:v>4601</x:v></x:c><x:c r="J12" t="s"><x:v>34</x:v></x:c><x:c r="K12"><x:v>0</x:v></x:c></x:row><x:row r="13"><x:c r="A13" t="s"><x:v>95</x:v></x:c><x:c r="B13" t="s"><x:v>96</x:v></x:c><x:c r="C13" t="s"><x:v>97</x:v></x:c><x:c r="D13"><x:v>0</x:v></x:c><x:c r="E13" t="s"><x:v>34</x:v></x:c><x:c r="F13"><x:v>0</x:v></x:c><x:c r="G13"><x:v>0</x:v></x:c><x:c r="H13"><x:v>0</x:v></x:c><x:c r="I13" t="s"><x:v>19</x:v></x:c><x:c r="J13" t="s"><x:v>61</x:v></x:c><x:c r="K13"><x:v>0</x:v></x:c></x:row><x:row r="14"><x:c r="A14" t="s"><x:v>98</x:v></x:c><x:c r="B14" t="s"><x:v>79</x:v></x:c><x:c r="C14" t="s"><x:v>99</x:v></x:c><x:c r="D14"><x:v>300</x:v></x:c><x:c r="E14"><x:v>4</x:v></x:c><x:c r="F14"><x:v>0</x:v></x:c><x:c r="G14"><x:v>0</x:v></x:c><x:c r="H14"><x:v>3190</x:v></x:c><x:c r="I14" t="s"><x:v>100</x:v></x:c><x:c r="J14" t="s"><x:v>61</x:v></x:c><x:c r="K14"><x:v>0</x:v></x:c></x:row></x:sheetData></x:worksheet>
 </file>
--- a/tests/fixtures/etoro/releve-demo.xlsx
+++ b/tests/fixtures/etoro/releve-demo.xlsx
@@ -6,21 +6,25 @@
     <x:sheet name="Holdings" sheetId="2" r:id="rId3"/>
     <x:sheet name="Positions fermées" sheetId="3" r:id="rId4"/>
     <x:sheet name="Activité du compte" sheetId="4" r:id="rId5"/>
+    <x:sheet name="Dividendes" sheetId="5" r:id="rId6"/>
   </x:sheets>
 </x:workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?><x:sst count="101"><x:si><x:r><x:t xml:space="preserve">No</x:t></x:r><x:r><x:t xml:space="preserve">m</x:t></x:r></x:si><x:si><x:t>Totaux</x:t></x:si><x:si><x:t>Deposits</x:t></x:si><x:si><x:t>Récapitulatif du compte (USD)</x:t></x:si><x:si><x:t>Total&#10; en (USD)</x:t></x:si><x:si><x:t>Snapshot Date</x:t></x:si><x:si><x:t>Asset</x:t></x:si><x:si><x:t>Position ID</x:t></x:si><x:si><x:t>Direction</x:t></x:si><x:si><x:t>Open Date</x:t></x:si><x:si><x:t>Leverage</x:t></x:si><x:si><x:t>Open Rate</x:t></x:si><x:si><x:t>Units</x:t></x:si><x:si><x:t>Current Rate</x:t></x:si><x:si><x:t>Value in USD</x:t></x:si><x:si><x:t>Value in EUR</x:t></x:si><x:si><x:t>Type</x:t></x:si><x:si><x:t>ISIN</x:t></x:si><x:si><x:t>Demo Industries Inc.</x:t></x:si><x:si><x:t>p-101</x:t></x:si><x:si><x:t>Long</x:t></x:si><x:si><x:t>12/02/2025 09:30:00</x:t></x:si><x:si><x:t>X1</x:t></x:si><x:si><x:t>Stocks</x:t></x:si><x:si><x:t>XX0000000001</x:t></x:si><x:si><x:t>Indice Monde UCITS ETF</x:t></x:si><x:si><x:t>p-102</x:t></x:si><x:si><x:t>03/03/2025 11:00:00</x:t></x:si><x:si><x:t>ETF</x:t></x:si><x:si><x:t>XX0000000002</x:t></x:si><x:si><x:t>Bitcoin</x:t></x:si><x:si><x:t>p-103</x:t></x:si><x:si><x:t>20/05/2025 16:45:00</x:t></x:si><x:si><x:t>Crypto Currencies</x:t></x:si><x:si><x:t>-</x:t></x:si><x:si><x:t>Identifiant de position</x:t></x:si><x:si><x:t>Action</x:t></x:si><x:si><x:t>Long / Short</x:t></x:si><x:si><x:t>Montant</x:t></x:si><x:si><x:t>Unités</x:t></x:si><x:si><x:t>Date d'ouverture</x:t></x:si><x:si><x:t>Date de clôture</x:t></x:si><x:si><x:t>Effet de levier</x:t></x:si><x:si><x:t>Frais de spread (USD)</x:t></x:si><x:si><x:t>Spread du marché (USD)</x:t></x:si><x:si><x:t>Profit (USD)</x:t></x:si><x:si><x:t>Profit (EUR)</x:t></x:si><x:si><x:t>Taux de change à l'ouverture (USD)</x:t></x:si><x:si><x:t>Taux de change à la clôture (USD)</x:t></x:si><x:si><x:t>Taux à l'ouverture</x:t></x:si><x:si><x:t>Taux à la clôture</x:t></x:si><x:si><x:t>Taux Take Profit</x:t></x:si><x:si><x:t>Taux Stop Loss</x:t></x:si><x:si><x:t>Frais overnight et dividendes</x:t></x:si><x:si><x:t>Copie de</x:t></x:si><x:si><x:t>Remarques</x:t></x:si><x:si><x:t>p-201</x:t></x:si><x:si><x:t>Demo Industries Inc. (DEMO)</x:t></x:si><x:si><x:t>05/01/2025 10:00:00</x:t></x:si><x:si><x:t>10/04/2025 15:00:00</x:t></x:si><x:si><x:t>1</x:t></x:si><x:si><x:t>Actions</x:t></x:si><x:si><x:t>p-202</x:t></x:si><x:si><x:t>Pétrole (OIL)</x:t></x:si><x:si><x:t>06/01/2025 10:00:00</x:t></x:si><x:si><x:t>11/04/2025 15:00:00</x:t></x:si><x:si><x:t>2</x:t></x:si><x:si><x:t>CFD</x:t></x:si><x:si><x:t>XX0000000005</x:t></x:si><x:si><x:t>Date</x:t></x:si><x:si><x:t>Détails</x:t></x:si><x:si><x:t>Variation Fonds propres réalisés</x:t></x:si><x:si><x:t>Équité réalisée</x:t></x:si><x:si><x:t>Solde</x:t></x:si><x:si><x:t>Type d'actif</x:t></x:si><x:si><x:t>NWA (fonds non retirables)</x:t></x:si><x:si><x:t>01/02/2025 08:00:00</x:t></x:si><x:si><x:t>Dépôt</x:t></x:si><x:si><x:t>Virement</x:t></x:si><x:si><x:t>Position ouverte</x:t></x:si><x:si><x:t>DEMO/USD</x:t></x:si><x:si><x:t>IDX.DE/EUR</x:t></x:si><x:si><x:t>BTC/USD</x:t></x:si><x:si><x:t>Crypto-monnaies</x:t></x:si><x:si><x:t>02/06/2025 10:00:00</x:t></x:si><x:si><x:t>OIL/USD</x:t></x:si><x:si><x:t>p-104</x:t></x:si><x:si><x:t>15/07/2025 12:00:00</x:t></x:si><x:si><x:t>Frais overnight</x:t></x:si><x:si><x:t>Spread d’ouverture et de clôture</x:t></x:si><x:si><x:t>À l'ouverture</x:t></x:si><x:si><x:t>18/08/2025 15:00:00</x:t></x:si><x:si><x:t>À la fermeture</x:t></x:si><x:si><x:t>01/03/2025 09:00:00</x:t></x:si><x:si><x:t>Paiement des intérêts</x:t></x:si><x:si><x:t>30/06/2026 06:00:00</x:t></x:si><x:si><x:t>corp action: Split</x:t></x:si><x:si><x:t>DEMO/USD 1:2</x:t></x:si><x:si><x:t>14/04/2026 14:20:00</x:t></x:si><x:si><x:t>NEWCO/USD</x:t></x:si><x:si><x:t>p-301</x:t></x:si></x:sst>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?><x:sst count="123"><x:si><x:r><x:t xml:space="preserve">No</x:t></x:r><x:r><x:t xml:space="preserve">m</x:t></x:r></x:si><x:si><x:t>Totaux</x:t></x:si><x:si><x:t>Deposits</x:t></x:si><x:si><x:t>Récapitulatif du compte (USD)</x:t></x:si><x:si><x:t>Total&#10; en (USD)</x:t></x:si><x:si><x:t>Snapshot Date</x:t></x:si><x:si><x:t>Asset</x:t></x:si><x:si><x:t>Position ID</x:t></x:si><x:si><x:t>Direction</x:t></x:si><x:si><x:t>Open Date</x:t></x:si><x:si><x:t>Leverage</x:t></x:si><x:si><x:t>Open Rate</x:t></x:si><x:si><x:t>Units</x:t></x:si><x:si><x:t>Current Rate</x:t></x:si><x:si><x:t>Value in USD</x:t></x:si><x:si><x:t>Value in EUR</x:t></x:si><x:si><x:t>Type</x:t></x:si><x:si><x:t>ISIN</x:t></x:si><x:si><x:t>Demo Industries Inc.</x:t></x:si><x:si><x:t>p-101</x:t></x:si><x:si><x:t>Long</x:t></x:si><x:si><x:t>12/02/2025 09:30:00</x:t></x:si><x:si><x:t>X1</x:t></x:si><x:si><x:t>Stocks</x:t></x:si><x:si><x:t>XX0000000001</x:t></x:si><x:si><x:t>Indice Monde UCITS ETF</x:t></x:si><x:si><x:t>p-102</x:t></x:si><x:si><x:t>03/03/2025 11:00:00</x:t></x:si><x:si><x:t>ETF</x:t></x:si><x:si><x:t>XX0000000002</x:t></x:si><x:si><x:t>p-901</x:t></x:si><x:si><x:t>18/11/2024 09:00:00</x:t></x:si><x:si><x:t>Bitcoin</x:t></x:si><x:si><x:t>p-103</x:t></x:si><x:si><x:t>20/05/2025 16:45:00</x:t></x:si><x:si><x:t>Crypto Currencies</x:t></x:si><x:si><x:t>-</x:t></x:si><x:si><x:t>Identifiant de position</x:t></x:si><x:si><x:t>Action</x:t></x:si><x:si><x:t>Long / Short</x:t></x:si><x:si><x:t>Montant</x:t></x:si><x:si><x:t>Unités</x:t></x:si><x:si><x:t>Date d'ouverture</x:t></x:si><x:si><x:t>Date de clôture</x:t></x:si><x:si><x:t>Effet de levier</x:t></x:si><x:si><x:t>Frais de spread (USD)</x:t></x:si><x:si><x:t>Spread du marché (USD)</x:t></x:si><x:si><x:t>Profit (USD)</x:t></x:si><x:si><x:t>Profit (EUR)</x:t></x:si><x:si><x:t>Taux de change à l'ouverture (USD)</x:t></x:si><x:si><x:t>Taux de change à la clôture (USD)</x:t></x:si><x:si><x:t>Taux à l'ouverture</x:t></x:si><x:si><x:t>Taux à la clôture</x:t></x:si><x:si><x:t>Taux Take Profit</x:t></x:si><x:si><x:t>Taux Stop Loss</x:t></x:si><x:si><x:t>Frais overnight et dividendes</x:t></x:si><x:si><x:t>Copie de</x:t></x:si><x:si><x:t>Remarques</x:t></x:si><x:si><x:t>p-201</x:t></x:si><x:si><x:t>Demo Industries Inc. (DEMO)</x:t></x:si><x:si><x:t>05/01/2025 10:00:00</x:t></x:si><x:si><x:t>10/04/2025 15:00:00</x:t></x:si><x:si><x:t>1</x:t></x:si><x:si><x:t>Actions</x:t></x:si><x:si><x:t>p-202</x:t></x:si><x:si><x:t>Pétrole (OIL)</x:t></x:si><x:si><x:t>06/01/2025 10:00:00</x:t></x:si><x:si><x:t>11/04/2025 15:00:00</x:t></x:si><x:si><x:t>2</x:t></x:si><x:si><x:t>CFD</x:t></x:si><x:si><x:t>XX0000000005</x:t></x:si><x:si><x:t>Date</x:t></x:si><x:si><x:t>Détails</x:t></x:si><x:si><x:t>Variation Fonds propres réalisés</x:t></x:si><x:si><x:t>Équité réalisée</x:t></x:si><x:si><x:t>Solde</x:t></x:si><x:si><x:t>Type d'actif</x:t></x:si><x:si><x:t>NWA (fonds non retirables)</x:t></x:si><x:si><x:t>01/02/2025 08:00:00</x:t></x:si><x:si><x:t>Dépôt</x:t></x:si><x:si><x:t>Virement</x:t></x:si><x:si><x:t>Position ouverte</x:t></x:si><x:si><x:t>DEMO/USD</x:t></x:si><x:si><x:t>IDX.DE/EUR</x:t></x:si><x:si><x:t>BTC/USD</x:t></x:si><x:si><x:t>Crypto-monnaies</x:t></x:si><x:si><x:t>02/06/2025 10:00:00</x:t></x:si><x:si><x:t>OIL/USD</x:t></x:si><x:si><x:t>p-104</x:t></x:si><x:si><x:t>15/07/2025 12:00:00</x:t></x:si><x:si><x:t>Frais overnight</x:t></x:si><x:si><x:t>Spread d’ouverture et de clôture</x:t></x:si><x:si><x:t>À l'ouverture</x:t></x:si><x:si><x:t>18/08/2025 15:00:00</x:t></x:si><x:si><x:t>À la fermeture</x:t></x:si><x:si><x:t>01/03/2025 09:00:00</x:t></x:si><x:si><x:t>Paiement des intérêts</x:t></x:si><x:si><x:t>30/06/2026 06:00:00</x:t></x:si><x:si><x:t>corp action: Split</x:t></x:si><x:si><x:t>DEMO/USD 1:2</x:t></x:si><x:si><x:t>14/04/2026 14:20:00</x:t></x:si><x:si><x:t>NEWCO/USD</x:t></x:si><x:si><x:t>p-301</x:t></x:si><x:si><x:t>Date du paiement</x:t></x:si><x:si><x:t>Nom de l'instrument</x:t></x:si><x:si><x:t>Dividende net reçu (USD)</x:t></x:si><x:si><x:t>Net dividends</x:t></x:si><x:si><x:t>Currency</x:t></x:si><x:si><x:t>Affranchi/Non affranchi</x:t></x:si><x:si><x:t>Crédits d’affranchissement (AUD)</x:t></x:si><x:si><x:t>Dividende net reçu (EUR)</x:t></x:si><x:si><x:t>Taux de retenue à la source (%)</x:t></x:si><x:si><x:t>Montant du prélèvement à la source (USD)</x:t></x:si><x:si><x:t>Montant du prélèvement à la source (EUR)</x:t></x:si><x:si><x:t>15/04/2025</x:t></x:si><x:si><x:t>15 %</x:t></x:si><x:si><x:t>20/05/2025</x:t></x:si><x:si><x:t>25 %</x:t></x:si><x:si><x:t>10/06/2025</x:t></x:si><x:si><x:t>Vanished Corp.</x:t></x:si><x:si><x:t>0 %</x:t></x:si><x:si><x:t>p-999</x:t></x:si><x:si><x:t>XX0000000009</x:t></x:si></x:sst>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?><x:worksheet><x:sheetData><x:row r="1"><x:c r="A1" t="s"><x:v>0</x:v></x:c><x:c r="B1" t="s"><x:v>1</x:v></x:c></x:row><x:row r="2"><x:c r="A2" t="s"><x:v>2</x:v></x:c><x:c r="B2"><x:v>5000</x:v></x:c></x:row><x:row r="3"><x:c r="A3" t="s"><x:v>3</x:v></x:c><x:c r="B3" t="s"><x:v>4</x:v></x:c></x:row></x:sheetData></x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?><x:worksheet><x:sheetData><x:row r="1"><x:c r="A1" t="s"><x:v>5</x:v></x:c><x:c r="B1" t="s"><x:v>6</x:v></x:c><x:c r="C1" t="s"><x:v>7</x:v></x:c><x:c r="D1" t="s"><x:v>8</x:v></x:c><x:c r="E1" t="s"><x:v>9</x:v></x:c><x:c r="F1" t="s"><x:v>10</x:v></x:c><x:c r="G1" t="s"><x:v>11</x:v></x:c><x:c r="H1" t="s"><x:v>12</x:v></x:c><x:c r="I1" t="s"><x:v>13</x:v></x:c><x:c r="J1" t="s"><x:v>14</x:v></x:c><x:c r="K1" t="s"><x:v>15</x:v></x:c><x:c r="L1" t="s"><x:v>16</x:v></x:c><x:c r="M1" t="s"><x:v>17</x:v></x:c></x:row><x:row r="2"><x:c r="A2"><x:v>45838</x:v></x:c><x:c r="B2" t="s"><x:v>18</x:v></x:c><x:c r="C2" t="s"><x:v>19</x:v></x:c><x:c r="D2" t="s"><x:v>20</x:v></x:c><x:c r="E2" t="s"><x:v>21</x:v></x:c><x:c r="F2" t="s"><x:v>22</x:v></x:c><x:c r="G2"><x:v>40</x:v></x:c><x:c r="H2"><x:v>10</x:v></x:c><x:c r="I2"><x:v>45</x:v></x:c><x:c r="J2"><x:v>450</x:v></x:c><x:c r="K2"><x:v>410</x:v></x:c><x:c r="L2" t="s"><x:v>23</x:v></x:c><x:c r="M2" t="s"><x:v>24</x:v></x:c></x:row><x:row r="3"><x:c r="A3"><x:v>45838</x:v></x:c><x:c r="B3" t="s"><x:v>25</x:v></x:c><x:c r="C3" t="s"><x:v>26</x:v></x:c><x:c r="D3" t="s"><x:v>20</x:v></x:c><x:c r="E3" t="s"><x:v>27</x:v></x:c><x:c r="F3" t="s"><x:v>22</x:v></x:c><x:c r="G3"><x:v>90</x:v></x:c><x:c r="H3"><x:v>5</x:v></x:c><x:c r="I3"><x:v>95</x:v></x:c><x:c r="J3"><x:v>475</x:v></x:c><x:c r="K3"><x:v>432</x:v></x:c><x:c r="L3" t="s"><x:v>28</x:v></x:c><x:c r="M3" t="s"><x:v>29</x:v></x:c></x:row><x:row r="4"><x:c r="A4"><x:v>46023</x:v></x:c><x:c r="B4" t="s"><x:v>18</x:v></x:c><x:c r="C4" t="s"><x:v>19</x:v></x:c><x:c r="D4" t="s"><x:v>20</x:v></x:c><x:c r="E4" t="s"><x:v>21</x:v></x:c><x:c r="F4" t="s"><x:v>22</x:v></x:c><x:c r="G4"><x:v>40</x:v></x:c><x:c r="H4"><x:v>10</x:v></x:c><x:c r="I4"><x:v>52</x:v></x:c><x:c r="J4"><x:v>520</x:v></x:c><x:c r="K4"><x:v>470</x:v></x:c><x:c r="L4" t="s"><x:v>23</x:v></x:c><x:c r="M4" t="s"><x:v>24</x:v></x:c></x:row><x:row r="5"><x:c r="A5"><x:v>46023</x:v></x:c><x:c r="B5" t="s"><x:v>25</x:v></x:c><x:c r="C5" t="s"><x:v>26</x:v></x:c><x:c r="D5" t="s"><x:v>20</x:v></x:c><x:c r="E5" t="s"><x:v>27</x:v></x:c><x:c r="F5" t="s"><x:v>22</x:v></x:c><x:c r="G5"><x:v>90</x:v></x:c><x:c r="H5"><x:v>5</x:v></x:c><x:c r="I5"><x:v>101</x:v></x:c><x:c r="J5"><x:v>505</x:v></x:c><x:c r="K5"><x:v>456</x:v></x:c><x:c r="L5" t="s"><x:v>28</x:v></x:c><x:c r="M5" t="s"><x:v>29</x:v></x:c></x:row><x:row r="6"><x:c r="A6"><x:v>46023</x:v></x:c><x:c r="B6" t="s"><x:v>30</x:v></x:c><x:c r="C6" t="s"><x:v>31</x:v></x:c><x:c r="D6" t="s"><x:v>20</x:v></x:c><x:c r="E6" t="s"><x:v>32</x:v></x:c><x:c r="F6" t="s"><x:v>22</x:v></x:c><x:c r="G6"><x:v>300</x:v></x:c><x:c r="H6"><x:v>2</x:v></x:c><x:c r="I6"><x:v>350</x:v></x:c><x:c r="J6"><x:v>700</x:v></x:c><x:c r="K6"><x:v>633</x:v></x:c><x:c r="L6" t="s"><x:v>33</x:v></x:c><x:c r="M6" t="s"><x:v>34</x:v></x:c></x:row></x:sheetData></x:worksheet>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?><x:worksheet><x:sheetData><x:row r="1"><x:c r="A1" t="s"><x:v>5</x:v></x:c><x:c r="B1" t="s"><x:v>6</x:v></x:c><x:c r="C1" t="s"><x:v>7</x:v></x:c><x:c r="D1" t="s"><x:v>8</x:v></x:c><x:c r="E1" t="s"><x:v>9</x:v></x:c><x:c r="F1" t="s"><x:v>10</x:v></x:c><x:c r="G1" t="s"><x:v>11</x:v></x:c><x:c r="H1" t="s"><x:v>12</x:v></x:c><x:c r="I1" t="s"><x:v>13</x:v></x:c><x:c r="J1" t="s"><x:v>14</x:v></x:c><x:c r="K1" t="s"><x:v>15</x:v></x:c><x:c r="L1" t="s"><x:v>16</x:v></x:c><x:c r="M1" t="s"><x:v>17</x:v></x:c></x:row><x:row r="2"><x:c r="A2"><x:v>45838</x:v></x:c><x:c r="B2" t="s"><x:v>18</x:v></x:c><x:c r="C2" t="s"><x:v>19</x:v></x:c><x:c r="D2" t="s"><x:v>20</x:v></x:c><x:c r="E2" t="s"><x:v>21</x:v></x:c><x:c r="F2" t="s"><x:v>22</x:v></x:c><x:c r="G2"><x:v>40</x:v></x:c><x:c r="H2"><x:v>10</x:v></x:c><x:c r="I2"><x:v>45</x:v></x:c><x:c r="J2"><x:v>450</x:v></x:c><x:c r="K2"><x:v>410</x:v></x:c><x:c r="L2" t="s"><x:v>23</x:v></x:c><x:c r="M2" t="s"><x:v>24</x:v></x:c></x:row><x:row r="3"><x:c r="A3"><x:v>45838</x:v></x:c><x:c r="B3" t="s"><x:v>25</x:v></x:c><x:c r="C3" t="s"><x:v>26</x:v></x:c><x:c r="D3" t="s"><x:v>20</x:v></x:c><x:c r="E3" t="s"><x:v>27</x:v></x:c><x:c r="F3" t="s"><x:v>22</x:v></x:c><x:c r="G3"><x:v>90</x:v></x:c><x:c r="H3"><x:v>5</x:v></x:c><x:c r="I3"><x:v>95</x:v></x:c><x:c r="J3"><x:v>475</x:v></x:c><x:c r="K3"><x:v>432</x:v></x:c><x:c r="L3" t="s"><x:v>28</x:v></x:c><x:c r="M3" t="s"><x:v>29</x:v></x:c></x:row><x:row r="4"><x:c r="A4"><x:v>46023</x:v></x:c><x:c r="B4" t="s"><x:v>18</x:v></x:c><x:c r="C4" t="s"><x:v>19</x:v></x:c><x:c r="D4" t="s"><x:v>20</x:v></x:c><x:c r="E4" t="s"><x:v>21</x:v></x:c><x:c r="F4" t="s"><x:v>22</x:v></x:c><x:c r="G4"><x:v>40</x:v></x:c><x:c r="H4"><x:v>10</x:v></x:c><x:c r="I4"><x:v>52</x:v></x:c><x:c r="J4"><x:v>520</x:v></x:c><x:c r="K4"><x:v>470</x:v></x:c><x:c r="L4" t="s"><x:v>23</x:v></x:c><x:c r="M4" t="s"><x:v>24</x:v></x:c></x:row><x:row r="5"><x:c r="A5"><x:v>46023</x:v></x:c><x:c r="B5" t="s"><x:v>25</x:v></x:c><x:c r="C5" t="s"><x:v>26</x:v></x:c><x:c r="D5" t="s"><x:v>20</x:v></x:c><x:c r="E5" t="s"><x:v>27</x:v></x:c><x:c r="F5" t="s"><x:v>22</x:v></x:c><x:c r="G5"><x:v>90</x:v></x:c><x:c r="H5"><x:v>5</x:v></x:c><x:c r="I5"><x:v>101</x:v></x:c><x:c r="J5"><x:v>505</x:v></x:c><x:c r="K5"><x:v>456</x:v></x:c><x:c r="L5" t="s"><x:v>28</x:v></x:c><x:c r="M5" t="s"><x:v>29</x:v></x:c></x:row><x:row r="6"><x:c r="A6"><x:v>46023</x:v></x:c><x:c r="B6" t="s"><x:v>18</x:v></x:c><x:c r="C6" t="s"><x:v>30</x:v></x:c><x:c r="D6" t="s"><x:v>20</x:v></x:c><x:c r="E6" t="s"><x:v>31</x:v></x:c><x:c r="F6" t="s"><x:v>22</x:v></x:c><x:c r="G6"><x:v>30</x:v></x:c><x:c r="H6"><x:v>2</x:v></x:c><x:c r="I6"><x:v>52</x:v></x:c><x:c r="J6"><x:v>104</x:v></x:c><x:c r="K6"><x:v>94</x:v></x:c><x:c r="L6" t="s"><x:v>23</x:v></x:c><x:c r="M6" t="s"><x:v>24</x:v></x:c></x:row><x:row r="7"><x:c r="A7"><x:v>46023</x:v></x:c><x:c r="B7" t="s"><x:v>32</x:v></x:c><x:c r="C7" t="s"><x:v>33</x:v></x:c><x:c r="D7" t="s"><x:v>20</x:v></x:c><x:c r="E7" t="s"><x:v>34</x:v></x:c><x:c r="F7" t="s"><x:v>22</x:v></x:c><x:c r="G7"><x:v>300</x:v></x:c><x:c r="H7"><x:v>2</x:v></x:c><x:c r="I7"><x:v>350</x:v></x:c><x:c r="J7"><x:v>700</x:v></x:c><x:c r="K7"><x:v>633</x:v></x:c><x:c r="L7" t="s"><x:v>35</x:v></x:c><x:c r="M7" t="s"><x:v>36</x:v></x:c></x:row></x:sheetData></x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?><x:worksheet><x:sheetData><x:row r="1"><x:c r="A1" t="s"><x:v>35</x:v></x:c><x:c r="B1" t="s"><x:v>36</x:v></x:c><x:c r="C1" t="s"><x:v>37</x:v></x:c><x:c r="D1" t="s"><x:v>38</x:v></x:c><x:c r="E1" t="s"><x:v>39</x:v></x:c><x:c r="F1" t="s"><x:v>40</x:v></x:c><x:c r="G1" t="s"><x:v>41</x:v></x:c><x:c r="H1" t="s"><x:v>42</x:v></x:c><x:c r="I1" t="s"><x:v>43</x:v></x:c><x:c r="J1" t="s"><x:v>44</x:v></x:c><x:c r="K1" t="s"><x:v>45</x:v></x:c><x:c r="L1" t="s"><x:v>46</x:v></x:c><x:c r="M1" t="s"><x:v>47</x:v></x:c><x:c r="N1" t="s"><x:v>48</x:v></x:c><x:c r="O1" t="s"><x:v>49</x:v></x:c><x:c r="P1" t="s"><x:v>50</x:v></x:c><x:c r="Q1" t="s"><x:v>51</x:v></x:c><x:c r="R1" t="s"><x:v>52</x:v></x:c><x:c r="S1" t="s"><x:v>53</x:v></x:c><x:c r="T1" t="s"><x:v>54</x:v></x:c><x:c r="U1" t="s"><x:v>16</x:v></x:c><x:c r="V1" t="s"><x:v>17</x:v></x:c><x:c r="W1" t="s"><x:v>55</x:v></x:c></x:row><x:row r="2"><x:c r="A2" t="s"><x:v>56</x:v></x:c><x:c r="B2" t="s"><x:v>57</x:v></x:c><x:c r="C2" t="s"><x:v>20</x:v></x:c><x:c r="D2"><x:v>200</x:v></x:c><x:c r="E2"><x:v>5</x:v></x:c><x:c r="F2" t="s"><x:v>58</x:v></x:c><x:c r="G2" t="s"><x:v>59</x:v></x:c><x:c r="H2" t="s"><x:v>60</x:v></x:c><x:c r="I2"><x:v>0</x:v></x:c><x:c r="J2"><x:v>0</x:v></x:c><x:c r="K2"><x:v>40</x:v></x:c><x:c r="L2"><x:v>36</x:v></x:c><x:c r="M2"><x:v>1</x:v></x:c><x:c r="N2"><x:v>1</x:v></x:c><x:c r="O2"><x:v>40</x:v></x:c><x:c r="P2"><x:v>48</x:v></x:c><x:c r="Q2"><x:v>0</x:v></x:c><x:c r="R2"><x:v>0</x:v></x:c><x:c r="S2"><x:v>0</x:v></x:c><x:c r="U2" t="s"><x:v>61</x:v></x:c><x:c r="V2" t="s"><x:v>24</x:v></x:c></x:row><x:row r="3"><x:c r="A3" t="s"><x:v>62</x:v></x:c><x:c r="B3" t="s"><x:v>63</x:v></x:c><x:c r="C3" t="s"><x:v>20</x:v></x:c><x:c r="D3"><x:v>100</x:v></x:c><x:c r="E3"><x:v>1</x:v></x:c><x:c r="F3" t="s"><x:v>64</x:v></x:c><x:c r="G3" t="s"><x:v>65</x:v></x:c><x:c r="H3" t="s"><x:v>66</x:v></x:c><x:c r="I3"><x:v>0</x:v></x:c><x:c r="J3"><x:v>0</x:v></x:c><x:c r="K3"><x:v>5</x:v></x:c><x:c r="L3"><x:v>4</x:v></x:c><x:c r="M3"><x:v>1</x:v></x:c><x:c r="N3"><x:v>1</x:v></x:c><x:c r="O3"><x:v>100</x:v></x:c><x:c r="P3"><x:v>105</x:v></x:c><x:c r="Q3"><x:v>0</x:v></x:c><x:c r="R3"><x:v>0</x:v></x:c><x:c r="S3"><x:v>0</x:v></x:c><x:c r="U3" t="s"><x:v>67</x:v></x:c><x:c r="V3" t="s"><x:v>68</x:v></x:c></x:row></x:sheetData></x:worksheet>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?><x:worksheet><x:sheetData><x:row r="1"><x:c r="A1" t="s"><x:v>37</x:v></x:c><x:c r="B1" t="s"><x:v>38</x:v></x:c><x:c r="C1" t="s"><x:v>39</x:v></x:c><x:c r="D1" t="s"><x:v>40</x:v></x:c><x:c r="E1" t="s"><x:v>41</x:v></x:c><x:c r="F1" t="s"><x:v>42</x:v></x:c><x:c r="G1" t="s"><x:v>43</x:v></x:c><x:c r="H1" t="s"><x:v>44</x:v></x:c><x:c r="I1" t="s"><x:v>45</x:v></x:c><x:c r="J1" t="s"><x:v>46</x:v></x:c><x:c r="K1" t="s"><x:v>47</x:v></x:c><x:c r="L1" t="s"><x:v>48</x:v></x:c><x:c r="M1" t="s"><x:v>49</x:v></x:c><x:c r="N1" t="s"><x:v>50</x:v></x:c><x:c r="O1" t="s"><x:v>51</x:v></x:c><x:c r="P1" t="s"><x:v>52</x:v></x:c><x:c r="Q1" t="s"><x:v>53</x:v></x:c><x:c r="R1" t="s"><x:v>54</x:v></x:c><x:c r="S1" t="s"><x:v>55</x:v></x:c><x:c r="T1" t="s"><x:v>56</x:v></x:c><x:c r="U1" t="s"><x:v>16</x:v></x:c><x:c r="V1" t="s"><x:v>17</x:v></x:c><x:c r="W1" t="s"><x:v>57</x:v></x:c></x:row><x:row r="2"><x:c r="A2" t="s"><x:v>58</x:v></x:c><x:c r="B2" t="s"><x:v>59</x:v></x:c><x:c r="C2" t="s"><x:v>20</x:v></x:c><x:c r="D2"><x:v>200</x:v></x:c><x:c r="E2"><x:v>5</x:v></x:c><x:c r="F2" t="s"><x:v>60</x:v></x:c><x:c r="G2" t="s"><x:v>61</x:v></x:c><x:c r="H2" t="s"><x:v>62</x:v></x:c><x:c r="I2"><x:v>0</x:v></x:c><x:c r="J2"><x:v>0</x:v></x:c><x:c r="K2"><x:v>40</x:v></x:c><x:c r="L2"><x:v>36</x:v></x:c><x:c r="M2"><x:v>1</x:v></x:c><x:c r="N2"><x:v>1</x:v></x:c><x:c r="O2"><x:v>40</x:v></x:c><x:c r="P2"><x:v>48</x:v></x:c><x:c r="Q2"><x:v>0</x:v></x:c><x:c r="R2"><x:v>0</x:v></x:c><x:c r="S2"><x:v>0</x:v></x:c><x:c r="U2" t="s"><x:v>63</x:v></x:c><x:c r="V2" t="s"><x:v>24</x:v></x:c></x:row><x:row r="3"><x:c r="A3" t="s"><x:v>64</x:v></x:c><x:c r="B3" t="s"><x:v>65</x:v></x:c><x:c r="C3" t="s"><x:v>20</x:v></x:c><x:c r="D3"><x:v>100</x:v></x:c><x:c r="E3"><x:v>1</x:v></x:c><x:c r="F3" t="s"><x:v>66</x:v></x:c><x:c r="G3" t="s"><x:v>67</x:v></x:c><x:c r="H3" t="s"><x:v>68</x:v></x:c><x:c r="I3"><x:v>0</x:v></x:c><x:c r="J3"><x:v>0</x:v></x:c><x:c r="K3"><x:v>5</x:v></x:c><x:c r="L3"><x:v>4</x:v></x:c><x:c r="M3"><x:v>1</x:v></x:c><x:c r="N3"><x:v>1</x:v></x:c><x:c r="O3"><x:v>100</x:v></x:c><x:c r="P3"><x:v>105</x:v></x:c><x:c r="Q3"><x:v>0</x:v></x:c><x:c r="R3"><x:v>0</x:v></x:c><x:c r="S3"><x:v>0</x:v></x:c><x:c r="U3" t="s"><x:v>69</x:v></x:c><x:c r="V3" t="s"><x:v>70</x:v></x:c></x:row></x:sheetData></x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?><x:worksheet><x:sheetData><x:row r="1"><x:c r="A1" t="s"><x:v>69</x:v></x:c><x:c r="B1" t="s"><x:v>16</x:v></x:c><x:c r="C1" t="s"><x:v>70</x:v></x:c><x:c r="D1" t="s"><x:v>38</x:v></x:c><x:c r="E1" t="s"><x:v>39</x:v></x:c><x:c r="F1" t="s"><x:v>71</x:v></x:c><x:c r="G1" t="s"><x:v>72</x:v></x:c><x:c r="H1" t="s"><x:v>73</x:v></x:c><x:c r="I1" t="s"><x:v>35</x:v></x:c><x:c r="J1" t="s"><x:v>74</x:v></x:c><x:c r="K1" t="s"><x:v>75</x:v></x:c></x:row><x:row r="2"><x:c r="A2" t="s"><x:v>76</x:v></x:c><x:c r="B2" t="s"><x:v>77</x:v></x:c><x:c r="C2" t="s"><x:v>78</x:v></x:c><x:c r="D2"><x:v>5000</x:v></x:c><x:c r="E2" t="s"><x:v>34</x:v></x:c><x:c r="F2"><x:v>0</x:v></x:c><x:c r="G2"><x:v>0</x:v></x:c><x:c r="H2"><x:v>5000</x:v></x:c><x:c r="J2" t="s"><x:v>34</x:v></x:c><x:c r="K2"><x:v>0</x:v></x:c></x:row><x:row r="3"><x:c r="A3" t="s"><x:v>58</x:v></x:c><x:c r="B3" t="s"><x:v>79</x:v></x:c><x:c r="C3" t="s"><x:v>80</x:v></x:c><x:c r="D3"><x:v>200</x:v></x:c><x:c r="E3"><x:v>5</x:v></x:c><x:c r="F3"><x:v>0</x:v></x:c><x:c r="G3"><x:v>0</x:v></x:c><x:c r="H3"><x:v>4800</x:v></x:c><x:c r="I3" t="s"><x:v>56</x:v></x:c><x:c r="J3" t="s"><x:v>61</x:v></x:c><x:c r="K3"><x:v>0</x:v></x:c></x:row><x:row r="4"><x:c r="A4" t="s"><x:v>21</x:v></x:c><x:c r="B4" t="s"><x:v>79</x:v></x:c><x:c r="C4" t="s"><x:v>80</x:v></x:c><x:c r="D4"><x:v>400</x:v></x:c><x:c r="E4"><x:v>10</x:v></x:c><x:c r="F4"><x:v>0</x:v></x:c><x:c r="G4"><x:v>0</x:v></x:c><x:c r="H4"><x:v>4600</x:v></x:c><x:c r="I4" t="s"><x:v>19</x:v></x:c><x:c r="J4" t="s"><x:v>61</x:v></x:c><x:c r="K4"><x:v>0</x:v></x:c></x:row><x:row r="5"><x:c r="A5" t="s"><x:v>27</x:v></x:c><x:c r="B5" t="s"><x:v>79</x:v></x:c><x:c r="C5" t="s"><x:v>81</x:v></x:c><x:c r="D5"><x:v>450</x:v></x:c><x:c r="E5"><x:v>5</x:v></x:c><x:c r="F5"><x:v>0</x:v></x:c><x:c r="G5"><x:v>0</x:v></x:c><x:c r="H5"><x:v>4150</x:v></x:c><x:c r="I5" t="s"><x:v>26</x:v></x:c><x:c r="J5" t="s"><x:v>28</x:v></x:c><x:c r="K5"><x:v>0</x:v></x:c></x:row><x:row r="6"><x:c r="A6" t="s"><x:v>32</x:v></x:c><x:c r="B6" t="s"><x:v>79</x:v></x:c><x:c r="C6" t="s"><x:v>82</x:v></x:c><x:c r="D6"><x:v>600</x:v></x:c><x:c r="E6"><x:v>2</x:v></x:c><x:c r="F6"><x:v>0</x:v></x:c><x:c r="G6"><x:v>0</x:v></x:c><x:c r="H6"><x:v>3550</x:v></x:c><x:c r="I6" t="s"><x:v>31</x:v></x:c><x:c r="J6" t="s"><x:v>83</x:v></x:c><x:c r="K6"><x:v>0</x:v></x:c></x:row><x:row r="7"><x:c r="A7" t="s"><x:v>84</x:v></x:c><x:c r="B7" t="s"><x:v>79</x:v></x:c><x:c r="C7" t="s"><x:v>85</x:v></x:c><x:c r="D7"><x:v>60</x:v></x:c><x:c r="E7"><x:v>3</x:v></x:c><x:c r="F7"><x:v>0</x:v></x:c><x:c r="G7"><x:v>0</x:v></x:c><x:c r="H7"><x:v>3490</x:v></x:c><x:c r="I7" t="s"><x:v>86</x:v></x:c><x:c r="J7" t="s"><x:v>67</x:v></x:c><x:c r="K7"><x:v>0</x:v></x:c></x:row><x:row r="8"><x:c r="A8" t="s"><x:v>87</x:v></x:c><x:c r="B8" t="s"><x:v>88</x:v></x:c><x:c r="C8" t="s"><x:v>85</x:v></x:c><x:c r="D8"><x:v>-2</x:v></x:c><x:c r="E8" t="s"><x:v>34</x:v></x:c><x:c r="F8"><x:v>0</x:v></x:c><x:c r="G8"><x:v>0</x:v></x:c><x:c r="H8"><x:v>3488</x:v></x:c><x:c r="I8" t="s"><x:v>86</x:v></x:c><x:c r="J8" t="s"><x:v>67</x:v></x:c><x:c r="K8"><x:v>0</x:v></x:c></x:row><x:row r="9"><x:c r="A9" t="s"><x:v>21</x:v></x:c><x:c r="B9" t="s"><x:v>89</x:v></x:c><x:c r="C9" t="s"><x:v>90</x:v></x:c><x:c r="D9"><x:v>-4</x:v></x:c><x:c r="E9" t="s"><x:v>34</x:v></x:c><x:c r="F9"><x:v>0</x:v></x:c><x:c r="G9"><x:v>0</x:v></x:c><x:c r="H9"><x:v>4596</x:v></x:c><x:c r="I9" t="s"><x:v>19</x:v></x:c><x:c r="J9" t="s"><x:v>61</x:v></x:c><x:c r="K9"><x:v>0</x:v></x:c></x:row><x:row r="10"><x:c r="A10" t="s"><x:v>91</x:v></x:c><x:c r="B10" t="s"><x:v>89</x:v></x:c><x:c r="C10" t="s"><x:v>92</x:v></x:c><x:c r="D10"><x:v>-3</x:v></x:c><x:c r="E10" t="s"><x:v>34</x:v></x:c><x:c r="F10"><x:v>0</x:v></x:c><x:c r="G10"><x:v>0</x:v></x:c><x:c r="H10"><x:v>4593</x:v></x:c><x:c r="I10" t="s"><x:v>56</x:v></x:c><x:c r="J10" t="s"><x:v>61</x:v></x:c><x:c r="K10"><x:v>0</x:v></x:c></x:row><x:row r="11"><x:c r="A11" t="s"><x:v>84</x:v></x:c><x:c r="B11" t="s"><x:v>89</x:v></x:c><x:c r="C11" t="s"><x:v>90</x:v></x:c><x:c r="D11"><x:v>-1</x:v></x:c><x:c r="E11" t="s"><x:v>34</x:v></x:c><x:c r="F11"><x:v>0</x:v></x:c><x:c r="G11"><x:v>0</x:v></x:c><x:c r="H11"><x:v>3489</x:v></x:c><x:c r="I11" t="s"><x:v>86</x:v></x:c><x:c r="J11" t="s"><x:v>67</x:v></x:c><x:c r="K11"><x:v>0</x:v></x:c></x:row><x:row r="12"><x:c r="A12" t="s"><x:v>93</x:v></x:c><x:c r="B12" t="s"><x:v>94</x:v></x:c><x:c r="C12" t="s"><x:v>34</x:v></x:c><x:c r="D12"><x:v>1.5</x:v></x:c><x:c r="E12" t="s"><x:v>34</x:v></x:c><x:c r="F12"><x:v>1.5</x:v></x:c><x:c r="G12"><x:v>0</x:v></x:c><x:c r="H12"><x:v>4601</x:v></x:c><x:c r="J12" t="s"><x:v>34</x:v></x:c><x:c r="K12"><x:v>0</x:v></x:c></x:row><x:row r="13"><x:c r="A13" t="s"><x:v>95</x:v></x:c><x:c r="B13" t="s"><x:v>96</x:v></x:c><x:c r="C13" t="s"><x:v>97</x:v></x:c><x:c r="D13"><x:v>0</x:v></x:c><x:c r="E13" t="s"><x:v>34</x:v></x:c><x:c r="F13"><x:v>0</x:v></x:c><x:c r="G13"><x:v>0</x:v></x:c><x:c r="H13"><x:v>0</x:v></x:c><x:c r="I13" t="s"><x:v>19</x:v></x:c><x:c r="J13" t="s"><x:v>61</x:v></x:c><x:c r="K13"><x:v>0</x:v></x:c></x:row><x:row r="14"><x:c r="A14" t="s"><x:v>98</x:v></x:c><x:c r="B14" t="s"><x:v>79</x:v></x:c><x:c r="C14" t="s"><x:v>99</x:v></x:c><x:c r="D14"><x:v>300</x:v></x:c><x:c r="E14"><x:v>4</x:v></x:c><x:c r="F14"><x:v>0</x:v></x:c><x:c r="G14"><x:v>0</x:v></x:c><x:c r="H14"><x:v>3190</x:v></x:c><x:c r="I14" t="s"><x:v>100</x:v></x:c><x:c r="J14" t="s"><x:v>61</x:v></x:c><x:c r="K14"><x:v>0</x:v></x:c></x:row></x:sheetData></x:worksheet>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?><x:worksheet><x:sheetData><x:row r="1"><x:c r="A1" t="s"><x:v>71</x:v></x:c><x:c r="B1" t="s"><x:v>16</x:v></x:c><x:c r="C1" t="s"><x:v>72</x:v></x:c><x:c r="D1" t="s"><x:v>40</x:v></x:c><x:c r="E1" t="s"><x:v>41</x:v></x:c><x:c r="F1" t="s"><x:v>73</x:v></x:c><x:c r="G1" t="s"><x:v>74</x:v></x:c><x:c r="H1" t="s"><x:v>75</x:v></x:c><x:c r="I1" t="s"><x:v>37</x:v></x:c><x:c r="J1" t="s"><x:v>76</x:v></x:c><x:c r="K1" t="s"><x:v>77</x:v></x:c></x:row><x:row r="2"><x:c r="A2" t="s"><x:v>78</x:v></x:c><x:c r="B2" t="s"><x:v>79</x:v></x:c><x:c r="C2" t="s"><x:v>80</x:v></x:c><x:c r="D2"><x:v>5000</x:v></x:c><x:c r="E2" t="s"><x:v>36</x:v></x:c><x:c r="F2"><x:v>0</x:v></x:c><x:c r="G2"><x:v>0</x:v></x:c><x:c r="H2"><x:v>5000</x:v></x:c><x:c r="J2" t="s"><x:v>36</x:v></x:c><x:c r="K2"><x:v>0</x:v></x:c></x:row><x:row r="3"><x:c r="A3" t="s"><x:v>60</x:v></x:c><x:c r="B3" t="s"><x:v>81</x:v></x:c><x:c r="C3" t="s"><x:v>82</x:v></x:c><x:c r="D3"><x:v>200</x:v></x:c><x:c r="E3"><x:v>5</x:v></x:c><x:c r="F3"><x:v>0</x:v></x:c><x:c r="G3"><x:v>0</x:v></x:c><x:c r="H3"><x:v>4800</x:v></x:c><x:c r="I3" t="s"><x:v>58</x:v></x:c><x:c r="J3" t="s"><x:v>63</x:v></x:c><x:c r="K3"><x:v>0</x:v></x:c></x:row><x:row r="4"><x:c r="A4" t="s"><x:v>21</x:v></x:c><x:c r="B4" t="s"><x:v>81</x:v></x:c><x:c r="C4" t="s"><x:v>82</x:v></x:c><x:c r="D4"><x:v>400</x:v></x:c><x:c r="E4"><x:v>10</x:v></x:c><x:c r="F4"><x:v>0</x:v></x:c><x:c r="G4"><x:v>0</x:v></x:c><x:c r="H4"><x:v>4600</x:v></x:c><x:c r="I4" t="s"><x:v>19</x:v></x:c><x:c r="J4" t="s"><x:v>63</x:v></x:c><x:c r="K4"><x:v>0</x:v></x:c></x:row><x:row r="5"><x:c r="A5" t="s"><x:v>27</x:v></x:c><x:c r="B5" t="s"><x:v>81</x:v></x:c><x:c r="C5" t="s"><x:v>83</x:v></x:c><x:c r="D5"><x:v>450</x:v></x:c><x:c r="E5"><x:v>5</x:v></x:c><x:c r="F5"><x:v>0</x:v></x:c><x:c r="G5"><x:v>0</x:v></x:c><x:c r="H5"><x:v>4150</x:v></x:c><x:c r="I5" t="s"><x:v>26</x:v></x:c><x:c r="J5" t="s"><x:v>28</x:v></x:c><x:c r="K5"><x:v>0</x:v></x:c></x:row><x:row r="6"><x:c r="A6" t="s"><x:v>34</x:v></x:c><x:c r="B6" t="s"><x:v>81</x:v></x:c><x:c r="C6" t="s"><x:v>84</x:v></x:c><x:c r="D6"><x:v>600</x:v></x:c><x:c r="E6"><x:v>2</x:v></x:c><x:c r="F6"><x:v>0</x:v></x:c><x:c r="G6"><x:v>0</x:v></x:c><x:c r="H6"><x:v>3550</x:v></x:c><x:c r="I6" t="s"><x:v>33</x:v></x:c><x:c r="J6" t="s"><x:v>85</x:v></x:c><x:c r="K6"><x:v>0</x:v></x:c></x:row><x:row r="7"><x:c r="A7" t="s"><x:v>86</x:v></x:c><x:c r="B7" t="s"><x:v>81</x:v></x:c><x:c r="C7" t="s"><x:v>87</x:v></x:c><x:c r="D7"><x:v>60</x:v></x:c><x:c r="E7"><x:v>3</x:v></x:c><x:c r="F7"><x:v>0</x:v></x:c><x:c r="G7"><x:v>0</x:v></x:c><x:c r="H7"><x:v>3490</x:v></x:c><x:c r="I7" t="s"><x:v>88</x:v></x:c><x:c r="J7" t="s"><x:v>69</x:v></x:c><x:c r="K7"><x:v>0</x:v></x:c></x:row><x:row r="8"><x:c r="A8" t="s"><x:v>89</x:v></x:c><x:c r="B8" t="s"><x:v>90</x:v></x:c><x:c r="C8" t="s"><x:v>87</x:v></x:c><x:c r="D8"><x:v>-2</x:v></x:c><x:c r="E8" t="s"><x:v>36</x:v></x:c><x:c r="F8"><x:v>0</x:v></x:c><x:c r="G8"><x:v>0</x:v></x:c><x:c r="H8"><x:v>3488</x:v></x:c><x:c r="I8" t="s"><x:v>88</x:v></x:c><x:c r="J8" t="s"><x:v>69</x:v></x:c><x:c r="K8"><x:v>0</x:v></x:c></x:row><x:row r="9"><x:c r="A9" t="s"><x:v>21</x:v></x:c><x:c r="B9" t="s"><x:v>91</x:v></x:c><x:c r="C9" t="s"><x:v>92</x:v></x:c><x:c r="D9"><x:v>-4</x:v></x:c><x:c r="E9" t="s"><x:v>36</x:v></x:c><x:c r="F9"><x:v>0</x:v></x:c><x:c r="G9"><x:v>0</x:v></x:c><x:c r="H9"><x:v>4596</x:v></x:c><x:c r="I9" t="s"><x:v>19</x:v></x:c><x:c r="J9" t="s"><x:v>63</x:v></x:c><x:c r="K9"><x:v>0</x:v></x:c></x:row><x:row r="10"><x:c r="A10" t="s"><x:v>93</x:v></x:c><x:c r="B10" t="s"><x:v>91</x:v></x:c><x:c r="C10" t="s"><x:v>94</x:v></x:c><x:c r="D10"><x:v>-3</x:v></x:c><x:c r="E10" t="s"><x:v>36</x:v></x:c><x:c r="F10"><x:v>0</x:v></x:c><x:c r="G10"><x:v>0</x:v></x:c><x:c r="H10"><x:v>4593</x:v></x:c><x:c r="I10" t="s"><x:v>58</x:v></x:c><x:c r="J10" t="s"><x:v>63</x:v></x:c><x:c r="K10"><x:v>0</x:v></x:c></x:row><x:row r="11"><x:c r="A11" t="s"><x:v>86</x:v></x:c><x:c r="B11" t="s"><x:v>91</x:v></x:c><x:c r="C11" t="s"><x:v>92</x:v></x:c><x:c r="D11"><x:v>-1</x:v></x:c><x:c r="E11" t="s"><x:v>36</x:v></x:c><x:c r="F11"><x:v>0</x:v></x:c><x:c r="G11"><x:v>0</x:v></x:c><x:c r="H11"><x:v>3489</x:v></x:c><x:c r="I11" t="s"><x:v>88</x:v></x:c><x:c r="J11" t="s"><x:v>69</x:v></x:c><x:c r="K11"><x:v>0</x:v></x:c></x:row><x:row r="12"><x:c r="A12" t="s"><x:v>95</x:v></x:c><x:c r="B12" t="s"><x:v>96</x:v></x:c><x:c r="C12" t="s"><x:v>36</x:v></x:c><x:c r="D12"><x:v>1.5</x:v></x:c><x:c r="E12" t="s"><x:v>36</x:v></x:c><x:c r="F12"><x:v>1.5</x:v></x:c><x:c r="G12"><x:v>0</x:v></x:c><x:c r="H12"><x:v>4601</x:v></x:c><x:c r="J12" t="s"><x:v>36</x:v></x:c><x:c r="K12"><x:v>0</x:v></x:c></x:row><x:row r="13"><x:c r="A13" t="s"><x:v>97</x:v></x:c><x:c r="B13" t="s"><x:v>98</x:v></x:c><x:c r="C13" t="s"><x:v>99</x:v></x:c><x:c r="D13"><x:v>0</x:v></x:c><x:c r="E13" t="s"><x:v>36</x:v></x:c><x:c r="F13"><x:v>0</x:v></x:c><x:c r="G13"><x:v>0</x:v></x:c><x:c r="H13"><x:v>0</x:v></x:c><x:c r="I13" t="s"><x:v>19</x:v></x:c><x:c r="J13" t="s"><x:v>63</x:v></x:c><x:c r="K13"><x:v>0</x:v></x:c></x:row><x:row r="14"><x:c r="A14" t="s"><x:v>100</x:v></x:c><x:c r="B14" t="s"><x:v>81</x:v></x:c><x:c r="C14" t="s"><x:v>101</x:v></x:c><x:c r="D14"><x:v>300</x:v></x:c><x:c r="E14"><x:v>4</x:v></x:c><x:c r="F14"><x:v>0</x:v></x:c><x:c r="G14"><x:v>0</x:v></x:c><x:c r="H14"><x:v>3190</x:v></x:c><x:c r="I14" t="s"><x:v>102</x:v></x:c><x:c r="J14" t="s"><x:v>63</x:v></x:c><x:c r="K14"><x:v>0</x:v></x:c></x:row></x:sheetData></x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?><x:worksheet><x:sheetData><x:row r="1"><x:c r="A1" t="s"><x:v>103</x:v></x:c><x:c r="B1" t="s"><x:v>104</x:v></x:c><x:c r="C1" t="s"><x:v>105</x:v></x:c><x:c r="D1" t="s"><x:v>106</x:v></x:c><x:c r="E1" t="s"><x:v>107</x:v></x:c><x:c r="F1" t="s"><x:v>108</x:v></x:c><x:c r="G1" t="s"><x:v>109</x:v></x:c><x:c r="H1" t="s"><x:v>110</x:v></x:c><x:c r="I1" t="s"><x:v>111</x:v></x:c><x:c r="J1" t="s"><x:v>112</x:v></x:c><x:c r="K1" t="s"><x:v>113</x:v></x:c><x:c r="L1" t="s"><x:v>37</x:v></x:c><x:c r="M1" t="s"><x:v>16</x:v></x:c><x:c r="N1" t="s"><x:v>17</x:v></x:c></x:row><x:row r="2"><x:c r="A2" t="s"><x:v>114</x:v></x:c><x:c r="B2" t="s"><x:v>18</x:v></x:c><x:c r="C2"><x:v>0.5</x:v></x:c><x:c r="D2"><x:v>0</x:v></x:c><x:c r="F2" t="s"><x:v>36</x:v></x:c><x:c r="G2" t="s"><x:v>36</x:v></x:c><x:c r="H2"><x:v>0.45</x:v></x:c><x:c r="I2" t="s"><x:v>115</x:v></x:c><x:c r="J2"><x:v>0.08</x:v></x:c><x:c r="K2"><x:v>0.075</x:v></x:c><x:c r="L2" t="s"><x:v>19</x:v></x:c><x:c r="M2" t="s"><x:v>23</x:v></x:c><x:c r="N2" t="s"><x:v>24</x:v></x:c></x:row><x:row r="3"><x:c r="A3" t="s"><x:v>116</x:v></x:c><x:c r="B3" t="s"><x:v>18</x:v></x:c><x:c r="C3"><x:v>0.2</x:v></x:c><x:c r="D3"><x:v>0</x:v></x:c><x:c r="F3" t="s"><x:v>36</x:v></x:c><x:c r="G3" t="s"><x:v>36</x:v></x:c><x:c r="H3"><x:v>0.18</x:v></x:c><x:c r="I3" t="s"><x:v>117</x:v></x:c><x:c r="J3"><x:v>0.07</x:v></x:c><x:c r="K3"><x:v>0.06</x:v></x:c><x:c r="L3" t="s"><x:v>30</x:v></x:c><x:c r="M3" t="s"><x:v>23</x:v></x:c><x:c r="N3" t="s"><x:v>24</x:v></x:c></x:row><x:row r="4"><x:c r="A4" t="s"><x:v>118</x:v></x:c><x:c r="B4" t="s"><x:v>119</x:v></x:c><x:c r="C4"><x:v>0.1</x:v></x:c><x:c r="D4"><x:v>0</x:v></x:c><x:c r="F4" t="s"><x:v>36</x:v></x:c><x:c r="G4" t="s"><x:v>36</x:v></x:c><x:c r="H4"><x:v>0.09</x:v></x:c><x:c r="I4" t="s"><x:v>120</x:v></x:c><x:c r="J4"><x:v>0</x:v></x:c><x:c r="K4"><x:v>0</x:v></x:c><x:c r="L4" t="s"><x:v>121</x:v></x:c><x:c r="M4" t="s"><x:v>23</x:v></x:c><x:c r="N4" t="s"><x:v>122</x:v></x:c></x:row></x:sheetData></x:worksheet>
 </file>
--- a/tests/fixtures/etoro/releve-demo.xlsx
+++ b/tests/fixtures/etoro/releve-demo.xlsx
@@ -11,7 +11,7 @@
 </x:workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?><x:sst count="123"><x:si><x:r><x:t xml:space="preserve">No</x:t></x:r><x:r><x:t xml:space="preserve">m</x:t></x:r></x:si><x:si><x:t>Totaux</x:t></x:si><x:si><x:t>Deposits</x:t></x:si><x:si><x:t>Récapitulatif du compte (USD)</x:t></x:si><x:si><x:t>Total&#10; en (USD)</x:t></x:si><x:si><x:t>Snapshot Date</x:t></x:si><x:si><x:t>Asset</x:t></x:si><x:si><x:t>Position ID</x:t></x:si><x:si><x:t>Direction</x:t></x:si><x:si><x:t>Open Date</x:t></x:si><x:si><x:t>Leverage</x:t></x:si><x:si><x:t>Open Rate</x:t></x:si><x:si><x:t>Units</x:t></x:si><x:si><x:t>Current Rate</x:t></x:si><x:si><x:t>Value in USD</x:t></x:si><x:si><x:t>Value in EUR</x:t></x:si><x:si><x:t>Type</x:t></x:si><x:si><x:t>ISIN</x:t></x:si><x:si><x:t>Demo Industries Inc.</x:t></x:si><x:si><x:t>p-101</x:t></x:si><x:si><x:t>Long</x:t></x:si><x:si><x:t>12/02/2025 09:30:00</x:t></x:si><x:si><x:t>X1</x:t></x:si><x:si><x:t>Stocks</x:t></x:si><x:si><x:t>XX0000000001</x:t></x:si><x:si><x:t>Indice Monde UCITS ETF</x:t></x:si><x:si><x:t>p-102</x:t></x:si><x:si><x:t>03/03/2025 11:00:00</x:t></x:si><x:si><x:t>ETF</x:t></x:si><x:si><x:t>XX0000000002</x:t></x:si><x:si><x:t>p-901</x:t></x:si><x:si><x:t>18/11/2024 09:00:00</x:t></x:si><x:si><x:t>Bitcoin</x:t></x:si><x:si><x:t>p-103</x:t></x:si><x:si><x:t>20/05/2025 16:45:00</x:t></x:si><x:si><x:t>Crypto Currencies</x:t></x:si><x:si><x:t>-</x:t></x:si><x:si><x:t>Identifiant de position</x:t></x:si><x:si><x:t>Action</x:t></x:si><x:si><x:t>Long / Short</x:t></x:si><x:si><x:t>Montant</x:t></x:si><x:si><x:t>Unités</x:t></x:si><x:si><x:t>Date d'ouverture</x:t></x:si><x:si><x:t>Date de clôture</x:t></x:si><x:si><x:t>Effet de levier</x:t></x:si><x:si><x:t>Frais de spread (USD)</x:t></x:si><x:si><x:t>Spread du marché (USD)</x:t></x:si><x:si><x:t>Profit (USD)</x:t></x:si><x:si><x:t>Profit (EUR)</x:t></x:si><x:si><x:t>Taux de change à l'ouverture (USD)</x:t></x:si><x:si><x:t>Taux de change à la clôture (USD)</x:t></x:si><x:si><x:t>Taux à l'ouverture</x:t></x:si><x:si><x:t>Taux à la clôture</x:t></x:si><x:si><x:t>Taux Take Profit</x:t></x:si><x:si><x:t>Taux Stop Loss</x:t></x:si><x:si><x:t>Frais overnight et dividendes</x:t></x:si><x:si><x:t>Copie de</x:t></x:si><x:si><x:t>Remarques</x:t></x:si><x:si><x:t>p-201</x:t></x:si><x:si><x:t>Demo Industries Inc. (DEMO)</x:t></x:si><x:si><x:t>05/01/2025 10:00:00</x:t></x:si><x:si><x:t>10/04/2025 15:00:00</x:t></x:si><x:si><x:t>1</x:t></x:si><x:si><x:t>Actions</x:t></x:si><x:si><x:t>p-202</x:t></x:si><x:si><x:t>Pétrole (OIL)</x:t></x:si><x:si><x:t>06/01/2025 10:00:00</x:t></x:si><x:si><x:t>11/04/2025 15:00:00</x:t></x:si><x:si><x:t>2</x:t></x:si><x:si><x:t>CFD</x:t></x:si><x:si><x:t>XX0000000005</x:t></x:si><x:si><x:t>Date</x:t></x:si><x:si><x:t>Détails</x:t></x:si><x:si><x:t>Variation Fonds propres réalisés</x:t></x:si><x:si><x:t>Équité réalisée</x:t></x:si><x:si><x:t>Solde</x:t></x:si><x:si><x:t>Type d'actif</x:t></x:si><x:si><x:t>NWA (fonds non retirables)</x:t></x:si><x:si><x:t>01/02/2025 08:00:00</x:t></x:si><x:si><x:t>Dépôt</x:t></x:si><x:si><x:t>Virement</x:t></x:si><x:si><x:t>Position ouverte</x:t></x:si><x:si><x:t>DEMO/USD</x:t></x:si><x:si><x:t>IDX.DE/EUR</x:t></x:si><x:si><x:t>BTC/USD</x:t></x:si><x:si><x:t>Crypto-monnaies</x:t></x:si><x:si><x:t>02/06/2025 10:00:00</x:t></x:si><x:si><x:t>OIL/USD</x:t></x:si><x:si><x:t>p-104</x:t></x:si><x:si><x:t>15/07/2025 12:00:00</x:t></x:si><x:si><x:t>Frais overnight</x:t></x:si><x:si><x:t>Spread d’ouverture et de clôture</x:t></x:si><x:si><x:t>À l'ouverture</x:t></x:si><x:si><x:t>18/08/2025 15:00:00</x:t></x:si><x:si><x:t>À la fermeture</x:t></x:si><x:si><x:t>01/03/2025 09:00:00</x:t></x:si><x:si><x:t>Paiement des intérêts</x:t></x:si><x:si><x:t>30/06/2026 06:00:00</x:t></x:si><x:si><x:t>corp action: Split</x:t></x:si><x:si><x:t>DEMO/USD 1:2</x:t></x:si><x:si><x:t>14/04/2026 14:20:00</x:t></x:si><x:si><x:t>NEWCO/USD</x:t></x:si><x:si><x:t>p-301</x:t></x:si><x:si><x:t>Date du paiement</x:t></x:si><x:si><x:t>Nom de l'instrument</x:t></x:si><x:si><x:t>Dividende net reçu (USD)</x:t></x:si><x:si><x:t>Net dividends</x:t></x:si><x:si><x:t>Currency</x:t></x:si><x:si><x:t>Affranchi/Non affranchi</x:t></x:si><x:si><x:t>Crédits d’affranchissement (AUD)</x:t></x:si><x:si><x:t>Dividende net reçu (EUR)</x:t></x:si><x:si><x:t>Taux de retenue à la source (%)</x:t></x:si><x:si><x:t>Montant du prélèvement à la source (USD)</x:t></x:si><x:si><x:t>Montant du prélèvement à la source (EUR)</x:t></x:si><x:si><x:t>15/04/2025</x:t></x:si><x:si><x:t>15 %</x:t></x:si><x:si><x:t>20/05/2025</x:t></x:si><x:si><x:t>25 %</x:t></x:si><x:si><x:t>10/06/2025</x:t></x:si><x:si><x:t>Vanished Corp.</x:t></x:si><x:si><x:t>0 %</x:t></x:si><x:si><x:t>p-999</x:t></x:si><x:si><x:t>XX0000000009</x:t></x:si></x:sst>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?><x:sst count="125"><x:si><x:r><x:t xml:space="preserve">No</x:t></x:r><x:r><x:t xml:space="preserve">m</x:t></x:r></x:si><x:si><x:t>Totaux</x:t></x:si><x:si><x:t>Deposits</x:t></x:si><x:si><x:t>Récapitulatif du compte (USD)</x:t></x:si><x:si><x:t>Total&#10; en (USD)</x:t></x:si><x:si><x:t>Snapshot Date</x:t></x:si><x:si><x:t>Asset</x:t></x:si><x:si><x:t>Position ID</x:t></x:si><x:si><x:t>Direction</x:t></x:si><x:si><x:t>Open Date</x:t></x:si><x:si><x:t>Leverage</x:t></x:si><x:si><x:t>Open Rate</x:t></x:si><x:si><x:t>Units</x:t></x:si><x:si><x:t>Current Rate</x:t></x:si><x:si><x:t>Value in USD</x:t></x:si><x:si><x:t>Value in EUR</x:t></x:si><x:si><x:t>Type</x:t></x:si><x:si><x:t>ISIN</x:t></x:si><x:si><x:t>Demo Industries Inc.</x:t></x:si><x:si><x:t>p-101</x:t></x:si><x:si><x:t>Long</x:t></x:si><x:si><x:t>12/02/2025 09:30:00</x:t></x:si><x:si><x:t>X1</x:t></x:si><x:si><x:t>Stocks</x:t></x:si><x:si><x:t>XX0000000001</x:t></x:si><x:si><x:t>Indice Monde UCITS ETF</x:t></x:si><x:si><x:t>p-102</x:t></x:si><x:si><x:t>03/03/2025 11:00:00</x:t></x:si><x:si><x:t>ETF</x:t></x:si><x:si><x:t>XX0000000002</x:t></x:si><x:si><x:t>p-901</x:t></x:si><x:si><x:t>18/11/2024 09:00:00</x:t></x:si><x:si><x:t>Bitcoin</x:t></x:si><x:si><x:t>p-103</x:t></x:si><x:si><x:t>20/05/2025 16:45:00</x:t></x:si><x:si><x:t>Crypto Currencies</x:t></x:si><x:si><x:t>-</x:t></x:si><x:si><x:t>Identifiant de position</x:t></x:si><x:si><x:t>Action</x:t></x:si><x:si><x:t>Long / Short</x:t></x:si><x:si><x:t>Montant</x:t></x:si><x:si><x:t>Unités</x:t></x:si><x:si><x:t>Date d'ouverture</x:t></x:si><x:si><x:t>Date de clôture</x:t></x:si><x:si><x:t>Effet de levier</x:t></x:si><x:si><x:t>Frais de spread (USD)</x:t></x:si><x:si><x:t>Spread du marché (USD)</x:t></x:si><x:si><x:t>Profit (USD)</x:t></x:si><x:si><x:t>Profit (EUR)</x:t></x:si><x:si><x:t>Taux de change à l'ouverture (USD)</x:t></x:si><x:si><x:t>Taux de change à la clôture (USD)</x:t></x:si><x:si><x:t>Taux à l'ouverture</x:t></x:si><x:si><x:t>Taux à la clôture</x:t></x:si><x:si><x:t>Taux Take Profit</x:t></x:si><x:si><x:t>Taux Stop Loss</x:t></x:si><x:si><x:t>Frais overnight et dividendes</x:t></x:si><x:si><x:t>Copie de</x:t></x:si><x:si><x:t>Remarques</x:t></x:si><x:si><x:t>p-201</x:t></x:si><x:si><x:t>Demo Industries Inc. (DEMO)</x:t></x:si><x:si><x:t>05/01/2025 10:00:00</x:t></x:si><x:si><x:t>10/04/2025 15:00:00</x:t></x:si><x:si><x:t>1</x:t></x:si><x:si><x:t>Actions</x:t></x:si><x:si><x:t>p-202</x:t></x:si><x:si><x:t>Pétrole (OIL)</x:t></x:si><x:si><x:t>06/01/2025 10:00:00</x:t></x:si><x:si><x:t>11/04/2025 15:00:00</x:t></x:si><x:si><x:t>2</x:t></x:si><x:si><x:t>CFD</x:t></x:si><x:si><x:t>XX0000000005</x:t></x:si><x:si><x:t>Date</x:t></x:si><x:si><x:t>Détails</x:t></x:si><x:si><x:t>Variation Fonds propres réalisés</x:t></x:si><x:si><x:t>Équité réalisée</x:t></x:si><x:si><x:t>Solde</x:t></x:si><x:si><x:t>Type d'actif</x:t></x:si><x:si><x:t>NWA (fonds non retirables)</x:t></x:si><x:si><x:t>01/02/2025 08:00:00</x:t></x:si><x:si><x:t>Dépôt</x:t></x:si><x:si><x:t>Virement</x:t></x:si><x:si><x:t>Position ouverte</x:t></x:si><x:si><x:t>DEMO/USD</x:t></x:si><x:si><x:t>IDX.DE/EUR</x:t></x:si><x:si><x:t>BTC/USD</x:t></x:si><x:si><x:t>Crypto-monnaies</x:t></x:si><x:si><x:t>02/06/2025 10:00:00</x:t></x:si><x:si><x:t>OIL/USD</x:t></x:si><x:si><x:t>p-104</x:t></x:si><x:si><x:t>15/07/2025 12:00:00</x:t></x:si><x:si><x:t>Frais overnight</x:t></x:si><x:si><x:t>Spread d’ouverture et de clôture</x:t></x:si><x:si><x:t>À l'ouverture</x:t></x:si><x:si><x:t>18/08/2025 15:00:00</x:t></x:si><x:si><x:t>À la fermeture</x:t></x:si><x:si><x:t>01/03/2025 09:00:00</x:t></x:si><x:si><x:t>Paiement des intérêts</x:t></x:si><x:si><x:t>05/03/2025 11:00:00</x:t></x:si><x:si><x:t>Frais de conversion de dépôt</x:t></x:si><x:si><x:t>30/06/2026 06:00:00</x:t></x:si><x:si><x:t>corp action: Split</x:t></x:si><x:si><x:t>DEMO/USD 1:2</x:t></x:si><x:si><x:t>14/04/2026 14:20:00</x:t></x:si><x:si><x:t>NEWCO/USD</x:t></x:si><x:si><x:t>p-301</x:t></x:si><x:si><x:t>Date du paiement</x:t></x:si><x:si><x:t>Nom de l'instrument</x:t></x:si><x:si><x:t>Dividende net reçu (USD)</x:t></x:si><x:si><x:t>Net dividends</x:t></x:si><x:si><x:t>Currency</x:t></x:si><x:si><x:t>Affranchi/Non affranchi</x:t></x:si><x:si><x:t>Crédits d’affranchissement (AUD)</x:t></x:si><x:si><x:t>Dividende net reçu (EUR)</x:t></x:si><x:si><x:t>Taux de retenue à la source (%)</x:t></x:si><x:si><x:t>Montant du prélèvement à la source (USD)</x:t></x:si><x:si><x:t>Montant du prélèvement à la source (EUR)</x:t></x:si><x:si><x:t>15/04/2025</x:t></x:si><x:si><x:t>15 %</x:t></x:si><x:si><x:t>20/05/2025</x:t></x:si><x:si><x:t>25 %</x:t></x:si><x:si><x:t>10/06/2025</x:t></x:si><x:si><x:t>Vanished Corp.</x:t></x:si><x:si><x:t>0 %</x:t></x:si><x:si><x:t>p-999</x:t></x:si><x:si><x:t>XX0000000009</x:t></x:si></x:sst>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?><x:worksheet><x:sheetData><x:row r="1"><x:c r="A1" t="s"><x:v>0</x:v></x:c><x:c r="B1" t="s"><x:v>1</x:v></x:c></x:row><x:row r="2"><x:c r="A2" t="s"><x:v>2</x:v></x:c><x:c r="B2"><x:v>5000</x:v></x:c></x:row><x:row r="3"><x:c r="A3" t="s"><x:v>3</x:v></x:c><x:c r="B3" t="s"><x:v>4</x:v></x:c></x:row></x:sheetData></x:worksheet>
@@ -23,8 +23,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?><x:worksheet><x:sheetData><x:row r="1"><x:c r="A1" t="s"><x:v>37</x:v></x:c><x:c r="B1" t="s"><x:v>38</x:v></x:c><x:c r="C1" t="s"><x:v>39</x:v></x:c><x:c r="D1" t="s"><x:v>40</x:v></x:c><x:c r="E1" t="s"><x:v>41</x:v></x:c><x:c r="F1" t="s"><x:v>42</x:v></x:c><x:c r="G1" t="s"><x:v>43</x:v></x:c><x:c r="H1" t="s"><x:v>44</x:v></x:c><x:c r="I1" t="s"><x:v>45</x:v></x:c><x:c r="J1" t="s"><x:v>46</x:v></x:c><x:c r="K1" t="s"><x:v>47</x:v></x:c><x:c r="L1" t="s"><x:v>48</x:v></x:c><x:c r="M1" t="s"><x:v>49</x:v></x:c><x:c r="N1" t="s"><x:v>50</x:v></x:c><x:c r="O1" t="s"><x:v>51</x:v></x:c><x:c r="P1" t="s"><x:v>52</x:v></x:c><x:c r="Q1" t="s"><x:v>53</x:v></x:c><x:c r="R1" t="s"><x:v>54</x:v></x:c><x:c r="S1" t="s"><x:v>55</x:v></x:c><x:c r="T1" t="s"><x:v>56</x:v></x:c><x:c r="U1" t="s"><x:v>16</x:v></x:c><x:c r="V1" t="s"><x:v>17</x:v></x:c><x:c r="W1" t="s"><x:v>57</x:v></x:c></x:row><x:row r="2"><x:c r="A2" t="s"><x:v>58</x:v></x:c><x:c r="B2" t="s"><x:v>59</x:v></x:c><x:c r="C2" t="s"><x:v>20</x:v></x:c><x:c r="D2"><x:v>200</x:v></x:c><x:c r="E2"><x:v>5</x:v></x:c><x:c r="F2" t="s"><x:v>60</x:v></x:c><x:c r="G2" t="s"><x:v>61</x:v></x:c><x:c r="H2" t="s"><x:v>62</x:v></x:c><x:c r="I2"><x:v>0</x:v></x:c><x:c r="J2"><x:v>0</x:v></x:c><x:c r="K2"><x:v>40</x:v></x:c><x:c r="L2"><x:v>36</x:v></x:c><x:c r="M2"><x:v>1</x:v></x:c><x:c r="N2"><x:v>1</x:v></x:c><x:c r="O2"><x:v>40</x:v></x:c><x:c r="P2"><x:v>48</x:v></x:c><x:c r="Q2"><x:v>0</x:v></x:c><x:c r="R2"><x:v>0</x:v></x:c><x:c r="S2"><x:v>0</x:v></x:c><x:c r="U2" t="s"><x:v>63</x:v></x:c><x:c r="V2" t="s"><x:v>24</x:v></x:c></x:row><x:row r="3"><x:c r="A3" t="s"><x:v>64</x:v></x:c><x:c r="B3" t="s"><x:v>65</x:v></x:c><x:c r="C3" t="s"><x:v>20</x:v></x:c><x:c r="D3"><x:v>100</x:v></x:c><x:c r="E3"><x:v>1</x:v></x:c><x:c r="F3" t="s"><x:v>66</x:v></x:c><x:c r="G3" t="s"><x:v>67</x:v></x:c><x:c r="H3" t="s"><x:v>68</x:v></x:c><x:c r="I3"><x:v>0</x:v></x:c><x:c r="J3"><x:v>0</x:v></x:c><x:c r="K3"><x:v>5</x:v></x:c><x:c r="L3"><x:v>4</x:v></x:c><x:c r="M3"><x:v>1</x:v></x:c><x:c r="N3"><x:v>1</x:v></x:c><x:c r="O3"><x:v>100</x:v></x:c><x:c r="P3"><x:v>105</x:v></x:c><x:c r="Q3"><x:v>0</x:v></x:c><x:c r="R3"><x:v>0</x:v></x:c><x:c r="S3"><x:v>0</x:v></x:c><x:c r="U3" t="s"><x:v>69</x:v></x:c><x:c r="V3" t="s"><x:v>70</x:v></x:c></x:row></x:sheetData></x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?><x:worksheet><x:sheetData><x:row r="1"><x:c r="A1" t="s"><x:v>71</x:v></x:c><x:c r="B1" t="s"><x:v>16</x:v></x:c><x:c r="C1" t="s"><x:v>72</x:v></x:c><x:c r="D1" t="s"><x:v>40</x:v></x:c><x:c r="E1" t="s"><x:v>41</x:v></x:c><x:c r="F1" t="s"><x:v>73</x:v></x:c><x:c r="G1" t="s"><x:v>74</x:v></x:c><x:c r="H1" t="s"><x:v>75</x:v></x:c><x:c r="I1" t="s"><x:v>37</x:v></x:c><x:c r="J1" t="s"><x:v>76</x:v></x:c><x:c r="K1" t="s"><x:v>77</x:v></x:c></x:row><x:row r="2"><x:c r="A2" t="s"><x:v>78</x:v></x:c><x:c r="B2" t="s"><x:v>79</x:v></x:c><x:c r="C2" t="s"><x:v>80</x:v></x:c><x:c r="D2"><x:v>5000</x:v></x:c><x:c r="E2" t="s"><x:v>36</x:v></x:c><x:c r="F2"><x:v>0</x:v></x:c><x:c r="G2"><x:v>0</x:v></x:c><x:c r="H2"><x:v>5000</x:v></x:c><x:c r="J2" t="s"><x:v>36</x:v></x:c><x:c r="K2"><x:v>0</x:v></x:c></x:row><x:row r="3"><x:c r="A3" t="s"><x:v>60</x:v></x:c><x:c r="B3" t="s"><x:v>81</x:v></x:c><x:c r="C3" t="s"><x:v>82</x:v></x:c><x:c r="D3"><x:v>200</x:v></x:c><x:c r="E3"><x:v>5</x:v></x:c><x:c r="F3"><x:v>0</x:v></x:c><x:c r="G3"><x:v>0</x:v></x:c><x:c r="H3"><x:v>4800</x:v></x:c><x:c r="I3" t="s"><x:v>58</x:v></x:c><x:c r="J3" t="s"><x:v>63</x:v></x:c><x:c r="K3"><x:v>0</x:v></x:c></x:row><x:row r="4"><x:c r="A4" t="s"><x:v>21</x:v></x:c><x:c r="B4" t="s"><x:v>81</x:v></x:c><x:c r="C4" t="s"><x:v>82</x:v></x:c><x:c r="D4"><x:v>400</x:v></x:c><x:c r="E4"><x:v>10</x:v></x:c><x:c r="F4"><x:v>0</x:v></x:c><x:c r="G4"><x:v>0</x:v></x:c><x:c r="H4"><x:v>4600</x:v></x:c><x:c r="I4" t="s"><x:v>19</x:v></x:c><x:c r="J4" t="s"><x:v>63</x:v></x:c><x:c r="K4"><x:v>0</x:v></x:c></x:row><x:row r="5"><x:c r="A5" t="s"><x:v>27</x:v></x:c><x:c r="B5" t="s"><x:v>81</x:v></x:c><x:c r="C5" t="s"><x:v>83</x:v></x:c><x:c r="D5"><x:v>450</x:v></x:c><x:c r="E5"><x:v>5</x:v></x:c><x:c r="F5"><x:v>0</x:v></x:c><x:c r="G5"><x:v>0</x:v></x:c><x:c r="H5"><x:v>4150</x:v></x:c><x:c r="I5" t="s"><x:v>26</x:v></x:c><x:c r="J5" t="s"><x:v>28</x:v></x:c><x:c r="K5"><x:v>0</x:v></x:c></x:row><x:row r="6"><x:c r="A6" t="s"><x:v>34</x:v></x:c><x:c r="B6" t="s"><x:v>81</x:v></x:c><x:c r="C6" t="s"><x:v>84</x:v></x:c><x:c r="D6"><x:v>600</x:v></x:c><x:c r="E6"><x:v>2</x:v></x:c><x:c r="F6"><x:v>0</x:v></x:c><x:c r="G6"><x:v>0</x:v></x:c><x:c r="H6"><x:v>3550</x:v></x:c><x:c r="I6" t="s"><x:v>33</x:v></x:c><x:c r="J6" t="s"><x:v>85</x:v></x:c><x:c r="K6"><x:v>0</x:v></x:c></x:row><x:row r="7"><x:c r="A7" t="s"><x:v>86</x:v></x:c><x:c r="B7" t="s"><x:v>81</x:v></x:c><x:c r="C7" t="s"><x:v>87</x:v></x:c><x:c r="D7"><x:v>60</x:v></x:c><x:c r="E7"><x:v>3</x:v></x:c><x:c r="F7"><x:v>0</x:v></x:c><x:c r="G7"><x:v>0</x:v></x:c><x:c r="H7"><x:v>3490</x:v></x:c><x:c r="I7" t="s"><x:v>88</x:v></x:c><x:c r="J7" t="s"><x:v>69</x:v></x:c><x:c r="K7"><x:v>0</x:v></x:c></x:row><x:row r="8"><x:c r="A8" t="s"><x:v>89</x:v></x:c><x:c r="B8" t="s"><x:v>90</x:v></x:c><x:c r="C8" t="s"><x:v>87</x:v></x:c><x:c r="D8"><x:v>-2</x:v></x:c><x:c r="E8" t="s"><x:v>36</x:v></x:c><x:c r="F8"><x:v>0</x:v></x:c><x:c r="G8"><x:v>0</x:v></x:c><x:c r="H8"><x:v>3488</x:v></x:c><x:c r="I8" t="s"><x:v>88</x:v></x:c><x:c r="J8" t="s"><x:v>69</x:v></x:c><x:c r="K8"><x:v>0</x:v></x:c></x:row><x:row r="9"><x:c r="A9" t="s"><x:v>21</x:v></x:c><x:c r="B9" t="s"><x:v>91</x:v></x:c><x:c r="C9" t="s"><x:v>92</x:v></x:c><x:c r="D9"><x:v>-4</x:v></x:c><x:c r="E9" t="s"><x:v>36</x:v></x:c><x:c r="F9"><x:v>0</x:v></x:c><x:c r="G9"><x:v>0</x:v></x:c><x:c r="H9"><x:v>4596</x:v></x:c><x:c r="I9" t="s"><x:v>19</x:v></x:c><x:c r="J9" t="s"><x:v>63</x:v></x:c><x:c r="K9"><x:v>0</x:v></x:c></x:row><x:row r="10"><x:c r="A10" t="s"><x:v>93</x:v></x:c><x:c r="B10" t="s"><x:v>91</x:v></x:c><x:c r="C10" t="s"><x:v>94</x:v></x:c><x:c r="D10"><x:v>-3</x:v></x:c><x:c r="E10" t="s"><x:v>36</x:v></x:c><x:c r="F10"><x:v>0</x:v></x:c><x:c r="G10"><x:v>0</x:v></x:c><x:c r="H10"><x:v>4593</x:v></x:c><x:c r="I10" t="s"><x:v>58</x:v></x:c><x:c r="J10" t="s"><x:v>63</x:v></x:c><x:c r="K10"><x:v>0</x:v></x:c></x:row><x:row r="11"><x:c r="A11" t="s"><x:v>86</x:v></x:c><x:c r="B11" t="s"><x:v>91</x:v></x:c><x:c r="C11" t="s"><x:v>92</x:v></x:c><x:c r="D11"><x:v>-1</x:v></x:c><x:c r="E11" t="s"><x:v>36</x:v></x:c><x:c r="F11"><x:v>0</x:v></x:c><x:c r="G11"><x:v>0</x:v></x:c><x:c r="H11"><x:v>3489</x:v></x:c><x:c r="I11" t="s"><x:v>88</x:v></x:c><x:c r="J11" t="s"><x:v>69</x:v></x:c><x:c r="K11"><x:v>0</x:v></x:c></x:row><x:row r="12"><x:c r="A12" t="s"><x:v>95</x:v></x:c><x:c r="B12" t="s"><x:v>96</x:v></x:c><x:c r="C12" t="s"><x:v>36</x:v></x:c><x:c r="D12"><x:v>1.5</x:v></x:c><x:c r="E12" t="s"><x:v>36</x:v></x:c><x:c r="F12"><x:v>1.5</x:v></x:c><x:c r="G12"><x:v>0</x:v></x:c><x:c r="H12"><x:v>4601</x:v></x:c><x:c r="J12" t="s"><x:v>36</x:v></x:c><x:c r="K12"><x:v>0</x:v></x:c></x:row><x:row r="13"><x:c r="A13" t="s"><x:v>97</x:v></x:c><x:c r="B13" t="s"><x:v>98</x:v></x:c><x:c r="C13" t="s"><x:v>99</x:v></x:c><x:c r="D13"><x:v>0</x:v></x:c><x:c r="E13" t="s"><x:v>36</x:v></x:c><x:c r="F13"><x:v>0</x:v></x:c><x:c r="G13"><x:v>0</x:v></x:c><x:c r="H13"><x:v>0</x:v></x:c><x:c r="I13" t="s"><x:v>19</x:v></x:c><x:c r="J13" t="s"><x:v>63</x:v></x:c><x:c r="K13"><x:v>0</x:v></x:c></x:row><x:row r="14"><x:c r="A14" t="s"><x:v>100</x:v></x:c><x:c r="B14" t="s"><x:v>81</x:v></x:c><x:c r="C14" t="s"><x:v>101</x:v></x:c><x:c r="D14"><x:v>300</x:v></x:c><x:c r="E14"><x:v>4</x:v></x:c><x:c r="F14"><x:v>0</x:v></x:c><x:c r="G14"><x:v>0</x:v></x:c><x:c r="H14"><x:v>3190</x:v></x:c><x:c r="I14" t="s"><x:v>102</x:v></x:c><x:c r="J14" t="s"><x:v>63</x:v></x:c><x:c r="K14"><x:v>0</x:v></x:c></x:row></x:sheetData></x:worksheet>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?><x:worksheet><x:sheetData><x:row r="1"><x:c r="A1" t="s"><x:v>71</x:v></x:c><x:c r="B1" t="s"><x:v>16</x:v></x:c><x:c r="C1" t="s"><x:v>72</x:v></x:c><x:c r="D1" t="s"><x:v>40</x:v></x:c><x:c r="E1" t="s"><x:v>41</x:v></x:c><x:c r="F1" t="s"><x:v>73</x:v></x:c><x:c r="G1" t="s"><x:v>74</x:v></x:c><x:c r="H1" t="s"><x:v>75</x:v></x:c><x:c r="I1" t="s"><x:v>37</x:v></x:c><x:c r="J1" t="s"><x:v>76</x:v></x:c><x:c r="K1" t="s"><x:v>77</x:v></x:c></x:row><x:row r="2"><x:c r="A2" t="s"><x:v>78</x:v></x:c><x:c r="B2" t="s"><x:v>79</x:v></x:c><x:c r="C2" t="s"><x:v>80</x:v></x:c><x:c r="D2"><x:v>5000</x:v></x:c><x:c r="E2" t="s"><x:v>36</x:v></x:c><x:c r="F2"><x:v>0</x:v></x:c><x:c r="G2"><x:v>0</x:v></x:c><x:c r="H2"><x:v>5000</x:v></x:c><x:c r="J2" t="s"><x:v>36</x:v></x:c><x:c r="K2"><x:v>0</x:v></x:c></x:row><x:row r="3"><x:c r="A3" t="s"><x:v>60</x:v></x:c><x:c r="B3" t="s"><x:v>81</x:v></x:c><x:c r="C3" t="s"><x:v>82</x:v></x:c><x:c r="D3"><x:v>200</x:v></x:c><x:c r="E3"><x:v>5</x:v></x:c><x:c r="F3"><x:v>0</x:v></x:c><x:c r="G3"><x:v>0</x:v></x:c><x:c r="H3"><x:v>4800</x:v></x:c><x:c r="I3" t="s"><x:v>58</x:v></x:c><x:c r="J3" t="s"><x:v>63</x:v></x:c><x:c r="K3"><x:v>0</x:v></x:c></x:row><x:row r="4"><x:c r="A4" t="s"><x:v>21</x:v></x:c><x:c r="B4" t="s"><x:v>81</x:v></x:c><x:c r="C4" t="s"><x:v>82</x:v></x:c><x:c r="D4"><x:v>400</x:v></x:c><x:c r="E4"><x:v>10</x:v></x:c><x:c r="F4"><x:v>0</x:v></x:c><x:c r="G4"><x:v>0</x:v></x:c><x:c r="H4"><x:v>4600</x:v></x:c><x:c r="I4" t="s"><x:v>19</x:v></x:c><x:c r="J4" t="s"><x:v>63</x:v></x:c><x:c r="K4"><x:v>0</x:v></x:c></x:row><x:row r="5"><x:c r="A5" t="s"><x:v>27</x:v></x:c><x:c r="B5" t="s"><x:v>81</x:v></x:c><x:c r="C5" t="s"><x:v>83</x:v></x:c><x:c r="D5"><x:v>450</x:v></x:c><x:c r="E5"><x:v>5</x:v></x:c><x:c r="F5"><x:v>0</x:v></x:c><x:c r="G5"><x:v>0</x:v></x:c><x:c r="H5"><x:v>4150</x:v></x:c><x:c r="I5" t="s"><x:v>26</x:v></x:c><x:c r="J5" t="s"><x:v>28</x:v></x:c><x:c r="K5"><x:v>0</x:v></x:c></x:row><x:row r="6"><x:c r="A6" t="s"><x:v>34</x:v></x:c><x:c r="B6" t="s"><x:v>81</x:v></x:c><x:c r="C6" t="s"><x:v>84</x:v></x:c><x:c r="D6"><x:v>600</x:v></x:c><x:c r="E6"><x:v>2</x:v></x:c><x:c r="F6"><x:v>0</x:v></x:c><x:c r="G6"><x:v>0</x:v></x:c><x:c r="H6"><x:v>3550</x:v></x:c><x:c r="I6" t="s"><x:v>33</x:v></x:c><x:c r="J6" t="s"><x:v>85</x:v></x:c><x:c r="K6"><x:v>0</x:v></x:c></x:row><x:row r="7"><x:c r="A7" t="s"><x:v>86</x:v></x:c><x:c r="B7" t="s"><x:v>81</x:v></x:c><x:c r="C7" t="s"><x:v>87</x:v></x:c><x:c r="D7"><x:v>60</x:v></x:c><x:c r="E7"><x:v>3</x:v></x:c><x:c r="F7"><x:v>0</x:v></x:c><x:c r="G7"><x:v>0</x:v></x:c><x:c r="H7"><x:v>3490</x:v></x:c><x:c r="I7" t="s"><x:v>88</x:v></x:c><x:c r="J7" t="s"><x:v>69</x:v></x:c><x:c r="K7"><x:v>0</x:v></x:c></x:row><x:row r="8"><x:c r="A8" t="s"><x:v>89</x:v></x:c><x:c r="B8" t="s"><x:v>90</x:v></x:c><x:c r="C8" t="s"><x:v>87</x:v></x:c><x:c r="D8"><x:v>-2</x:v></x:c><x:c r="E8" t="s"><x:v>36</x:v></x:c><x:c r="F8"><x:v>0</x:v></x:c><x:c r="G8"><x:v>0</x:v></x:c><x:c r="H8"><x:v>3488</x:v></x:c><x:c r="I8" t="s"><x:v>88</x:v></x:c><x:c r="J8" t="s"><x:v>69</x:v></x:c><x:c r="K8"><x:v>0</x:v></x:c></x:row><x:row r="9"><x:c r="A9" t="s"><x:v>21</x:v></x:c><x:c r="B9" t="s"><x:v>91</x:v></x:c><x:c r="C9" t="s"><x:v>92</x:v></x:c><x:c r="D9"><x:v>-4</x:v></x:c><x:c r="E9" t="s"><x:v>36</x:v></x:c><x:c r="F9"><x:v>0</x:v></x:c><x:c r="G9"><x:v>0</x:v></x:c><x:c r="H9"><x:v>4596</x:v></x:c><x:c r="I9" t="s"><x:v>19</x:v></x:c><x:c r="J9" t="s"><x:v>63</x:v></x:c><x:c r="K9"><x:v>0</x:v></x:c></x:row><x:row r="10"><x:c r="A10" t="s"><x:v>93</x:v></x:c><x:c r="B10" t="s"><x:v>91</x:v></x:c><x:c r="C10" t="s"><x:v>94</x:v></x:c><x:c r="D10"><x:v>-3</x:v></x:c><x:c r="E10" t="s"><x:v>36</x:v></x:c><x:c r="F10"><x:v>0</x:v></x:c><x:c r="G10"><x:v>0</x:v></x:c><x:c r="H10"><x:v>4593</x:v></x:c><x:c r="I10" t="s"><x:v>58</x:v></x:c><x:c r="J10" t="s"><x:v>63</x:v></x:c><x:c r="K10"><x:v>0</x:v></x:c></x:row><x:row r="11"><x:c r="A11" t="s"><x:v>86</x:v></x:c><x:c r="B11" t="s"><x:v>91</x:v></x:c><x:c r="C11" t="s"><x:v>92</x:v></x:c><x:c r="D11"><x:v>-1</x:v></x:c><x:c r="E11" t="s"><x:v>36</x:v></x:c><x:c r="F11"><x:v>0</x:v></x:c><x:c r="G11"><x:v>0</x:v></x:c><x:c r="H11"><x:v>3489</x:v></x:c><x:c r="I11" t="s"><x:v>88</x:v></x:c><x:c r="J11" t="s"><x:v>69</x:v></x:c><x:c r="K11"><x:v>0</x:v></x:c></x:row><x:row r="12"><x:c r="A12" t="s"><x:v>95</x:v></x:c><x:c r="B12" t="s"><x:v>96</x:v></x:c><x:c r="C12" t="s"><x:v>36</x:v></x:c><x:c r="D12"><x:v>1.5</x:v></x:c><x:c r="E12" t="s"><x:v>36</x:v></x:c><x:c r="F12"><x:v>1.5</x:v></x:c><x:c r="G12"><x:v>0</x:v></x:c><x:c r="H12"><x:v>4601</x:v></x:c><x:c r="J12" t="s"><x:v>36</x:v></x:c><x:c r="K12"><x:v>0</x:v></x:c></x:row><x:row r="13"><x:c r="A13" t="s"><x:v>97</x:v></x:c><x:c r="B13" t="s"><x:v>98</x:v></x:c><x:c r="C13" t="s"><x:v>36</x:v></x:c><x:c r="D13"><x:v>-0.4</x:v></x:c><x:c r="E13" t="s"><x:v>36</x:v></x:c><x:c r="F13"><x:v>0</x:v></x:c><x:c r="G13"><x:v>0</x:v></x:c><x:c r="H13"><x:v>4600.6</x:v></x:c><x:c r="J13" t="s"><x:v>36</x:v></x:c><x:c r="K13"><x:v>0</x:v></x:c></x:row><x:row r="14"><x:c r="A14" t="s"><x:v>99</x:v></x:c><x:c r="B14" t="s"><x:v>100</x:v></x:c><x:c r="C14" t="s"><x:v>101</x:v></x:c><x:c r="D14"><x:v>0</x:v></x:c><x:c r="E14" t="s"><x:v>36</x:v></x:c><x:c r="F14"><x:v>0</x:v></x:c><x:c r="G14"><x:v>0</x:v></x:c><x:c r="H14"><x:v>0</x:v></x:c><x:c r="I14" t="s"><x:v>19</x:v></x:c><x:c r="J14" t="s"><x:v>63</x:v></x:c><x:c r="K14"><x:v>0</x:v></x:c></x:row><x:row r="15"><x:c r="A15" t="s"><x:v>102</x:v></x:c><x:c r="B15" t="s"><x:v>81</x:v></x:c><x:c r="C15" t="s"><x:v>103</x:v></x:c><x:c r="D15"><x:v>300</x:v></x:c><x:c r="E15"><x:v>4</x:v></x:c><x:c r="F15"><x:v>0</x:v></x:c><x:c r="G15"><x:v>0</x:v></x:c><x:c r="H15"><x:v>3190</x:v></x:c><x:c r="I15" t="s"><x:v>104</x:v></x:c><x:c r="J15" t="s"><x:v>63</x:v></x:c><x:c r="K15"><x:v>0</x:v></x:c></x:row></x:sheetData></x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?><x:worksheet><x:sheetData><x:row r="1"><x:c r="A1" t="s"><x:v>103</x:v></x:c><x:c r="B1" t="s"><x:v>104</x:v></x:c><x:c r="C1" t="s"><x:v>105</x:v></x:c><x:c r="D1" t="s"><x:v>106</x:v></x:c><x:c r="E1" t="s"><x:v>107</x:v></x:c><x:c r="F1" t="s"><x:v>108</x:v></x:c><x:c r="G1" t="s"><x:v>109</x:v></x:c><x:c r="H1" t="s"><x:v>110</x:v></x:c><x:c r="I1" t="s"><x:v>111</x:v></x:c><x:c r="J1" t="s"><x:v>112</x:v></x:c><x:c r="K1" t="s"><x:v>113</x:v></x:c><x:c r="L1" t="s"><x:v>37</x:v></x:c><x:c r="M1" t="s"><x:v>16</x:v></x:c><x:c r="N1" t="s"><x:v>17</x:v></x:c></x:row><x:row r="2"><x:c r="A2" t="s"><x:v>114</x:v></x:c><x:c r="B2" t="s"><x:v>18</x:v></x:c><x:c r="C2"><x:v>0.5</x:v></x:c><x:c r="D2"><x:v>0</x:v></x:c><x:c r="F2" t="s"><x:v>36</x:v></x:c><x:c r="G2" t="s"><x:v>36</x:v></x:c><x:c r="H2"><x:v>0.45</x:v></x:c><x:c r="I2" t="s"><x:v>115</x:v></x:c><x:c r="J2"><x:v>0.08</x:v></x:c><x:c r="K2"><x:v>0.075</x:v></x:c><x:c r="L2" t="s"><x:v>19</x:v></x:c><x:c r="M2" t="s"><x:v>23</x:v></x:c><x:c r="N2" t="s"><x:v>24</x:v></x:c></x:row><x:row r="3"><x:c r="A3" t="s"><x:v>116</x:v></x:c><x:c r="B3" t="s"><x:v>18</x:v></x:c><x:c r="C3"><x:v>0.2</x:v></x:c><x:c r="D3"><x:v>0</x:v></x:c><x:c r="F3" t="s"><x:v>36</x:v></x:c><x:c r="G3" t="s"><x:v>36</x:v></x:c><x:c r="H3"><x:v>0.18</x:v></x:c><x:c r="I3" t="s"><x:v>117</x:v></x:c><x:c r="J3"><x:v>0.07</x:v></x:c><x:c r="K3"><x:v>0.06</x:v></x:c><x:c r="L3" t="s"><x:v>30</x:v></x:c><x:c r="M3" t="s"><x:v>23</x:v></x:c><x:c r="N3" t="s"><x:v>24</x:v></x:c></x:row><x:row r="4"><x:c r="A4" t="s"><x:v>118</x:v></x:c><x:c r="B4" t="s"><x:v>119</x:v></x:c><x:c r="C4"><x:v>0.1</x:v></x:c><x:c r="D4"><x:v>0</x:v></x:c><x:c r="F4" t="s"><x:v>36</x:v></x:c><x:c r="G4" t="s"><x:v>36</x:v></x:c><x:c r="H4"><x:v>0.09</x:v></x:c><x:c r="I4" t="s"><x:v>120</x:v></x:c><x:c r="J4"><x:v>0</x:v></x:c><x:c r="K4"><x:v>0</x:v></x:c><x:c r="L4" t="s"><x:v>121</x:v></x:c><x:c r="M4" t="s"><x:v>23</x:v></x:c><x:c r="N4" t="s"><x:v>122</x:v></x:c></x:row></x:sheetData></x:worksheet>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?><x:worksheet><x:sheetData><x:row r="1"><x:c r="A1" t="s"><x:v>105</x:v></x:c><x:c r="B1" t="s"><x:v>106</x:v></x:c><x:c r="C1" t="s"><x:v>107</x:v></x:c><x:c r="D1" t="s"><x:v>108</x:v></x:c><x:c r="E1" t="s"><x:v>109</x:v></x:c><x:c r="F1" t="s"><x:v>110</x:v></x:c><x:c r="G1" t="s"><x:v>111</x:v></x:c><x:c r="H1" t="s"><x:v>112</x:v></x:c><x:c r="I1" t="s"><x:v>113</x:v></x:c><x:c r="J1" t="s"><x:v>114</x:v></x:c><x:c r="K1" t="s"><x:v>115</x:v></x:c><x:c r="L1" t="s"><x:v>37</x:v></x:c><x:c r="M1" t="s"><x:v>16</x:v></x:c><x:c r="N1" t="s"><x:v>17</x:v></x:c></x:row><x:row r="2"><x:c r="A2" t="s"><x:v>116</x:v></x:c><x:c r="B2" t="s"><x:v>18</x:v></x:c><x:c r="C2"><x:v>0.5</x:v></x:c><x:c r="D2"><x:v>0</x:v></x:c><x:c r="F2" t="s"><x:v>36</x:v></x:c><x:c r="G2" t="s"><x:v>36</x:v></x:c><x:c r="H2"><x:v>0.45</x:v></x:c><x:c r="I2" t="s"><x:v>117</x:v></x:c><x:c r="J2"><x:v>0.08</x:v></x:c><x:c r="K2"><x:v>0.075</x:v></x:c><x:c r="L2" t="s"><x:v>19</x:v></x:c><x:c r="M2" t="s"><x:v>23</x:v></x:c><x:c r="N2" t="s"><x:v>24</x:v></x:c></x:row><x:row r="3"><x:c r="A3" t="s"><x:v>118</x:v></x:c><x:c r="B3" t="s"><x:v>18</x:v></x:c><x:c r="C3"><x:v>0.2</x:v></x:c><x:c r="D3"><x:v>0</x:v></x:c><x:c r="F3" t="s"><x:v>36</x:v></x:c><x:c r="G3" t="s"><x:v>36</x:v></x:c><x:c r="H3"><x:v>0.18</x:v></x:c><x:c r="I3" t="s"><x:v>119</x:v></x:c><x:c r="J3"><x:v>0.07</x:v></x:c><x:c r="K3"><x:v>0.06</x:v></x:c><x:c r="L3" t="s"><x:v>30</x:v></x:c><x:c r="M3" t="s"><x:v>23</x:v></x:c><x:c r="N3" t="s"><x:v>24</x:v></x:c></x:row><x:row r="4"><x:c r="A4" t="s"><x:v>120</x:v></x:c><x:c r="B4" t="s"><x:v>121</x:v></x:c><x:c r="C4"><x:v>0.1</x:v></x:c><x:c r="D4"><x:v>0</x:v></x:c><x:c r="F4" t="s"><x:v>36</x:v></x:c><x:c r="G4" t="s"><x:v>36</x:v></x:c><x:c r="H4"><x:v>0.09</x:v></x:c><x:c r="I4" t="s"><x:v>122</x:v></x:c><x:c r="J4"><x:v>0</x:v></x:c><x:c r="K4"><x:v>0</x:v></x:c><x:c r="L4" t="s"><x:v>123</x:v></x:c><x:c r="M4" t="s"><x:v>23</x:v></x:c><x:c r="N4" t="s"><x:v>124</x:v></x:c></x:row></x:sheetData></x:worksheet>
 </file>